--- a/flask_backend/test_output/auto_bianche.xlsx
+++ b/flask_backend/test_output/auto_bianche.xlsx
@@ -499,7 +499,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L591"/>
+  <dimension ref="A1:L560"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -3256,7 +3256,7 @@
         </is>
       </c>
       <c r="F161" s="9" t="n">
-        <v>14375</v>
+        <v>12083</v>
       </c>
       <c r="G161" s="6" t="n"/>
       <c r="H161" s="6" t="n"/>
@@ -3307,7 +3307,7 @@
         </is>
       </c>
       <c r="F164" s="9" t="n">
-        <v>12808</v>
+        <v>636</v>
       </c>
       <c r="G164" s="6" t="n"/>
       <c r="H164" s="6" t="n"/>
@@ -3343,11 +3343,11 @@
       <c r="A166" s="7" t="n"/>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>( HP5123 )</t>
+          <t>SL 72 RTN ( IH5569 )</t>
         </is>
       </c>
       <c r="F166" s="9" t="n">
-        <v>3530</v>
+        <v>830</v>
       </c>
       <c r="G166" s="6" t="n"/>
       <c r="H166" s="6" t="n"/>
@@ -3360,11 +3360,11 @@
       <c r="A167" s="7" t="n"/>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t>( HP5124 )</t>
+          <t>SL 72 RS ( JI1281 )</t>
         </is>
       </c>
       <c r="F167" s="9" t="n">
-        <v>5030</v>
+        <v>16</v>
       </c>
       <c r="G167" s="6" t="n"/>
       <c r="H167" s="6" t="n"/>
@@ -3377,11 +3377,11 @@
       <c r="A168" s="7" t="n"/>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RTN ( IH5569 )</t>
+          <t>SL 72 RS ( JI1282 )</t>
         </is>
       </c>
       <c r="F168" s="9" t="n">
-        <v>830</v>
+        <v>1399</v>
       </c>
       <c r="G168" s="6" t="n"/>
       <c r="H168" s="6" t="n"/>
@@ -3394,11 +3394,11 @@
       <c r="A169" s="7" t="n"/>
       <c r="B169" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( JI1281 )</t>
+          <t>SL 72 RS ( JQ9555 )</t>
         </is>
       </c>
       <c r="F169" s="9" t="n">
-        <v>16</v>
+        <v>951</v>
       </c>
       <c r="G169" s="6" t="n"/>
       <c r="H169" s="6" t="n"/>
@@ -3411,11 +3411,11 @@
       <c r="A170" s="7" t="n"/>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( JI1282 )</t>
+          <t>SL 72 RS ( KH9644 )</t>
         </is>
       </c>
       <c r="F170" s="9" t="n">
-        <v>3464</v>
+        <v>181</v>
       </c>
       <c r="G170" s="6" t="n"/>
       <c r="H170" s="6" t="n"/>
@@ -3428,11 +3428,11 @@
       <c r="A171" s="7" t="n"/>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( JQ9555 )</t>
+          <t>SL 72 RS ( KH9646 )</t>
         </is>
       </c>
       <c r="F171" s="9" t="n">
-        <v>951</v>
+        <v>502</v>
       </c>
       <c r="G171" s="6" t="n"/>
       <c r="H171" s="6" t="n"/>
@@ -3445,11 +3445,11 @@
       <c r="A172" s="7" t="n"/>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9644 )</t>
+          <t>SL 72 RS ( KH9647 )</t>
         </is>
       </c>
       <c r="F172" s="9" t="n">
-        <v>829</v>
+        <v>310</v>
       </c>
       <c r="G172" s="6" t="n"/>
       <c r="H172" s="6" t="n"/>
@@ -3462,11 +3462,11 @@
       <c r="A173" s="7" t="n"/>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9646 )</t>
+          <t>SL 72 RS ( KH9648 )</t>
         </is>
       </c>
       <c r="F173" s="9" t="n">
-        <v>1350</v>
+        <v>1777</v>
       </c>
       <c r="G173" s="6" t="n"/>
       <c r="H173" s="6" t="n"/>
@@ -3479,11 +3479,11 @@
       <c r="A174" s="7" t="n"/>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9647 )</t>
+          <t>SL 72 RS ( KH9650 )</t>
         </is>
       </c>
       <c r="F174" s="9" t="n">
-        <v>310</v>
+        <v>749</v>
       </c>
       <c r="G174" s="6" t="n"/>
       <c r="H174" s="6" t="n"/>
@@ -3496,11 +3496,11 @@
       <c r="A175" s="7" t="n"/>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9648 )</t>
+          <t>SL 72 RS ( KH9651 )</t>
         </is>
       </c>
       <c r="F175" s="9" t="n">
-        <v>2209</v>
+        <v>1012</v>
       </c>
       <c r="G175" s="6" t="n"/>
       <c r="H175" s="6" t="n"/>
@@ -3513,11 +3513,11 @@
       <c r="A176" s="7" t="n"/>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9650 )</t>
+          <t>SL 72 RS ( KH9652 )</t>
         </is>
       </c>
       <c r="F176" s="9" t="n">
-        <v>749</v>
+        <v>1912</v>
       </c>
       <c r="G176" s="6" t="n"/>
       <c r="H176" s="6" t="n"/>
@@ -3530,11 +3530,11 @@
       <c r="A177" s="7" t="n"/>
       <c r="B177" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9651 )</t>
+          <t>SL 72 RS ( KH9653 )</t>
         </is>
       </c>
       <c r="F177" s="9" t="n">
-        <v>1012</v>
+        <v>1755</v>
       </c>
       <c r="G177" s="6" t="n"/>
       <c r="H177" s="6" t="n"/>
@@ -3547,11 +3547,11 @@
       <c r="A178" s="7" t="n"/>
       <c r="B178" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9652 )</t>
+          <t>SL 72 RS ( KJ1674 )</t>
         </is>
       </c>
       <c r="F178" s="9" t="n">
-        <v>2640</v>
+        <v>2012</v>
       </c>
       <c r="G178" s="6" t="n"/>
       <c r="H178" s="6" t="n"/>
@@ -3564,11 +3564,11 @@
       <c r="A179" s="7" t="n"/>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9653 )</t>
+          <t>SL 72 RS J ( KJ7404 )</t>
         </is>
       </c>
       <c r="F179" s="9" t="n">
-        <v>6668</v>
+        <v>300</v>
       </c>
       <c r="G179" s="6" t="n"/>
       <c r="H179" s="6" t="n"/>
@@ -3577,32 +3577,28 @@
       <c r="K179" s="6" t="n"/>
       <c r="L179" s="6" t="n"/>
     </row>
-    <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="7" t="n"/>
-      <c r="B180" s="8" t="inlineStr">
-        <is>
-          <t>SL 72 RS ( KH9656 )</t>
-        </is>
-      </c>
-      <c r="F180" s="9" t="n">
-        <v>1466</v>
-      </c>
-      <c r="G180" s="6" t="n"/>
-      <c r="H180" s="6" t="n"/>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="6" t="n"/>
-      <c r="K180" s="6" t="n"/>
-      <c r="L180" s="6" t="n"/>
-    </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="7" t="n"/>
-      <c r="B181" s="8" t="inlineStr">
-        <is>
-          <t>SL 72 RS ( KH9658 )</t>
-        </is>
-      </c>
-      <c r="F181" s="9" t="n">
-        <v>583</v>
+    <row r="180">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 6 （加6部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="18" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
+        <is>
+          <t>6A</t>
+        </is>
+      </c>
+      <c r="B181" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F181" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G181" s="6" t="n"/>
       <c r="H181" s="6" t="n"/>
@@ -3615,11 +3611,11 @@
       <c r="A182" s="7" t="n"/>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1674 )</t>
+          <t>OZGAIA W ( IG6045 )</t>
         </is>
       </c>
       <c r="F182" s="9" t="n">
-        <v>2715</v>
+        <v>33906</v>
       </c>
       <c r="G182" s="6" t="n"/>
       <c r="H182" s="6" t="n"/>
@@ -3632,11 +3628,11 @@
       <c r="A183" s="7" t="n"/>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS J ( KJ7404 )</t>
+          <t>MEGARIDE ( JH5523 )</t>
         </is>
       </c>
       <c r="F183" s="9" t="n">
-        <v>600</v>
+        <v>620</v>
       </c>
       <c r="G183" s="6" t="n"/>
       <c r="H183" s="6" t="n"/>
@@ -3649,11 +3645,11 @@
       <c r="A184" s="7" t="n"/>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( LA1750 )</t>
+          <t>MEGARIDE ( JP9626 )</t>
         </is>
       </c>
       <c r="F184" s="9" t="n">
-        <v>305</v>
+        <v>967</v>
       </c>
       <c r="G184" s="6" t="n"/>
       <c r="H184" s="6" t="n"/>
@@ -3662,28 +3658,32 @@
       <c r="K184" s="6" t="n"/>
       <c r="L184" s="6" t="n"/>
     </row>
-    <row r="185">
-      <c r="A185" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 6 （加6部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="186" ht="18" customHeight="1">
-      <c r="A186" s="5" t="inlineStr">
-        <is>
-          <t>6A</t>
-        </is>
-      </c>
-      <c r="B186" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F186" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="185" ht="15" customHeight="1">
+      <c r="A185" s="7" t="n"/>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t>MEGA GHOSTRIDE W ( JQ0553 )</t>
+        </is>
+      </c>
+      <c r="F185" s="9" t="n">
+        <v>161</v>
+      </c>
+      <c r="G185" s="6" t="n"/>
+      <c r="H185" s="6" t="n"/>
+      <c r="I185" s="6" t="n"/>
+      <c r="J185" s="6" t="n"/>
+      <c r="K185" s="6" t="n"/>
+      <c r="L185" s="6" t="n"/>
+    </row>
+    <row r="186" ht="15" customHeight="1">
+      <c r="A186" s="7" t="n"/>
+      <c r="B186" s="8" t="inlineStr">
+        <is>
+          <t>MEGARIDE ( KH9590 )</t>
+        </is>
+      </c>
+      <c r="F186" s="9" t="n">
+        <v>2457</v>
       </c>
       <c r="G186" s="6" t="n"/>
       <c r="H186" s="6" t="n"/>
@@ -3696,11 +3696,11 @@
       <c r="A187" s="7" t="n"/>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6045 )</t>
+          <t>MEGA GHOSTRIDE W ( KI4673 )</t>
         </is>
       </c>
       <c r="F187" s="9" t="n">
-        <v>33906</v>
+        <v>1453</v>
       </c>
       <c r="G187" s="6" t="n"/>
       <c r="H187" s="6" t="n"/>
@@ -3713,11 +3713,11 @@
       <c r="A188" s="7" t="n"/>
       <c r="B188" s="8" t="inlineStr">
         <is>
-          <t>MEGARIDE ( JH5523 )</t>
+          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
         </is>
       </c>
       <c r="F188" s="9" t="n">
-        <v>620</v>
+        <v>1800</v>
       </c>
       <c r="G188" s="6" t="n"/>
       <c r="H188" s="6" t="n"/>
@@ -3730,11 +3730,11 @@
       <c r="A189" s="7" t="n"/>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t>MEGARIDE ( JP9626 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F189" s="9" t="n">
-        <v>967</v>
+        <v>5436</v>
       </c>
       <c r="G189" s="6" t="n"/>
       <c r="H189" s="6" t="n"/>
@@ -3747,11 +3747,11 @@
       <c r="A190" s="7" t="n"/>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t>MEGA GHOSTRIDE W ( JQ0553 )</t>
+          <t>F50 TUNIT MEGA JAH JAH ( LA3614 )</t>
         </is>
       </c>
       <c r="F190" s="9" t="n">
-        <v>161</v>
+        <v>909</v>
       </c>
       <c r="G190" s="6" t="n"/>
       <c r="H190" s="6" t="n"/>
@@ -3760,15 +3760,21 @@
       <c r="K190" s="6" t="n"/>
       <c r="L190" s="6" t="n"/>
     </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="7" t="n"/>
-      <c r="B191" s="8" t="inlineStr">
-        <is>
-          <t>MEGARIDE ( KH9590 )</t>
-        </is>
-      </c>
-      <c r="F191" s="9" t="n">
-        <v>2457</v>
+    <row r="191" ht="18" customHeight="1">
+      <c r="A191" s="5" t="inlineStr">
+        <is>
+          <t>6B</t>
+        </is>
+      </c>
+      <c r="B191" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F191" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G191" s="6" t="n"/>
       <c r="H191" s="6" t="n"/>
@@ -3781,11 +3787,11 @@
       <c r="A192" s="7" t="n"/>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t>MEGA GHOSTRIDE W ( KI4673 )</t>
+          <t>GHOST SPRINT BALLET W ( HQ7636 )</t>
         </is>
       </c>
       <c r="F192" s="9" t="n">
-        <v>1453</v>
+        <v>2257</v>
       </c>
       <c r="G192" s="6" t="n"/>
       <c r="H192" s="6" t="n"/>
@@ -3798,11 +3804,11 @@
       <c r="A193" s="7" t="n"/>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
+          <t>GHOST SPRINT W ( HQ7638 )</t>
         </is>
       </c>
       <c r="F193" s="9" t="n">
-        <v>1800</v>
+        <v>241</v>
       </c>
       <c r="G193" s="6" t="n"/>
       <c r="H193" s="6" t="n"/>
@@ -3815,11 +3821,11 @@
       <c r="A194" s="7" t="n"/>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
+          <t>GHOST SPRINT W ( JQ6439 )</t>
         </is>
       </c>
       <c r="F194" s="9" t="n">
-        <v>5436</v>
+        <v>304</v>
       </c>
       <c r="G194" s="6" t="n"/>
       <c r="H194" s="6" t="n"/>
@@ -3832,11 +3838,11 @@
       <c r="A195" s="7" t="n"/>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t>F50 TUNIT MEGA JAH JAH ( LA3614 )</t>
+          <t>GHOST SPRINT BALLET W ( KI0435 )</t>
         </is>
       </c>
       <c r="F195" s="9" t="n">
-        <v>909</v>
+        <v>759</v>
       </c>
       <c r="G195" s="6" t="n"/>
       <c r="H195" s="6" t="n"/>
@@ -3845,21 +3851,15 @@
       <c r="K195" s="6" t="n"/>
       <c r="L195" s="6" t="n"/>
     </row>
-    <row r="196" ht="18" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
-        <is>
-          <t>6B</t>
-        </is>
-      </c>
-      <c r="B196" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F196" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="196" ht="15" customHeight="1">
+      <c r="A196" s="7" t="n"/>
+      <c r="B196" s="8" t="inlineStr">
+        <is>
+          <t>GHOST SPRINT BALLET W ( KI0436 )</t>
+        </is>
+      </c>
+      <c r="F196" s="9" t="n">
+        <v>1204</v>
       </c>
       <c r="G196" s="6" t="n"/>
       <c r="H196" s="6" t="n"/>
@@ -3872,11 +3872,11 @@
       <c r="A197" s="7" t="n"/>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( HQ7636 )</t>
+          <t>GHOST SPRINT W ( KI4563 )</t>
         </is>
       </c>
       <c r="F197" s="9" t="n">
-        <v>2257</v>
+        <v>800</v>
       </c>
       <c r="G197" s="6" t="n"/>
       <c r="H197" s="6" t="n"/>
@@ -3889,11 +3889,11 @@
       <c r="A198" s="7" t="n"/>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( HQ7638 )</t>
+          <t>GHOST SPRINT W ( KI4564 )</t>
         </is>
       </c>
       <c r="F198" s="9" t="n">
-        <v>241</v>
+        <v>403</v>
       </c>
       <c r="G198" s="6" t="n"/>
       <c r="H198" s="6" t="n"/>
@@ -3906,11 +3906,11 @@
       <c r="A199" s="7" t="n"/>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( JQ6439 )</t>
+          <t>GHOST MOTO LOW W ( KI4566 )</t>
         </is>
       </c>
       <c r="F199" s="9" t="n">
-        <v>304</v>
+        <v>1715</v>
       </c>
       <c r="G199" s="6" t="n"/>
       <c r="H199" s="6" t="n"/>
@@ -3923,11 +3923,11 @@
       <c r="A200" s="7" t="n"/>
       <c r="B200" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI0435 )</t>
+          <t>GHOST SPRINT W ( KI4568 )</t>
         </is>
       </c>
       <c r="F200" s="9" t="n">
-        <v>759</v>
+        <v>1390</v>
       </c>
       <c r="G200" s="6" t="n"/>
       <c r="H200" s="6" t="n"/>
@@ -3940,11 +3940,11 @@
       <c r="A201" s="7" t="n"/>
       <c r="B201" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI0436 )</t>
+          <t>GHOST SPRINT W ( KI4569 )</t>
         </is>
       </c>
       <c r="F201" s="9" t="n">
-        <v>1204</v>
+        <v>3064</v>
       </c>
       <c r="G201" s="6" t="n"/>
       <c r="H201" s="6" t="n"/>
@@ -3957,11 +3957,11 @@
       <c r="A202" s="7" t="n"/>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4563 )</t>
+          <t>GHOST SPRINT W ( KI4570 )</t>
         </is>
       </c>
       <c r="F202" s="9" t="n">
-        <v>800</v>
+        <v>100</v>
       </c>
       <c r="G202" s="6" t="n"/>
       <c r="H202" s="6" t="n"/>
@@ -3974,11 +3974,11 @@
       <c r="A203" s="7" t="n"/>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4564 )</t>
+          <t>GHOST SPRINT W ( KI4571 )</t>
         </is>
       </c>
       <c r="F203" s="9" t="n">
-        <v>403</v>
+        <v>280</v>
       </c>
       <c r="G203" s="6" t="n"/>
       <c r="H203" s="6" t="n"/>
@@ -3991,11 +3991,11 @@
       <c r="A204" s="7" t="n"/>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t>GHOST MOTO LOW W ( KI4566 )</t>
+          <t>GHOST SPRINT W ( KI4572 )</t>
         </is>
       </c>
       <c r="F204" s="9" t="n">
-        <v>1715</v>
+        <v>140</v>
       </c>
       <c r="G204" s="6" t="n"/>
       <c r="H204" s="6" t="n"/>
@@ -4008,11 +4008,11 @@
       <c r="A205" s="7" t="n"/>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4568 )</t>
+          <t>GHOST SPRINT W ( KJ0645 )</t>
         </is>
       </c>
       <c r="F205" s="9" t="n">
-        <v>1390</v>
+        <v>1483</v>
       </c>
       <c r="G205" s="6" t="n"/>
       <c r="H205" s="6" t="n"/>
@@ -4025,11 +4025,11 @@
       <c r="A206" s="7" t="n"/>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4569 )</t>
+          <t>GHOST SPRINT W ( LA4019 )</t>
         </is>
       </c>
       <c r="F206" s="9" t="n">
-        <v>3064</v>
+        <v>190</v>
       </c>
       <c r="G206" s="6" t="n"/>
       <c r="H206" s="6" t="n"/>
@@ -4042,11 +4042,11 @@
       <c r="A207" s="7" t="n"/>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4570 )</t>
+          <t>GHOST SPRINT W ( LA7682 )</t>
         </is>
       </c>
       <c r="F207" s="9" t="n">
-        <v>100</v>
+        <v>8803</v>
       </c>
       <c r="G207" s="6" t="n"/>
       <c r="H207" s="6" t="n"/>
@@ -4059,11 +4059,11 @@
       <c r="A208" s="7" t="n"/>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4571 )</t>
+          <t>GHOST SPRINT W ( LA7683 )</t>
         </is>
       </c>
       <c r="F208" s="9" t="n">
-        <v>280</v>
+        <v>5940</v>
       </c>
       <c r="G208" s="6" t="n"/>
       <c r="H208" s="6" t="n"/>
@@ -4072,15 +4072,21 @@
       <c r="K208" s="6" t="n"/>
       <c r="L208" s="6" t="n"/>
     </row>
-    <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="7" t="n"/>
-      <c r="B209" s="8" t="inlineStr">
-        <is>
-          <t>GHOST SPRINT W ( KI4572 )</t>
-        </is>
-      </c>
-      <c r="F209" s="9" t="n">
-        <v>140</v>
+    <row r="209" ht="18" customHeight="1">
+      <c r="A209" s="5" t="inlineStr">
+        <is>
+          <t>6C</t>
+        </is>
+      </c>
+      <c r="B209" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F209" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G209" s="6" t="n"/>
       <c r="H209" s="6" t="n"/>
@@ -4093,11 +4099,11 @@
       <c r="A210" s="7" t="n"/>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KJ0645 )</t>
+          <t>SAMBA ( IH6000 )</t>
         </is>
       </c>
       <c r="F210" s="9" t="n">
-        <v>1483</v>
+        <v>6116</v>
       </c>
       <c r="G210" s="6" t="n"/>
       <c r="H210" s="6" t="n"/>
@@ -4110,11 +4116,11 @@
       <c r="A211" s="7" t="n"/>
       <c r="B211" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( LA4019 )</t>
+          <t>SAMBA ( IH6001 )</t>
         </is>
       </c>
       <c r="F211" s="9" t="n">
-        <v>190</v>
+        <v>7452</v>
       </c>
       <c r="G211" s="6" t="n"/>
       <c r="H211" s="6" t="n"/>
@@ -4127,11 +4133,11 @@
       <c r="A212" s="7" t="n"/>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( LA7682 )</t>
+          <t>SAMBA GOLF ( JH6149 )</t>
         </is>
       </c>
       <c r="F212" s="9" t="n">
-        <v>8803</v>
+        <v>373</v>
       </c>
       <c r="G212" s="6" t="n"/>
       <c r="H212" s="6" t="n"/>
@@ -4144,11 +4150,11 @@
       <c r="A213" s="7" t="n"/>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( LA7683 )</t>
+          <t>SAMBA GOLF ( JH6151 )</t>
         </is>
       </c>
       <c r="F213" s="9" t="n">
-        <v>5940</v>
+        <v>575</v>
       </c>
       <c r="G213" s="6" t="n"/>
       <c r="H213" s="6" t="n"/>
@@ -4157,21 +4163,15 @@
       <c r="K213" s="6" t="n"/>
       <c r="L213" s="6" t="n"/>
     </row>
-    <row r="214" ht="18" customHeight="1">
-      <c r="A214" s="5" t="inlineStr">
-        <is>
-          <t>6C</t>
-        </is>
-      </c>
-      <c r="B214" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F214" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="214" ht="15" customHeight="1">
+      <c r="A214" s="7" t="n"/>
+      <c r="B214" s="8" t="inlineStr">
+        <is>
+          <t>SAMBA GOLF ( KJ5430 )</t>
+        </is>
+      </c>
+      <c r="F214" s="9" t="n">
+        <v>94</v>
       </c>
       <c r="G214" s="6" t="n"/>
       <c r="H214" s="6" t="n"/>
@@ -4184,11 +4184,11 @@
       <c r="A215" s="7" t="n"/>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t>SAMBA ( IH6000 )</t>
+          <t>SAMBA GOLF ( KJ5431 )</t>
         </is>
       </c>
       <c r="F215" s="9" t="n">
-        <v>6116</v>
+        <v>16</v>
       </c>
       <c r="G215" s="6" t="n"/>
       <c r="H215" s="6" t="n"/>
@@ -4201,11 +4201,11 @@
       <c r="A216" s="7" t="n"/>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t>SAMBA ( IH6001 )</t>
+          <t>SAMBA GOLF ( KJ8225 )</t>
         </is>
       </c>
       <c r="F216" s="9" t="n">
-        <v>7452</v>
+        <v>1841</v>
       </c>
       <c r="G216" s="6" t="n"/>
       <c r="H216" s="6" t="n"/>
@@ -4218,11 +4218,11 @@
       <c r="A217" s="7" t="n"/>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t>SAMBA GOLF ( JH6149 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F217" s="9" t="n">
-        <v>373</v>
+        <v>4279</v>
       </c>
       <c r="G217" s="6" t="n"/>
       <c r="H217" s="6" t="n"/>
@@ -4231,32 +4231,28 @@
       <c r="K217" s="6" t="n"/>
       <c r="L217" s="6" t="n"/>
     </row>
-    <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="7" t="n"/>
-      <c r="B218" s="8" t="inlineStr">
-        <is>
-          <t>SAMBA GOLF ( JH6151 )</t>
-        </is>
-      </c>
-      <c r="F218" s="9" t="n">
-        <v>575</v>
-      </c>
-      <c r="G218" s="6" t="n"/>
-      <c r="H218" s="6" t="n"/>
-      <c r="I218" s="6" t="n"/>
-      <c r="J218" s="6" t="n"/>
-      <c r="K218" s="6" t="n"/>
-      <c r="L218" s="6" t="n"/>
-    </row>
-    <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="7" t="n"/>
-      <c r="B219" s="8" t="inlineStr">
-        <is>
-          <t>SAMBA GOLF ( KJ5430 )</t>
-        </is>
-      </c>
-      <c r="F219" s="9" t="n">
-        <v>94</v>
+    <row r="218">
+      <c r="A218" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 7 （加7部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="18" customHeight="1">
+      <c r="A219" s="5" t="inlineStr">
+        <is>
+          <t>7A</t>
+        </is>
+      </c>
+      <c r="B219" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F219" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G219" s="6" t="n"/>
       <c r="H219" s="6" t="n"/>
@@ -4269,11 +4265,11 @@
       <c r="A220" s="7" t="n"/>
       <c r="B220" s="8" t="inlineStr">
         <is>
-          <t>SAMBA GOLF ( KJ5431 )</t>
+          <t>GHOST SPRINT W ( HQ3330 )</t>
         </is>
       </c>
       <c r="F220" s="9" t="n">
-        <v>16</v>
+        <v>2725</v>
       </c>
       <c r="G220" s="6" t="n"/>
       <c r="H220" s="6" t="n"/>
@@ -4286,11 +4282,11 @@
       <c r="A221" s="7" t="n"/>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t>SAMBA GOLF ( KJ8225 )</t>
+          <t>GHOST SPRINT W ( HQ7638 )</t>
         </is>
       </c>
       <c r="F221" s="9" t="n">
-        <v>1841</v>
+        <v>529</v>
       </c>
       <c r="G221" s="6" t="n"/>
       <c r="H221" s="6" t="n"/>
@@ -4303,11 +4299,11 @@
       <c r="A222" s="7" t="n"/>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
+          <t>GHOST SPRINT W ( JS1067 )</t>
         </is>
       </c>
       <c r="F222" s="9" t="n">
-        <v>4279</v>
+        <v>1633</v>
       </c>
       <c r="G222" s="6" t="n"/>
       <c r="H222" s="6" t="n"/>
@@ -4316,28 +4312,32 @@
       <c r="K222" s="6" t="n"/>
       <c r="L222" s="6" t="n"/>
     </row>
-    <row r="223">
-      <c r="A223" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 7 （加7部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="224" ht="18" customHeight="1">
-      <c r="A224" s="5" t="inlineStr">
-        <is>
-          <t>7A</t>
-        </is>
-      </c>
-      <c r="B224" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F224" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="223" ht="15" customHeight="1">
+      <c r="A223" s="7" t="n"/>
+      <c r="B223" s="8" t="inlineStr">
+        <is>
+          <t>GHOST SPRINT W ( KI4563 )</t>
+        </is>
+      </c>
+      <c r="F223" s="9" t="n">
+        <v>505</v>
+      </c>
+      <c r="G223" s="6" t="n"/>
+      <c r="H223" s="6" t="n"/>
+      <c r="I223" s="6" t="n"/>
+      <c r="J223" s="6" t="n"/>
+      <c r="K223" s="6" t="n"/>
+      <c r="L223" s="6" t="n"/>
+    </row>
+    <row r="224" ht="15" customHeight="1">
+      <c r="A224" s="7" t="n"/>
+      <c r="B224" s="8" t="inlineStr">
+        <is>
+          <t>GHOST SPRINT W ( KI4569 )</t>
+        </is>
+      </c>
+      <c r="F224" s="9" t="n">
+        <v>410</v>
       </c>
       <c r="G224" s="6" t="n"/>
       <c r="H224" s="6" t="n"/>
@@ -4350,11 +4350,11 @@
       <c r="A225" s="7" t="n"/>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( HQ3330 )</t>
+          <t>GHOST SPRINT W ( KJ0644 )</t>
         </is>
       </c>
       <c r="F225" s="9" t="n">
-        <v>8451</v>
+        <v>378</v>
       </c>
       <c r="G225" s="6" t="n"/>
       <c r="H225" s="6" t="n"/>
@@ -4367,11 +4367,11 @@
       <c r="A226" s="7" t="n"/>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( HQ7638 )</t>
+          <t>GHOST SPRINT W ( KJ0646 )</t>
         </is>
       </c>
       <c r="F226" s="9" t="n">
-        <v>529</v>
+        <v>1580</v>
       </c>
       <c r="G226" s="6" t="n"/>
       <c r="H226" s="6" t="n"/>
@@ -4384,11 +4384,11 @@
       <c r="A227" s="7" t="n"/>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( JS1067 )</t>
+          <t>GHOST SPRINT W ( LA7682 )</t>
         </is>
       </c>
       <c r="F227" s="9" t="n">
-        <v>3229</v>
+        <v>3424</v>
       </c>
       <c r="G227" s="6" t="n"/>
       <c r="H227" s="6" t="n"/>
@@ -4401,11 +4401,11 @@
       <c r="A228" s="7" t="n"/>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KI4563 )</t>
+          <t>GHOST SPRINT W ( LA7683 )</t>
         </is>
       </c>
       <c r="F228" s="9" t="n">
-        <v>882</v>
+        <v>8233</v>
       </c>
       <c r="G228" s="6" t="n"/>
       <c r="H228" s="6" t="n"/>
@@ -4414,15 +4414,21 @@
       <c r="K228" s="6" t="n"/>
       <c r="L228" s="6" t="n"/>
     </row>
-    <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="7" t="n"/>
-      <c r="B229" s="8" t="inlineStr">
-        <is>
-          <t>GHOST SPRINT W ( KI4569 )</t>
-        </is>
-      </c>
-      <c r="F229" s="9" t="n">
-        <v>410</v>
+    <row r="229" ht="18" customHeight="1">
+      <c r="A229" s="5" t="inlineStr">
+        <is>
+          <t>7B</t>
+        </is>
+      </c>
+      <c r="B229" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F229" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G229" s="6" t="n"/>
       <c r="H229" s="6" t="n"/>
@@ -4435,11 +4441,11 @@
       <c r="A230" s="7" t="n"/>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI7740 )</t>
+          <t>TOKYO W NATI ( HP5175 )</t>
         </is>
       </c>
       <c r="F230" s="9" t="n">
-        <v>1919</v>
+        <v>2859</v>
       </c>
       <c r="G230" s="6" t="n"/>
       <c r="H230" s="6" t="n"/>
@@ -4452,11 +4458,11 @@
       <c r="A231" s="7" t="n"/>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KJ0644 )</t>
+          <t>TOKYO W ( HQ2887 )</t>
         </is>
       </c>
       <c r="F231" s="9" t="n">
-        <v>378</v>
+        <v>300</v>
       </c>
       <c r="G231" s="6" t="n"/>
       <c r="H231" s="6" t="n"/>
@@ -4469,11 +4475,11 @@
       <c r="A232" s="7" t="n"/>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( KJ0646 )</t>
+          <t>TOKYO W ( HQ9512 )</t>
         </is>
       </c>
       <c r="F232" s="9" t="n">
-        <v>1580</v>
+        <v>598</v>
       </c>
       <c r="G232" s="6" t="n"/>
       <c r="H232" s="6" t="n"/>
@@ -4486,11 +4492,11 @@
       <c r="A233" s="7" t="n"/>
       <c r="B233" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( LA7682 )</t>
+          <t>TOKYO MJ W ( IH3999 )</t>
         </is>
       </c>
       <c r="F233" s="9" t="n">
-        <v>6683</v>
+        <v>525</v>
       </c>
       <c r="G233" s="6" t="n"/>
       <c r="H233" s="6" t="n"/>
@@ -4503,11 +4509,11 @@
       <c r="A234" s="7" t="n"/>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT W ( LA7683 )</t>
+          <t>TOKYO W ( JQ0597 )</t>
         </is>
       </c>
       <c r="F234" s="9" t="n">
-        <v>11880</v>
+        <v>5268</v>
       </c>
       <c r="G234" s="6" t="n"/>
       <c r="H234" s="6" t="n"/>
@@ -4516,21 +4522,15 @@
       <c r="K234" s="6" t="n"/>
       <c r="L234" s="6" t="n"/>
     </row>
-    <row r="235" ht="18" customHeight="1">
-      <c r="A235" s="5" t="inlineStr">
-        <is>
-          <t>7B</t>
-        </is>
-      </c>
-      <c r="B235" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F235" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="235" ht="15" customHeight="1">
+      <c r="A235" s="7" t="n"/>
+      <c r="B235" s="8" t="inlineStr">
+        <is>
+          <t>TOKYO W ( KI3584 )</t>
+        </is>
+      </c>
+      <c r="F235" s="9" t="n">
+        <v>683</v>
       </c>
       <c r="G235" s="6" t="n"/>
       <c r="H235" s="6" t="n"/>
@@ -4543,11 +4543,11 @@
       <c r="A236" s="7" t="n"/>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W NATI ( HP5175 )</t>
+          <t>TOKYO MJ W ( KJ5221 )</t>
         </is>
       </c>
       <c r="F236" s="9" t="n">
-        <v>5718</v>
+        <v>1257</v>
       </c>
       <c r="G236" s="6" t="n"/>
       <c r="H236" s="6" t="n"/>
@@ -4560,11 +4560,11 @@
       <c r="A237" s="7" t="n"/>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( HQ2887 )</t>
+          <t>TOKYO W ( KJ7499 )</t>
         </is>
       </c>
       <c r="F237" s="9" t="n">
-        <v>6049</v>
+        <v>331</v>
       </c>
       <c r="G237" s="6" t="n"/>
       <c r="H237" s="6" t="n"/>
@@ -4577,11 +4577,11 @@
       <c r="A238" s="7" t="n"/>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( HQ9512 )</t>
+          <t>TOKYO W ( KJ7539 )</t>
         </is>
       </c>
       <c r="F238" s="9" t="n">
-        <v>1196</v>
+        <v>2730</v>
       </c>
       <c r="G238" s="6" t="n"/>
       <c r="H238" s="6" t="n"/>
@@ -4594,11 +4594,11 @@
       <c r="A239" s="7" t="n"/>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( IH3999 )</t>
+          <t>TOKYO W ( KJ7543 )</t>
         </is>
       </c>
       <c r="F239" s="9" t="n">
-        <v>1050</v>
+        <v>3211</v>
       </c>
       <c r="G239" s="6" t="n"/>
       <c r="H239" s="6" t="n"/>
@@ -4611,11 +4611,11 @@
       <c r="A240" s="7" t="n"/>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( JQ0597 )</t>
+          <t>TOKYO W ( KJ7544 )</t>
         </is>
       </c>
       <c r="F240" s="9" t="n">
-        <v>10536</v>
+        <v>673</v>
       </c>
       <c r="G240" s="6" t="n"/>
       <c r="H240" s="6" t="n"/>
@@ -4628,11 +4628,11 @@
       <c r="A241" s="7" t="n"/>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KI3584 )</t>
+          <t>TOKYO MJ W ( KJ8377 )</t>
         </is>
       </c>
       <c r="F241" s="9" t="n">
-        <v>2131</v>
+        <v>1110</v>
       </c>
       <c r="G241" s="6" t="n"/>
       <c r="H241" s="6" t="n"/>
@@ -4645,11 +4645,11 @@
       <c r="A242" s="7" t="n"/>
       <c r="B242" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( KJ5221 )</t>
+          <t>TOKYO MJ W ( KJ8378 )</t>
         </is>
       </c>
       <c r="F242" s="9" t="n">
-        <v>2514</v>
+        <v>308</v>
       </c>
       <c r="G242" s="6" t="n"/>
       <c r="H242" s="6" t="n"/>
@@ -4662,11 +4662,11 @@
       <c r="A243" s="7" t="n"/>
       <c r="B243" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7499 )</t>
+          <t>TOKYO W ( KK0030 )</t>
         </is>
       </c>
       <c r="F243" s="9" t="n">
-        <v>662</v>
+        <v>760</v>
       </c>
       <c r="G243" s="6" t="n"/>
       <c r="H243" s="6" t="n"/>
@@ -4679,11 +4679,11 @@
       <c r="A244" s="7" t="n"/>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7539 )</t>
+          <t>TOKYO W ( KK0031 )</t>
         </is>
       </c>
       <c r="F244" s="9" t="n">
-        <v>5460</v>
+        <v>1753</v>
       </c>
       <c r="G244" s="6" t="n"/>
       <c r="H244" s="6" t="n"/>
@@ -4696,11 +4696,11 @@
       <c r="A245" s="7" t="n"/>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7541 )</t>
+          <t>TOKYO W ( KK2621 )</t>
         </is>
       </c>
       <c r="F245" s="9" t="n">
-        <v>2812</v>
+        <v>2358</v>
       </c>
       <c r="G245" s="6" t="n"/>
       <c r="H245" s="6" t="n"/>
@@ -4709,32 +4709,28 @@
       <c r="K245" s="6" t="n"/>
       <c r="L245" s="6" t="n"/>
     </row>
-    <row r="246" ht="15" customHeight="1">
-      <c r="A246" s="7" t="n"/>
-      <c r="B246" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( KJ7542 )</t>
-        </is>
-      </c>
-      <c r="F246" s="9" t="n">
-        <v>660</v>
-      </c>
-      <c r="G246" s="6" t="n"/>
-      <c r="H246" s="6" t="n"/>
-      <c r="I246" s="6" t="n"/>
-      <c r="J246" s="6" t="n"/>
-      <c r="K246" s="6" t="n"/>
-      <c r="L246" s="6" t="n"/>
-    </row>
-    <row r="247" ht="15" customHeight="1">
-      <c r="A247" s="7" t="n"/>
-      <c r="B247" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( KJ7543 )</t>
-        </is>
-      </c>
-      <c r="F247" s="9" t="n">
-        <v>8804</v>
+    <row r="246">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 8 （加8部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="18" customHeight="1">
+      <c r="A247" s="5" t="inlineStr">
+        <is>
+          <t>8A</t>
+        </is>
+      </c>
+      <c r="B247" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F247" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G247" s="6" t="n"/>
       <c r="H247" s="6" t="n"/>
@@ -4747,11 +4743,11 @@
       <c r="A248" s="7" t="n"/>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7544 )</t>
+          <t>SAMBA ( IH6001 )</t>
         </is>
       </c>
       <c r="F248" s="9" t="n">
-        <v>2622</v>
+        <v>5000</v>
       </c>
       <c r="G248" s="6" t="n"/>
       <c r="H248" s="6" t="n"/>
@@ -4764,11 +4760,11 @@
       <c r="A249" s="7" t="n"/>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7551 )</t>
+          <t>ADISTAR XLG 2.0 J ( KH7374 )</t>
         </is>
       </c>
       <c r="F249" s="9" t="n">
-        <v>4172</v>
+        <v>5464</v>
       </c>
       <c r="G249" s="6" t="n"/>
       <c r="H249" s="6" t="n"/>
@@ -4781,11 +4777,11 @@
       <c r="A250" s="7" t="n"/>
       <c r="B250" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7552 )</t>
+          <t>BUSENITZ ( KI7713 )</t>
         </is>
       </c>
       <c r="F250" s="9" t="n">
-        <v>1250</v>
+        <v>264</v>
       </c>
       <c r="G250" s="6" t="n"/>
       <c r="H250" s="6" t="n"/>
@@ -4798,11 +4794,11 @@
       <c r="A251" s="7" t="n"/>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( KJ8377 )</t>
+          <t>BUSENITZ VINTAGE ( KI7714 )</t>
         </is>
       </c>
       <c r="F251" s="9" t="n">
-        <v>1110</v>
+        <v>668</v>
       </c>
       <c r="G251" s="6" t="n"/>
       <c r="H251" s="6" t="n"/>
@@ -4815,11 +4811,11 @@
       <c r="A252" s="7" t="n"/>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( KJ8378 )</t>
+          <t>BUSENITZ VINTAGE ( KI7725 )</t>
         </is>
       </c>
       <c r="F252" s="9" t="n">
-        <v>616</v>
+        <v>636</v>
       </c>
       <c r="G252" s="6" t="n"/>
       <c r="H252" s="6" t="n"/>
@@ -4832,11 +4828,11 @@
       <c r="A253" s="7" t="n"/>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0030 )</t>
+          <t>BUSENITZ ( KJ0259 )</t>
         </is>
       </c>
       <c r="F253" s="9" t="n">
-        <v>1520</v>
+        <v>203</v>
       </c>
       <c r="G253" s="6" t="n"/>
       <c r="H253" s="6" t="n"/>
@@ -4849,11 +4845,11 @@
       <c r="A254" s="7" t="n"/>
       <c r="B254" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0031 )</t>
+          <t>BUSENITZ ( KJ0260 )</t>
         </is>
       </c>
       <c r="F254" s="9" t="n">
-        <v>3506</v>
+        <v>865</v>
       </c>
       <c r="G254" s="6" t="n"/>
       <c r="H254" s="6" t="n"/>
@@ -4866,11 +4862,11 @@
       <c r="A255" s="7" t="n"/>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK2621 )</t>
+          <t>BUSENITZ ( KJ0261 )</t>
         </is>
       </c>
       <c r="F255" s="9" t="n">
-        <v>7554</v>
+        <v>694</v>
       </c>
       <c r="G255" s="6" t="n"/>
       <c r="H255" s="6" t="n"/>
@@ -4879,28 +4875,32 @@
       <c r="K255" s="6" t="n"/>
       <c r="L255" s="6" t="n"/>
     </row>
-    <row r="256">
-      <c r="A256" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 8 （加8部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="257" ht="18" customHeight="1">
-      <c r="A257" s="5" t="inlineStr">
-        <is>
-          <t>8A</t>
-        </is>
-      </c>
-      <c r="B257" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F257" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="256" ht="15" customHeight="1">
+      <c r="A256" s="7" t="n"/>
+      <c r="B256" s="8" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
+        </is>
+      </c>
+      <c r="F256" s="9" t="n">
+        <v>10951</v>
+      </c>
+      <c r="G256" s="6" t="n"/>
+      <c r="H256" s="6" t="n"/>
+      <c r="I256" s="6" t="n"/>
+      <c r="J256" s="6" t="n"/>
+      <c r="K256" s="6" t="n"/>
+      <c r="L256" s="6" t="n"/>
+    </row>
+    <row r="257" ht="15" customHeight="1">
+      <c r="A257" s="7" t="n"/>
+      <c r="B257" s="8" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J ( KJ7893 )</t>
+        </is>
+      </c>
+      <c r="F257" s="9" t="n">
+        <v>675</v>
       </c>
       <c r="G257" s="6" t="n"/>
       <c r="H257" s="6" t="n"/>
@@ -4913,11 +4913,11 @@
       <c r="A258" s="7" t="n"/>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t>SAMBA ( IH6001 )</t>
+          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
         </is>
       </c>
       <c r="F258" s="9" t="n">
-        <v>5000</v>
+        <v>200</v>
       </c>
       <c r="G258" s="6" t="n"/>
       <c r="H258" s="6" t="n"/>
@@ -4930,11 +4930,11 @@
       <c r="A259" s="7" t="n"/>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KH7374 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F259" s="9" t="n">
-        <v>5464</v>
+        <v>2436</v>
       </c>
       <c r="G259" s="6" t="n"/>
       <c r="H259" s="6" t="n"/>
@@ -4943,15 +4943,21 @@
       <c r="K259" s="6" t="n"/>
       <c r="L259" s="6" t="n"/>
     </row>
-    <row r="260" ht="15" customHeight="1">
-      <c r="A260" s="7" t="n"/>
-      <c r="B260" s="8" t="inlineStr">
-        <is>
-          <t>BUSENITZ ( KI7713 )</t>
-        </is>
-      </c>
-      <c r="F260" s="9" t="n">
-        <v>264</v>
+    <row r="260" ht="18" customHeight="1">
+      <c r="A260" s="5" t="inlineStr">
+        <is>
+          <t>8B</t>
+        </is>
+      </c>
+      <c r="B260" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F260" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G260" s="6" t="n"/>
       <c r="H260" s="6" t="n"/>
@@ -4964,11 +4970,11 @@
       <c r="A261" s="7" t="n"/>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t>BUSENITZ VINTAGE ( KI7714 )</t>
+          <t>BB F50 GHOST SPRINT ( HP4218 )</t>
         </is>
       </c>
       <c r="F261" s="9" t="n">
-        <v>668</v>
+        <v>7247</v>
       </c>
       <c r="G261" s="6" t="n"/>
       <c r="H261" s="6" t="n"/>
@@ -4981,11 +4987,11 @@
       <c r="A262" s="7" t="n"/>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t>BUSENITZ VINTAGE ( KI7725 )</t>
+          <t>GHOST SPRINT BALLET W ( HQ7636 )</t>
         </is>
       </c>
       <c r="F262" s="9" t="n">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G262" s="6" t="n"/>
       <c r="H262" s="6" t="n"/>
@@ -4998,11 +5004,11 @@
       <c r="A263" s="7" t="n"/>
       <c r="B263" s="8" t="inlineStr">
         <is>
-          <t>BUSENITZ ( KJ0259 )</t>
+          <t>GHOST SPRINT BALLET W ( HQ7637 )</t>
         </is>
       </c>
       <c r="F263" s="9" t="n">
-        <v>203</v>
+        <v>365</v>
       </c>
       <c r="G263" s="6" t="n"/>
       <c r="H263" s="6" t="n"/>
@@ -5015,11 +5021,11 @@
       <c r="A264" s="7" t="n"/>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t>BUSENITZ ( KJ0260 )</t>
+          <t>adidas F50 ADIFRAME ( KH6569 )</t>
         </is>
       </c>
       <c r="F264" s="9" t="n">
-        <v>865</v>
+        <v>402</v>
       </c>
       <c r="G264" s="6" t="n"/>
       <c r="H264" s="6" t="n"/>
@@ -5032,11 +5038,11 @@
       <c r="A265" s="7" t="n"/>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t>BUSENITZ ( KJ0261 )</t>
+          <t>adidas F50 ADIFRAME ( KH6570 )</t>
         </is>
       </c>
       <c r="F265" s="9" t="n">
-        <v>694</v>
+        <v>402</v>
       </c>
       <c r="G265" s="6" t="n"/>
       <c r="H265" s="6" t="n"/>
@@ -5049,11 +5055,11 @@
       <c r="A266" s="7" t="n"/>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
+          <t>GHOST SPRINT BALLET W ( KI0435 )</t>
         </is>
       </c>
       <c r="F266" s="9" t="n">
-        <v>10951</v>
+        <v>2882</v>
       </c>
       <c r="G266" s="6" t="n"/>
       <c r="H266" s="6" t="n"/>
@@ -5066,11 +5072,11 @@
       <c r="A267" s="7" t="n"/>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7893 )</t>
+          <t>GHOST SPRINT BALLET W ( KI0436 )</t>
         </is>
       </c>
       <c r="F267" s="9" t="n">
-        <v>675</v>
+        <v>4981</v>
       </c>
       <c r="G267" s="6" t="n"/>
       <c r="H267" s="6" t="n"/>
@@ -5083,11 +5089,11 @@
       <c r="A268" s="7" t="n"/>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
+          <t>GHOST SPRINT BALLET W ( KI7738 )</t>
         </is>
       </c>
       <c r="F268" s="9" t="n">
-        <v>200</v>
+        <v>1198</v>
       </c>
       <c r="G268" s="6" t="n"/>
       <c r="H268" s="6" t="n"/>
@@ -5100,11 +5106,11 @@
       <c r="A269" s="7" t="n"/>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
+          <t>GHOST SPRINT BALLET W ( KI7739 )</t>
         </is>
       </c>
       <c r="F269" s="9" t="n">
-        <v>2436</v>
+        <v>853</v>
       </c>
       <c r="G269" s="6" t="n"/>
       <c r="H269" s="6" t="n"/>
@@ -5113,21 +5119,15 @@
       <c r="K269" s="6" t="n"/>
       <c r="L269" s="6" t="n"/>
     </row>
-    <row r="270" ht="18" customHeight="1">
-      <c r="A270" s="5" t="inlineStr">
-        <is>
-          <t>8B</t>
-        </is>
-      </c>
-      <c r="B270" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F270" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="270" ht="15" customHeight="1">
+      <c r="A270" s="7" t="n"/>
+      <c r="B270" s="8" t="inlineStr">
+        <is>
+          <t>GHOST SPRINT BALLET W ( KI7740 )</t>
+        </is>
+      </c>
+      <c r="F270" s="9" t="n">
+        <v>2944</v>
       </c>
       <c r="G270" s="6" t="n"/>
       <c r="H270" s="6" t="n"/>
@@ -5140,11 +5140,11 @@
       <c r="A271" s="7" t="n"/>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t>BB F50 GHOST SPRINT ( HP4218 )</t>
+          <t>adidas F50 ADIFRAME W ( KK0908 )</t>
         </is>
       </c>
       <c r="F271" s="9" t="n">
-        <v>7247</v>
+        <v>345</v>
       </c>
       <c r="G271" s="6" t="n"/>
       <c r="H271" s="6" t="n"/>
@@ -5157,11 +5157,11 @@
       <c r="A272" s="7" t="n"/>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( HQ7636 )</t>
+          <t>adidas F50 ADIFRAME W ( KK0909 )</t>
         </is>
       </c>
       <c r="F272" s="9" t="n">
-        <v>637</v>
+        <v>310</v>
       </c>
       <c r="G272" s="6" t="n"/>
       <c r="H272" s="6" t="n"/>
@@ -5174,11 +5174,11 @@
       <c r="A273" s="7" t="n"/>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( HQ7637 )</t>
+          <t>GHOST SPRINT BALLET W ( KZ7290 )</t>
         </is>
       </c>
       <c r="F273" s="9" t="n">
-        <v>365</v>
+        <v>930</v>
       </c>
       <c r="G273" s="6" t="n"/>
       <c r="H273" s="6" t="n"/>
@@ -5191,11 +5191,11 @@
       <c r="A274" s="7" t="n"/>
       <c r="B274" s="8" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME ( KH6569 )</t>
+          <t>GHOST SPRINT BALLET W ( KZ7291 )</t>
         </is>
       </c>
       <c r="F274" s="9" t="n">
-        <v>402</v>
+        <v>1230</v>
       </c>
       <c r="G274" s="6" t="n"/>
       <c r="H274" s="6" t="n"/>
@@ -5204,15 +5204,21 @@
       <c r="K274" s="6" t="n"/>
       <c r="L274" s="6" t="n"/>
     </row>
-    <row r="275" ht="15" customHeight="1">
-      <c r="A275" s="7" t="n"/>
-      <c r="B275" s="8" t="inlineStr">
-        <is>
-          <t>adidas F50 ADIFRAME ( KH6570 )</t>
-        </is>
-      </c>
-      <c r="F275" s="9" t="n">
-        <v>402</v>
+    <row r="275" ht="18" customHeight="1">
+      <c r="A275" s="5" t="inlineStr">
+        <is>
+          <t>8C</t>
+        </is>
+      </c>
+      <c r="B275" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F275" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G275" s="6" t="n"/>
       <c r="H275" s="6" t="n"/>
@@ -5225,11 +5231,11 @@
       <c r="A276" s="7" t="n"/>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI0435 )</t>
+          <t>TOKYO W ( IH3991 )</t>
         </is>
       </c>
       <c r="F276" s="9" t="n">
-        <v>2882</v>
+        <v>442</v>
       </c>
       <c r="G276" s="6" t="n"/>
       <c r="H276" s="6" t="n"/>
@@ -5242,11 +5248,11 @@
       <c r="A277" s="7" t="n"/>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI0436 )</t>
+          <t>TOKYO W ( IH3994 )</t>
         </is>
       </c>
       <c r="F277" s="9" t="n">
-        <v>4981</v>
+        <v>1829</v>
       </c>
       <c r="G277" s="6" t="n"/>
       <c r="H277" s="6" t="n"/>
@@ -5259,11 +5265,11 @@
       <c r="A278" s="7" t="n"/>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI7738 )</t>
+          <t>TOKYO MJ W ( IH3999 )</t>
         </is>
       </c>
       <c r="F278" s="9" t="n">
-        <v>1198</v>
+        <v>2874</v>
       </c>
       <c r="G278" s="6" t="n"/>
       <c r="H278" s="6" t="n"/>
@@ -5276,11 +5282,11 @@
       <c r="A279" s="7" t="n"/>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI7739 )</t>
+          <t>TOKYO MJ W ( JR4790 )</t>
         </is>
       </c>
       <c r="F279" s="9" t="n">
-        <v>853</v>
+        <v>4793</v>
       </c>
       <c r="G279" s="6" t="n"/>
       <c r="H279" s="6" t="n"/>
@@ -5293,11 +5299,11 @@
       <c r="A280" s="7" t="n"/>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KI7740 )</t>
+          <t>TOKYO W ( KI3584 )</t>
         </is>
       </c>
       <c r="F280" s="9" t="n">
-        <v>2944</v>
+        <v>2100</v>
       </c>
       <c r="G280" s="6" t="n"/>
       <c r="H280" s="6" t="n"/>
@@ -5310,11 +5316,11 @@
       <c r="A281" s="7" t="n"/>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME W ( KK0908 )</t>
+          <t>TOKYO W ( KJ7510 )</t>
         </is>
       </c>
       <c r="F281" s="9" t="n">
-        <v>345</v>
+        <v>4200</v>
       </c>
       <c r="G281" s="6" t="n"/>
       <c r="H281" s="6" t="n"/>
@@ -5327,11 +5333,11 @@
       <c r="A282" s="7" t="n"/>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t>adidas F50 ADIFRAME W ( KK0909 )</t>
+          <t>TOKYO W ( KJ7542 )</t>
         </is>
       </c>
       <c r="F282" s="9" t="n">
-        <v>310</v>
+        <v>480</v>
       </c>
       <c r="G282" s="6" t="n"/>
       <c r="H282" s="6" t="n"/>
@@ -5344,11 +5350,11 @@
       <c r="A283" s="7" t="n"/>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KZ7290 )</t>
+          <t>TOKYO MJ W ( KJ8377 )</t>
         </is>
       </c>
       <c r="F283" s="9" t="n">
-        <v>930</v>
+        <v>1366</v>
       </c>
       <c r="G283" s="6" t="n"/>
       <c r="H283" s="6" t="n"/>
@@ -5361,11 +5367,11 @@
       <c r="A284" s="7" t="n"/>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t>GHOST SPRINT BALLET W ( KZ7291 )</t>
+          <t>TOKYO MJ W ( KJ8378 )</t>
         </is>
       </c>
       <c r="F284" s="9" t="n">
-        <v>1230</v>
+        <v>600</v>
       </c>
       <c r="G284" s="6" t="n"/>
       <c r="H284" s="6" t="n"/>
@@ -5374,21 +5380,15 @@
       <c r="K284" s="6" t="n"/>
       <c r="L284" s="6" t="n"/>
     </row>
-    <row r="285" ht="18" customHeight="1">
-      <c r="A285" s="5" t="inlineStr">
-        <is>
-          <t>8C</t>
-        </is>
-      </c>
-      <c r="B285" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F285" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="285" ht="15" customHeight="1">
+      <c r="A285" s="7" t="n"/>
+      <c r="B285" s="8" t="inlineStr">
+        <is>
+          <t>HANDBALL SPEZIAL ( LA3255 )</t>
+        </is>
+      </c>
+      <c r="F285" s="9" t="n">
+        <v>1598</v>
       </c>
       <c r="G285" s="6" t="n"/>
       <c r="H285" s="6" t="n"/>
@@ -5397,32 +5397,28 @@
       <c r="K285" s="6" t="n"/>
       <c r="L285" s="6" t="n"/>
     </row>
-    <row r="286" ht="15" customHeight="1">
-      <c r="A286" s="7" t="n"/>
-      <c r="B286" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( IH3991 )</t>
-        </is>
-      </c>
-      <c r="F286" s="9" t="n">
-        <v>442</v>
-      </c>
-      <c r="G286" s="6" t="n"/>
-      <c r="H286" s="6" t="n"/>
-      <c r="I286" s="6" t="n"/>
-      <c r="J286" s="6" t="n"/>
-      <c r="K286" s="6" t="n"/>
-      <c r="L286" s="6" t="n"/>
-    </row>
-    <row r="287" ht="15" customHeight="1">
-      <c r="A287" s="7" t="n"/>
-      <c r="B287" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( IH3994 )</t>
-        </is>
-      </c>
-      <c r="F287" s="9" t="n">
-        <v>1829</v>
+    <row r="286">
+      <c r="A286" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 9 （加9部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="18" customHeight="1">
+      <c r="A287" s="5" t="inlineStr">
+        <is>
+          <t>9A</t>
+        </is>
+      </c>
+      <c r="B287" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F287" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G287" s="6" t="n"/>
       <c r="H287" s="6" t="n"/>
@@ -5435,11 +5431,11 @@
       <c r="A288" s="7" t="n"/>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( IH3999 )</t>
+          <t>OZGAIA W ( IG6045 )</t>
         </is>
       </c>
       <c r="F288" s="9" t="n">
-        <v>4064</v>
+        <v>28903</v>
       </c>
       <c r="G288" s="6" t="n"/>
       <c r="H288" s="6" t="n"/>
@@ -5452,11 +5448,11 @@
       <c r="A289" s="7" t="n"/>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( JR4790 )</t>
+          <t>OZGAIA W ( IG6047 )</t>
         </is>
       </c>
       <c r="F289" s="9" t="n">
-        <v>4793</v>
+        <v>916</v>
       </c>
       <c r="G289" s="6" t="n"/>
       <c r="H289" s="6" t="n"/>
@@ -5469,11 +5465,11 @@
       <c r="A290" s="7" t="n"/>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KI3584 )</t>
+          <t>OZGAIA W ( IG6049 )</t>
         </is>
       </c>
       <c r="F290" s="9" t="n">
-        <v>2100</v>
+        <v>5950</v>
       </c>
       <c r="G290" s="6" t="n"/>
       <c r="H290" s="6" t="n"/>
@@ -5486,11 +5482,11 @@
       <c r="A291" s="7" t="n"/>
       <c r="B291" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7510 )</t>
+          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
         </is>
       </c>
       <c r="F291" s="9" t="n">
-        <v>4200</v>
+        <v>4146</v>
       </c>
       <c r="G291" s="6" t="n"/>
       <c r="H291" s="6" t="n"/>
@@ -5503,11 +5499,11 @@
       <c r="A292" s="7" t="n"/>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7542 )</t>
+          <t>OZGAIA W ( KZ7071 )</t>
         </is>
       </c>
       <c r="F292" s="9" t="n">
-        <v>480</v>
+        <v>6969</v>
       </c>
       <c r="G292" s="6" t="n"/>
       <c r="H292" s="6" t="n"/>
@@ -5520,11 +5516,11 @@
       <c r="A293" s="7" t="n"/>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7552 )</t>
+          <t>OZGAIA W ( KZ7072 )</t>
         </is>
       </c>
       <c r="F293" s="9" t="n">
-        <v>775</v>
+        <v>5468</v>
       </c>
       <c r="G293" s="6" t="n"/>
       <c r="H293" s="6" t="n"/>
@@ -5533,15 +5529,21 @@
       <c r="K293" s="6" t="n"/>
       <c r="L293" s="6" t="n"/>
     </row>
-    <row r="294" ht="15" customHeight="1">
-      <c r="A294" s="7" t="n"/>
-      <c r="B294" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO MJ W ( KJ8377 )</t>
-        </is>
-      </c>
-      <c r="F294" s="9" t="n">
-        <v>1682</v>
+    <row r="294" ht="18" customHeight="1">
+      <c r="A294" s="5" t="inlineStr">
+        <is>
+          <t>9B</t>
+        </is>
+      </c>
+      <c r="B294" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F294" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G294" s="6" t="n"/>
       <c r="H294" s="6" t="n"/>
@@ -5554,11 +5556,11 @@
       <c r="A295" s="7" t="n"/>
       <c r="B295" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( KJ8378 )</t>
+          <t>TOKYO W ( IH3994 )</t>
         </is>
       </c>
       <c r="F295" s="9" t="n">
-        <v>600</v>
+        <v>1177</v>
       </c>
       <c r="G295" s="6" t="n"/>
       <c r="H295" s="6" t="n"/>
@@ -5571,11 +5573,11 @@
       <c r="A296" s="7" t="n"/>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( LA3255 )</t>
+          <t>TOKYO W ( JI0182 )</t>
         </is>
       </c>
       <c r="F296" s="9" t="n">
-        <v>1598</v>
+        <v>322</v>
       </c>
       <c r="G296" s="6" t="n"/>
       <c r="H296" s="6" t="n"/>
@@ -5584,28 +5586,32 @@
       <c r="K296" s="6" t="n"/>
       <c r="L296" s="6" t="n"/>
     </row>
-    <row r="297">
-      <c r="A297" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 9 （加9部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="298" ht="18" customHeight="1">
-      <c r="A298" s="5" t="inlineStr">
-        <is>
-          <t>9A</t>
-        </is>
-      </c>
-      <c r="B298" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F298" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="297" ht="15" customHeight="1">
+      <c r="A297" s="7" t="n"/>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t>SL 72 RS ( KH9653 )</t>
+        </is>
+      </c>
+      <c r="F297" s="9" t="n">
+        <v>1120</v>
+      </c>
+      <c r="G297" s="6" t="n"/>
+      <c r="H297" s="6" t="n"/>
+      <c r="I297" s="6" t="n"/>
+      <c r="J297" s="6" t="n"/>
+      <c r="K297" s="6" t="n"/>
+      <c r="L297" s="6" t="n"/>
+    </row>
+    <row r="298" ht="15" customHeight="1">
+      <c r="A298" s="7" t="n"/>
+      <c r="B298" s="8" t="inlineStr">
+        <is>
+          <t>SL 72 RS ( KJ1674 )</t>
+        </is>
+      </c>
+      <c r="F298" s="9" t="n">
+        <v>2103</v>
       </c>
       <c r="G298" s="6" t="n"/>
       <c r="H298" s="6" t="n"/>
@@ -5618,11 +5624,11 @@
       <c r="A299" s="7" t="n"/>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6045 )</t>
+          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
         </is>
       </c>
       <c r="F299" s="9" t="n">
-        <v>28903</v>
+        <v>11247</v>
       </c>
       <c r="G299" s="6" t="n"/>
       <c r="H299" s="6" t="n"/>
@@ -5635,11 +5641,11 @@
       <c r="A300" s="7" t="n"/>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6047 )</t>
+          <t>ADISTAR XLG 2.0 J ( KZ6449 )</t>
         </is>
       </c>
       <c r="F300" s="9" t="n">
-        <v>916</v>
+        <v>7616</v>
       </c>
       <c r="G300" s="6" t="n"/>
       <c r="H300" s="6" t="n"/>
@@ -5652,11 +5658,11 @@
       <c r="A301" s="7" t="n"/>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6049 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ8301 )</t>
         </is>
       </c>
       <c r="F301" s="9" t="n">
-        <v>5950</v>
+        <v>6025</v>
       </c>
       <c r="G301" s="6" t="n"/>
       <c r="H301" s="6" t="n"/>
@@ -5669,11 +5675,11 @@
       <c r="A302" s="7" t="n"/>
       <c r="B302" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F302" s="9" t="n">
-        <v>4146</v>
+        <v>1154</v>
       </c>
       <c r="G302" s="6" t="n"/>
       <c r="H302" s="6" t="n"/>
@@ -5682,15 +5688,21 @@
       <c r="K302" s="6" t="n"/>
       <c r="L302" s="6" t="n"/>
     </row>
-    <row r="303" ht="15" customHeight="1">
-      <c r="A303" s="7" t="n"/>
-      <c r="B303" s="8" t="inlineStr">
-        <is>
-          <t>OZGAIA W ( KZ7071 )</t>
-        </is>
-      </c>
-      <c r="F303" s="9" t="n">
-        <v>6969</v>
+    <row r="303" ht="18" customHeight="1">
+      <c r="A303" s="5" t="inlineStr">
+        <is>
+          <t>9C</t>
+        </is>
+      </c>
+      <c r="B303" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F303" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G303" s="6" t="n"/>
       <c r="H303" s="6" t="n"/>
@@ -5703,11 +5715,11 @@
       <c r="A304" s="7" t="n"/>
       <c r="B304" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( KZ7072 )</t>
+          <t>( HP5123 )</t>
         </is>
       </c>
       <c r="F304" s="9" t="n">
-        <v>5468</v>
+        <v>2000</v>
       </c>
       <c r="G304" s="6" t="n"/>
       <c r="H304" s="6" t="n"/>
@@ -5716,21 +5728,15 @@
       <c r="K304" s="6" t="n"/>
       <c r="L304" s="6" t="n"/>
     </row>
-    <row r="305" ht="18" customHeight="1">
-      <c r="A305" s="5" t="inlineStr">
-        <is>
-          <t>9B</t>
-        </is>
-      </c>
-      <c r="B305" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F305" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="305" ht="15" customHeight="1">
+      <c r="A305" s="7" t="n"/>
+      <c r="B305" s="8" t="inlineStr">
+        <is>
+          <t>SL 72 RS ( HQ4909 )</t>
+        </is>
+      </c>
+      <c r="F305" s="9" t="n">
+        <v>1865</v>
       </c>
       <c r="G305" s="6" t="n"/>
       <c r="H305" s="6" t="n"/>
@@ -5743,11 +5749,11 @@
       <c r="A306" s="7" t="n"/>
       <c r="B306" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( IH3994 )</t>
+          <t>SL 72 RS EL I ( IH2978 )</t>
         </is>
       </c>
       <c r="F306" s="9" t="n">
-        <v>1177</v>
+        <v>727</v>
       </c>
       <c r="G306" s="6" t="n"/>
       <c r="H306" s="6" t="n"/>
@@ -5760,11 +5766,11 @@
       <c r="A307" s="7" t="n"/>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( JI0182 )</t>
+          <t>SL 72 RS EL C ( IH2982 )</t>
         </is>
       </c>
       <c r="F307" s="9" t="n">
-        <v>2145</v>
+        <v>260</v>
       </c>
       <c r="G307" s="6" t="n"/>
       <c r="H307" s="6" t="n"/>
@@ -5777,11 +5783,11 @@
       <c r="A308" s="7" t="n"/>
       <c r="B308" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( JI0183 )</t>
+          <t>SL 72 RS EL C ( JH9953 )</t>
         </is>
       </c>
       <c r="F308" s="9" t="n">
-        <v>2079</v>
+        <v>263</v>
       </c>
       <c r="G308" s="6" t="n"/>
       <c r="H308" s="6" t="n"/>
@@ -5794,11 +5800,11 @@
       <c r="A309" s="7" t="n"/>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9653 )</t>
+          <t>SL 72 RS EL I ( JI3089 )</t>
         </is>
       </c>
       <c r="F309" s="9" t="n">
-        <v>1120</v>
+        <v>455</v>
       </c>
       <c r="G309" s="6" t="n"/>
       <c r="H309" s="6" t="n"/>
@@ -5811,11 +5817,11 @@
       <c r="A310" s="7" t="n"/>
       <c r="B310" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1674 )</t>
+          <t>SL 72 RS ( JQ9824 )</t>
         </is>
       </c>
       <c r="F310" s="9" t="n">
-        <v>2103</v>
+        <v>1608</v>
       </c>
       <c r="G310" s="6" t="n"/>
       <c r="H310" s="6" t="n"/>
@@ -5828,11 +5834,11 @@
       <c r="A311" s="7" t="n"/>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7510 )</t>
+          <t>SL 72 RS ( KH9652 )</t>
         </is>
       </c>
       <c r="F311" s="9" t="n">
-        <v>3929</v>
+        <v>890</v>
       </c>
       <c r="G311" s="6" t="n"/>
       <c r="H311" s="6" t="n"/>
@@ -5845,11 +5851,11 @@
       <c r="A312" s="7" t="n"/>
       <c r="B312" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
+          <t>SL 72 RS ( KH9653 )</t>
         </is>
       </c>
       <c r="F312" s="9" t="n">
-        <v>11247</v>
+        <v>1134</v>
       </c>
       <c r="G312" s="6" t="n"/>
       <c r="H312" s="6" t="n"/>
@@ -5862,11 +5868,11 @@
       <c r="A313" s="7" t="n"/>
       <c r="B313" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KZ6449 )</t>
+          <t>SL 72 RS ( KH9656 )</t>
         </is>
       </c>
       <c r="F313" s="9" t="n">
-        <v>7616</v>
+        <v>152</v>
       </c>
       <c r="G313" s="6" t="n"/>
       <c r="H313" s="6" t="n"/>
@@ -5879,11 +5885,11 @@
       <c r="A314" s="7" t="n"/>
       <c r="B314" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ8301 )</t>
+          <t>SL 72 RS ( KH9657 )</t>
         </is>
       </c>
       <c r="F314" s="9" t="n">
-        <v>6025</v>
+        <v>300</v>
       </c>
       <c r="G314" s="6" t="n"/>
       <c r="H314" s="6" t="n"/>
@@ -5896,11 +5902,11 @@
       <c r="A315" s="7" t="n"/>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
+          <t>SL 72 RS ( KH9658 )</t>
         </is>
       </c>
       <c r="F315" s="9" t="n">
-        <v>1154</v>
+        <v>152</v>
       </c>
       <c r="G315" s="6" t="n"/>
       <c r="H315" s="6" t="n"/>
@@ -5909,21 +5915,15 @@
       <c r="K315" s="6" t="n"/>
       <c r="L315" s="6" t="n"/>
     </row>
-    <row r="316" ht="18" customHeight="1">
-      <c r="A316" s="5" t="inlineStr">
-        <is>
-          <t>9C</t>
-        </is>
-      </c>
-      <c r="B316" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F316" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="316" ht="15" customHeight="1">
+      <c r="A316" s="7" t="n"/>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
+          <t>SL 72 RS J ( KJ0690 )</t>
+        </is>
+      </c>
+      <c r="F316" s="9" t="n">
+        <v>1352</v>
       </c>
       <c r="G316" s="6" t="n"/>
       <c r="H316" s="6" t="n"/>
@@ -5936,11 +5936,11 @@
       <c r="A317" s="7" t="n"/>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t>( HP5123 )</t>
+          <t>SL 72 RS ( KJ1666 )</t>
         </is>
       </c>
       <c r="F317" s="9" t="n">
-        <v>4000</v>
+        <v>2516</v>
       </c>
       <c r="G317" s="6" t="n"/>
       <c r="H317" s="6" t="n"/>
@@ -5953,11 +5953,11 @@
       <c r="A318" s="7" t="n"/>
       <c r="B318" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( HQ4909 )</t>
+          <t>SL 72 RS ( KJ1667 )</t>
         </is>
       </c>
       <c r="F318" s="9" t="n">
-        <v>9127</v>
+        <v>1704</v>
       </c>
       <c r="G318" s="6" t="n"/>
       <c r="H318" s="6" t="n"/>
@@ -5970,11 +5970,11 @@
       <c r="A319" s="7" t="n"/>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS EL I ( IH2978 )</t>
+          <t>SL 72 RS ( KJ1669 )</t>
         </is>
       </c>
       <c r="F319" s="9" t="n">
-        <v>1454</v>
+        <v>1032</v>
       </c>
       <c r="G319" s="6" t="n"/>
       <c r="H319" s="6" t="n"/>
@@ -5987,11 +5987,11 @@
       <c r="A320" s="7" t="n"/>
       <c r="B320" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS EL C ( IH2982 )</t>
+          <t>SL 72 RS ( KJ1670 )</t>
         </is>
       </c>
       <c r="F320" s="9" t="n">
-        <v>520</v>
+        <v>1257</v>
       </c>
       <c r="G320" s="6" t="n"/>
       <c r="H320" s="6" t="n"/>
@@ -6004,11 +6004,11 @@
       <c r="A321" s="7" t="n"/>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS EL C ( JH9953 )</t>
+          <t>SL 72 RS ( KJ1672 )</t>
         </is>
       </c>
       <c r="F321" s="9" t="n">
-        <v>526</v>
+        <v>2910</v>
       </c>
       <c r="G321" s="6" t="n"/>
       <c r="H321" s="6" t="n"/>
@@ -6021,11 +6021,11 @@
       <c r="A322" s="7" t="n"/>
       <c r="B322" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS EL I ( JI3089 )</t>
+          <t>SL 72 RS ( KJ1673 )</t>
         </is>
       </c>
       <c r="F322" s="9" t="n">
-        <v>910</v>
+        <v>389</v>
       </c>
       <c r="G322" s="6" t="n"/>
       <c r="H322" s="6" t="n"/>
@@ -6038,11 +6038,11 @@
       <c r="A323" s="7" t="n"/>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( JQ9824 )</t>
+          <t>SL 72 OG W ( KJ2282 )</t>
         </is>
       </c>
       <c r="F323" s="9" t="n">
-        <v>6432</v>
+        <v>1112</v>
       </c>
       <c r="G323" s="6" t="n"/>
       <c r="H323" s="6" t="n"/>
@@ -6051,32 +6051,28 @@
       <c r="K323" s="6" t="n"/>
       <c r="L323" s="6" t="n"/>
     </row>
-    <row r="324" ht="15" customHeight="1">
-      <c r="A324" s="7" t="n"/>
-      <c r="B324" s="8" t="inlineStr">
-        <is>
-          <t>SL 72 RS ( KH9652 )</t>
-        </is>
-      </c>
-      <c r="F324" s="9" t="n">
-        <v>1540</v>
-      </c>
-      <c r="G324" s="6" t="n"/>
-      <c r="H324" s="6" t="n"/>
-      <c r="I324" s="6" t="n"/>
-      <c r="J324" s="6" t="n"/>
-      <c r="K324" s="6" t="n"/>
-      <c r="L324" s="6" t="n"/>
-    </row>
-    <row r="325" ht="15" customHeight="1">
-      <c r="A325" s="7" t="n"/>
-      <c r="B325" s="8" t="inlineStr">
-        <is>
-          <t>SL 72 RS ( KH9653 )</t>
-        </is>
-      </c>
-      <c r="F325" s="9" t="n">
-        <v>1764</v>
+    <row r="324">
+      <c r="A324" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 10 （加10部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="18" customHeight="1">
+      <c r="A325" s="5" t="inlineStr">
+        <is>
+          <t>10A</t>
+        </is>
+      </c>
+      <c r="B325" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F325" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G325" s="6" t="n"/>
       <c r="H325" s="6" t="n"/>
@@ -6089,11 +6085,11 @@
       <c r="A326" s="7" t="n"/>
       <c r="B326" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9656 )</t>
+          <t>OZGAIA W ( IG6045 )</t>
         </is>
       </c>
       <c r="F326" s="9" t="n">
-        <v>304</v>
+        <v>18755</v>
       </c>
       <c r="G326" s="6" t="n"/>
       <c r="H326" s="6" t="n"/>
@@ -6106,11 +6102,11 @@
       <c r="A327" s="7" t="n"/>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9657 )</t>
+          <t>OZGAIA W ( IG6047 )</t>
         </is>
       </c>
       <c r="F327" s="9" t="n">
-        <v>600</v>
+        <v>309</v>
       </c>
       <c r="G327" s="6" t="n"/>
       <c r="H327" s="6" t="n"/>
@@ -6123,11 +6119,11 @@
       <c r="A328" s="7" t="n"/>
       <c r="B328" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9658 )</t>
+          <t>OZGAIA W ( IG6049 )</t>
         </is>
       </c>
       <c r="F328" s="9" t="n">
-        <v>304</v>
+        <v>2015</v>
       </c>
       <c r="G328" s="6" t="n"/>
       <c r="H328" s="6" t="n"/>
@@ -6140,11 +6136,11 @@
       <c r="A329" s="7" t="n"/>
       <c r="B329" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9671 )</t>
+          <t>OZMILLEN ( IH0874 )</t>
         </is>
       </c>
       <c r="F329" s="9" t="n">
-        <v>137</v>
+        <v>600</v>
       </c>
       <c r="G329" s="6" t="n"/>
       <c r="H329" s="6" t="n"/>
@@ -6157,11 +6153,11 @@
       <c r="A330" s="7" t="n"/>
       <c r="B330" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9672 )</t>
+          <t>OZMILLEN W ( JH5642 )</t>
         </is>
       </c>
       <c r="F330" s="9" t="n">
-        <v>1544</v>
+        <v>580</v>
       </c>
       <c r="G330" s="6" t="n"/>
       <c r="H330" s="6" t="n"/>
@@ -6174,11 +6170,11 @@
       <c r="A331" s="7" t="n"/>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KH9673 )</t>
+          <t>OZMILLEN ( JI2632 )</t>
         </is>
       </c>
       <c r="F331" s="9" t="n">
-        <v>4979</v>
+        <v>500</v>
       </c>
       <c r="G331" s="6" t="n"/>
       <c r="H331" s="6" t="n"/>
@@ -6191,11 +6187,11 @@
       <c r="A332" s="7" t="n"/>
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS J ( KJ0690 )</t>
+          <t>OZMILLEN ( JI2633 )</t>
         </is>
       </c>
       <c r="F332" s="9" t="n">
-        <v>2704</v>
+        <v>1200</v>
       </c>
       <c r="G332" s="6" t="n"/>
       <c r="H332" s="6" t="n"/>
@@ -6208,11 +6204,11 @@
       <c r="A333" s="7" t="n"/>
       <c r="B333" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1666 )</t>
+          <t>OZMILLEN ( JP7827 )</t>
         </is>
       </c>
       <c r="F333" s="9" t="n">
-        <v>7162</v>
+        <v>2664</v>
       </c>
       <c r="G333" s="6" t="n"/>
       <c r="H333" s="6" t="n"/>
@@ -6225,11 +6221,11 @@
       <c r="A334" s="7" t="n"/>
       <c r="B334" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1667 )</t>
+          <t>ADISTAR XLG 2.0 W ( KJ7852 )</t>
         </is>
       </c>
       <c r="F334" s="9" t="n">
-        <v>3408</v>
+        <v>1865</v>
       </c>
       <c r="G334" s="6" t="n"/>
       <c r="H334" s="6" t="n"/>
@@ -6242,11 +6238,11 @@
       <c r="A335" s="7" t="n"/>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1669 )</t>
+          <t>ADISTAR XLG 2.0 W ( KJ7853 )</t>
         </is>
       </c>
       <c r="F335" s="9" t="n">
-        <v>2064</v>
+        <v>2705</v>
       </c>
       <c r="G335" s="6" t="n"/>
       <c r="H335" s="6" t="n"/>
@@ -6259,11 +6255,11 @@
       <c r="A336" s="7" t="n"/>
       <c r="B336" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1670 )</t>
+          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
         </is>
       </c>
       <c r="F336" s="9" t="n">
-        <v>2514</v>
+        <v>2100</v>
       </c>
       <c r="G336" s="6" t="n"/>
       <c r="H336" s="6" t="n"/>
@@ -6276,11 +6272,11 @@
       <c r="A337" s="7" t="n"/>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1672 )</t>
+          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
         </is>
       </c>
       <c r="F337" s="9" t="n">
-        <v>5820</v>
+        <v>2443</v>
       </c>
       <c r="G337" s="6" t="n"/>
       <c r="H337" s="6" t="n"/>
@@ -6293,11 +6289,11 @@
       <c r="A338" s="7" t="n"/>
       <c r="B338" s="8" t="inlineStr">
         <is>
-          <t>SL 72 RS ( KJ1673 )</t>
+          <t>ADISTAR XLG 2.0 W ( KZ9344 )</t>
         </is>
       </c>
       <c r="F338" s="9" t="n">
-        <v>2284</v>
+        <v>2796</v>
       </c>
       <c r="G338" s="6" t="n"/>
       <c r="H338" s="6" t="n"/>
@@ -6310,11 +6306,11 @@
       <c r="A339" s="7" t="n"/>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t>SL 72 OG W ( KJ2282 )</t>
+          <t>( LA6421 )</t>
         </is>
       </c>
       <c r="F339" s="9" t="n">
-        <v>2644</v>
+        <v>300</v>
       </c>
       <c r="G339" s="6" t="n"/>
       <c r="H339" s="6" t="n"/>
@@ -6323,28 +6319,38 @@
       <c r="K339" s="6" t="n"/>
       <c r="L339" s="6" t="n"/>
     </row>
-    <row r="340">
-      <c r="A340" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 10 （加10部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="341" ht="18" customHeight="1">
-      <c r="A341" s="5" t="inlineStr">
-        <is>
-          <t>10A</t>
-        </is>
-      </c>
-      <c r="B341" s="5" t="inlineStr">
+    <row r="340" ht="18" customHeight="1">
+      <c r="A340" s="5" t="inlineStr">
+        <is>
+          <t>10B</t>
+        </is>
+      </c>
+      <c r="B340" s="5" t="inlineStr">
         <is>
           <t>鞋型 + ART</t>
         </is>
       </c>
-      <c r="F341" s="5" t="inlineStr">
+      <c r="F340" s="5" t="inlineStr">
         <is>
           <t>訂單</t>
         </is>
+      </c>
+      <c r="G340" s="6" t="n"/>
+      <c r="H340" s="6" t="n"/>
+      <c r="I340" s="6" t="n"/>
+      <c r="J340" s="6" t="n"/>
+      <c r="K340" s="6" t="n"/>
+      <c r="L340" s="6" t="n"/>
+    </row>
+    <row r="341" ht="15" customHeight="1">
+      <c r="A341" s="7" t="n"/>
+      <c r="B341" s="8" t="inlineStr">
+        <is>
+          <t>ADISTAR XLG 2.0 J ( KH7374 )</t>
+        </is>
+      </c>
+      <c r="F341" s="9" t="n">
+        <v>1602</v>
       </c>
       <c r="G341" s="6" t="n"/>
       <c r="H341" s="6" t="n"/>
@@ -6357,11 +6363,11 @@
       <c r="A342" s="7" t="n"/>
       <c r="B342" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6045 )</t>
+          <t>ADISTAR XLG 2.0 J ( KJ7844 )</t>
         </is>
       </c>
       <c r="F342" s="9" t="n">
-        <v>18755</v>
+        <v>1050</v>
       </c>
       <c r="G342" s="6" t="n"/>
       <c r="H342" s="6" t="n"/>
@@ -6374,11 +6380,11 @@
       <c r="A343" s="7" t="n"/>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6047 )</t>
+          <t>ADISTAR XLG 2.0 J ( KJ7845 )</t>
         </is>
       </c>
       <c r="F343" s="9" t="n">
-        <v>309</v>
+        <v>1200</v>
       </c>
       <c r="G343" s="6" t="n"/>
       <c r="H343" s="6" t="n"/>
@@ -6391,11 +6397,11 @@
       <c r="A344" s="7" t="n"/>
       <c r="B344" s="8" t="inlineStr">
         <is>
-          <t>OZGAIA W ( IG6049 )</t>
+          <t>ADISTAR XLG 2.0 W ( KJ7852 )</t>
         </is>
       </c>
       <c r="F344" s="9" t="n">
-        <v>2015</v>
+        <v>3068</v>
       </c>
       <c r="G344" s="6" t="n"/>
       <c r="H344" s="6" t="n"/>
@@ -6408,11 +6414,11 @@
       <c r="A345" s="7" t="n"/>
       <c r="B345" s="8" t="inlineStr">
         <is>
-          <t>OZMILLEN ( IH0874 )</t>
+          <t>ADISTAR XLG 2.0 W ( KJ7853 )</t>
         </is>
       </c>
       <c r="F345" s="9" t="n">
-        <v>600</v>
+        <v>1225</v>
       </c>
       <c r="G345" s="6" t="n"/>
       <c r="H345" s="6" t="n"/>
@@ -6425,11 +6431,11 @@
       <c r="A346" s="7" t="n"/>
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t>OZMILLEN W ( JH5642 )</t>
+          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
         </is>
       </c>
       <c r="F346" s="9" t="n">
-        <v>580</v>
+        <v>1320</v>
       </c>
       <c r="G346" s="6" t="n"/>
       <c r="H346" s="6" t="n"/>
@@ -6442,11 +6448,11 @@
       <c r="A347" s="7" t="n"/>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t>OZMILLEN ( JI2632 )</t>
+          <t>ADISTAR XLG 2.0 W ( KK2904 )</t>
         </is>
       </c>
       <c r="F347" s="9" t="n">
-        <v>500</v>
+        <v>1862</v>
       </c>
       <c r="G347" s="6" t="n"/>
       <c r="H347" s="6" t="n"/>
@@ -6459,11 +6465,11 @@
       <c r="A348" s="7" t="n"/>
       <c r="B348" s="8" t="inlineStr">
         <is>
-          <t>OZMILLEN ( JI2633 )</t>
+          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
         </is>
       </c>
       <c r="F348" s="9" t="n">
-        <v>1200</v>
+        <v>8123</v>
       </c>
       <c r="G348" s="6" t="n"/>
       <c r="H348" s="6" t="n"/>
@@ -6476,11 +6482,11 @@
       <c r="A349" s="7" t="n"/>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t>OZMILLEN ( JP7827 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F349" s="9" t="n">
-        <v>2664</v>
+        <v>662</v>
       </c>
       <c r="G349" s="6" t="n"/>
       <c r="H349" s="6" t="n"/>
@@ -6493,11 +6499,11 @@
       <c r="A350" s="7" t="n"/>
       <c r="B350" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KJ7852 )</t>
+          <t>ADISTAR XLG 2.0 W ( LA0522 )</t>
         </is>
       </c>
       <c r="F350" s="9" t="n">
-        <v>1865</v>
+        <v>1</v>
       </c>
       <c r="G350" s="6" t="n"/>
       <c r="H350" s="6" t="n"/>
@@ -6506,15 +6512,21 @@
       <c r="K350" s="6" t="n"/>
       <c r="L350" s="6" t="n"/>
     </row>
-    <row r="351" ht="15" customHeight="1">
-      <c r="A351" s="7" t="n"/>
-      <c r="B351" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 W ( KJ7853 )</t>
-        </is>
-      </c>
-      <c r="F351" s="9" t="n">
-        <v>2705</v>
+    <row r="351" ht="18" customHeight="1">
+      <c r="A351" s="5" t="inlineStr">
+        <is>
+          <t>10C</t>
+        </is>
+      </c>
+      <c r="B351" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F351" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G351" s="6" t="n"/>
       <c r="H351" s="6" t="n"/>
@@ -6527,11 +6539,11 @@
       <c r="A352" s="7" t="n"/>
       <c r="B352" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
+          <t>HANDBALL SPEZIAL ( KH6397 )</t>
         </is>
       </c>
       <c r="F352" s="9" t="n">
-        <v>2100</v>
+        <v>310</v>
       </c>
       <c r="G352" s="6" t="n"/>
       <c r="H352" s="6" t="n"/>
@@ -6544,11 +6556,11 @@
       <c r="A353" s="7" t="n"/>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
+          <t>HANDBALL SPEZIAL ( KI5241 )</t>
         </is>
       </c>
       <c r="F353" s="9" t="n">
-        <v>2443</v>
+        <v>310</v>
       </c>
       <c r="G353" s="6" t="n"/>
       <c r="H353" s="6" t="n"/>
@@ -6561,11 +6573,11 @@
       <c r="A354" s="7" t="n"/>
       <c r="B354" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KZ9344 )</t>
+          <t>SPEZIAL GOLF ( KJ0849 )</t>
         </is>
       </c>
       <c r="F354" s="9" t="n">
-        <v>2796</v>
+        <v>3060</v>
       </c>
       <c r="G354" s="6" t="n"/>
       <c r="H354" s="6" t="n"/>
@@ -6578,11 +6590,11 @@
       <c r="A355" s="7" t="n"/>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t>( LA6421 )</t>
+          <t>SPEZIAL GOLF ( KJ0850 )</t>
         </is>
       </c>
       <c r="F355" s="9" t="n">
-        <v>300</v>
+        <v>2262</v>
       </c>
       <c r="G355" s="6" t="n"/>
       <c r="H355" s="6" t="n"/>
@@ -6591,21 +6603,15 @@
       <c r="K355" s="6" t="n"/>
       <c r="L355" s="6" t="n"/>
     </row>
-    <row r="356" ht="18" customHeight="1">
-      <c r="A356" s="5" t="inlineStr">
-        <is>
-          <t>10B</t>
-        </is>
-      </c>
-      <c r="B356" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F356" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="356" ht="15" customHeight="1">
+      <c r="A356" s="7" t="n"/>
+      <c r="B356" s="8" t="inlineStr">
+        <is>
+          <t>SPEZIAL GOLF ( KJ0851 )</t>
+        </is>
+      </c>
+      <c r="F356" s="9" t="n">
+        <v>1770</v>
       </c>
       <c r="G356" s="6" t="n"/>
       <c r="H356" s="6" t="n"/>
@@ -6618,11 +6624,11 @@
       <c r="A357" s="7" t="n"/>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KH7374 )</t>
+          <t>HANDBALL SPEZIAL ( KK3015 )</t>
         </is>
       </c>
       <c r="F357" s="9" t="n">
-        <v>1602</v>
+        <v>1030</v>
       </c>
       <c r="G357" s="6" t="n"/>
       <c r="H357" s="6" t="n"/>
@@ -6635,11 +6641,11 @@
       <c r="A358" s="7" t="n"/>
       <c r="B358" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7844 )</t>
+          <t>HANDBALL SPEZIAL ( KK3018 )</t>
         </is>
       </c>
       <c r="F358" s="9" t="n">
-        <v>1050</v>
+        <v>310</v>
       </c>
       <c r="G358" s="6" t="n"/>
       <c r="H358" s="6" t="n"/>
@@ -6652,11 +6658,11 @@
       <c r="A359" s="7" t="n"/>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7845 )</t>
+          <t>HANDBALL SPEZIAL ( KK3019 )</t>
         </is>
       </c>
       <c r="F359" s="9" t="n">
-        <v>1200</v>
+        <v>2774</v>
       </c>
       <c r="G359" s="6" t="n"/>
       <c r="H359" s="6" t="n"/>
@@ -6669,11 +6675,11 @@
       <c r="A360" s="7" t="n"/>
       <c r="B360" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KJ7852 )</t>
+          <t>HANDBALL SPEZIAL ( KK3025 )</t>
         </is>
       </c>
       <c r="F360" s="9" t="n">
-        <v>3068</v>
+        <v>994</v>
       </c>
       <c r="G360" s="6" t="n"/>
       <c r="H360" s="6" t="n"/>
@@ -6686,11 +6692,11 @@
       <c r="A361" s="7" t="n"/>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KJ7853 )</t>
+          <t>HANDBALL SPEZIAL ( KK3026 )</t>
         </is>
       </c>
       <c r="F361" s="9" t="n">
-        <v>1225</v>
+        <v>432</v>
       </c>
       <c r="G361" s="6" t="n"/>
       <c r="H361" s="6" t="n"/>
@@ -6703,11 +6709,11 @@
       <c r="A362" s="7" t="n"/>
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7892 )</t>
+          <t>HANDBALL SPEZIAL ( KK3027 )</t>
         </is>
       </c>
       <c r="F362" s="9" t="n">
-        <v>1320</v>
+        <v>432</v>
       </c>
       <c r="G362" s="6" t="n"/>
       <c r="H362" s="6" t="n"/>
@@ -6720,11 +6726,11 @@
       <c r="A363" s="7" t="n"/>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KK2904 )</t>
+          <t>HANDBALL SPEZIAL ( LA3255 )</t>
         </is>
       </c>
       <c r="F363" s="9" t="n">
-        <v>1862</v>
+        <v>1100</v>
       </c>
       <c r="G363" s="6" t="n"/>
       <c r="H363" s="6" t="n"/>
@@ -6733,32 +6739,28 @@
       <c r="K363" s="6" t="n"/>
       <c r="L363" s="6" t="n"/>
     </row>
-    <row r="364" ht="15" customHeight="1">
-      <c r="A364" s="7" t="n"/>
-      <c r="B364" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J ( KK4234 )</t>
-        </is>
-      </c>
-      <c r="F364" s="9" t="n">
-        <v>8123</v>
-      </c>
-      <c r="G364" s="6" t="n"/>
-      <c r="H364" s="6" t="n"/>
-      <c r="I364" s="6" t="n"/>
-      <c r="J364" s="6" t="n"/>
-      <c r="K364" s="6" t="n"/>
-      <c r="L364" s="6" t="n"/>
-    </row>
-    <row r="365" ht="15" customHeight="1">
-      <c r="A365" s="7" t="n"/>
-      <c r="B365" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
-        </is>
-      </c>
-      <c r="F365" s="9" t="n">
-        <v>662</v>
+    <row r="364">
+      <c r="A364" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 11 （加11部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="18" customHeight="1">
+      <c r="A365" s="5" t="inlineStr">
+        <is>
+          <t>11A1</t>
+        </is>
+      </c>
+      <c r="B365" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F365" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G365" s="6" t="n"/>
       <c r="H365" s="6" t="n"/>
@@ -6771,11 +6773,11 @@
       <c r="A366" s="7" t="n"/>
       <c r="B366" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( LA0522 )</t>
+          <t>S2G 26 LEATHER ( HP7087 )</t>
         </is>
       </c>
       <c r="F366" s="9" t="n">
-        <v>1</v>
+        <v>888</v>
       </c>
       <c r="G366" s="6" t="n"/>
       <c r="H366" s="6" t="n"/>
@@ -6784,21 +6786,15 @@
       <c r="K366" s="6" t="n"/>
       <c r="L366" s="6" t="n"/>
     </row>
-    <row r="367" ht="18" customHeight="1">
-      <c r="A367" s="5" t="inlineStr">
-        <is>
-          <t>10C</t>
-        </is>
-      </c>
-      <c r="B367" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F367" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="367" ht="15" customHeight="1">
+      <c r="A367" s="7" t="n"/>
+      <c r="B367" s="8" t="inlineStr">
+        <is>
+          <t>S2G 26 TEX ( HP7088 )</t>
+        </is>
+      </c>
+      <c r="F367" s="9" t="n">
+        <v>77</v>
       </c>
       <c r="G367" s="6" t="n"/>
       <c r="H367" s="6" t="n"/>
@@ -6811,11 +6807,11 @@
       <c r="A368" s="7" t="n"/>
       <c r="B368" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KH6397 )</t>
+          <t>S2G 26 LEATHER ( HQ5054 )</t>
         </is>
       </c>
       <c r="F368" s="9" t="n">
-        <v>310</v>
+        <v>1178</v>
       </c>
       <c r="G368" s="6" t="n"/>
       <c r="H368" s="6" t="n"/>
@@ -6828,11 +6824,11 @@
       <c r="A369" s="7" t="n"/>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KI5241 )</t>
+          <t>W ADIPOWER 26 SL BOA ( JP8385 )</t>
         </is>
       </c>
       <c r="F369" s="9" t="n">
-        <v>3876</v>
+        <v>349</v>
       </c>
       <c r="G369" s="6" t="n"/>
       <c r="H369" s="6" t="n"/>
@@ -6845,11 +6841,11 @@
       <c r="A370" s="7" t="n"/>
       <c r="B370" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KI5303 )</t>
+          <t>ADIPOWER 26 SL ( JP8394 )</t>
         </is>
       </c>
       <c r="F370" s="9" t="n">
-        <v>747</v>
+        <v>248</v>
       </c>
       <c r="G370" s="6" t="n"/>
       <c r="H370" s="6" t="n"/>
@@ -6862,11 +6858,11 @@
       <c r="A371" s="7" t="n"/>
       <c r="B371" s="8" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF ( KJ0849 )</t>
+          <t>ADIPOWER 26 SL ( JP8395 )</t>
         </is>
       </c>
       <c r="F371" s="9" t="n">
-        <v>4525</v>
+        <v>79</v>
       </c>
       <c r="G371" s="6" t="n"/>
       <c r="H371" s="6" t="n"/>
@@ -6879,11 +6875,11 @@
       <c r="A372" s="7" t="n"/>
       <c r="B372" s="8" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF ( KJ0850 )</t>
+          <t>W S2G 26 LEATHER ( JQ3560 )</t>
         </is>
       </c>
       <c r="F372" s="9" t="n">
-        <v>7284</v>
+        <v>1203</v>
       </c>
       <c r="G372" s="6" t="n"/>
       <c r="H372" s="6" t="n"/>
@@ -6896,11 +6892,11 @@
       <c r="A373" s="7" t="n"/>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF ( KJ0851 )</t>
+          <t>W S2G 26 TEX ( JQ3563 )</t>
         </is>
       </c>
       <c r="F373" s="9" t="n">
-        <v>2913</v>
+        <v>60</v>
       </c>
       <c r="G373" s="6" t="n"/>
       <c r="H373" s="6" t="n"/>
@@ -6913,11 +6909,11 @@
       <c r="A374" s="7" t="n"/>
       <c r="B374" s="8" t="inlineStr">
         <is>
-          <t>SPEZIAL GOLF ( KJ0852 )</t>
+          <t>S2G 26 LEATHER ( JQ9311 )</t>
         </is>
       </c>
       <c r="F374" s="9" t="n">
-        <v>3307</v>
+        <v>452</v>
       </c>
       <c r="G374" s="6" t="n"/>
       <c r="H374" s="6" t="n"/>
@@ -6930,11 +6926,11 @@
       <c r="A375" s="7" t="n"/>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3015 )</t>
+          <t>S2G 26 TEX ( JR1879 )</t>
         </is>
       </c>
       <c r="F375" s="9" t="n">
-        <v>1612</v>
+        <v>189</v>
       </c>
       <c r="G375" s="6" t="n"/>
       <c r="H375" s="6" t="n"/>
@@ -6947,11 +6943,11 @@
       <c r="A376" s="7" t="n"/>
       <c r="B376" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3017 )</t>
+          <t>ADIPOWER 26 SL BOA ( JS4138 )</t>
         </is>
       </c>
       <c r="F376" s="9" t="n">
-        <v>100</v>
+        <v>377</v>
       </c>
       <c r="G376" s="6" t="n"/>
       <c r="H376" s="6" t="n"/>
@@ -6964,11 +6960,11 @@
       <c r="A377" s="7" t="n"/>
       <c r="B377" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3018 )</t>
+          <t>ADIPOWER 26 SL BOA ( JS4140 )</t>
         </is>
       </c>
       <c r="F377" s="9" t="n">
-        <v>310</v>
+        <v>221</v>
       </c>
       <c r="G377" s="6" t="n"/>
       <c r="H377" s="6" t="n"/>
@@ -6981,11 +6977,11 @@
       <c r="A378" s="7" t="n"/>
       <c r="B378" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3019 )</t>
+          <t>S2G VENT ( KI1392 )</t>
         </is>
       </c>
       <c r="F378" s="9" t="n">
-        <v>2774</v>
+        <v>1107</v>
       </c>
       <c r="G378" s="6" t="n"/>
       <c r="H378" s="6" t="n"/>
@@ -6998,11 +6994,11 @@
       <c r="A379" s="7" t="n"/>
       <c r="B379" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3021 )</t>
+          <t>S2G VENT ( KI8398 )</t>
         </is>
       </c>
       <c r="F379" s="9" t="n">
-        <v>1189</v>
+        <v>1203</v>
       </c>
       <c r="G379" s="6" t="n"/>
       <c r="H379" s="6" t="n"/>
@@ -7015,11 +7011,11 @@
       <c r="A380" s="7" t="n"/>
       <c r="B380" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3025 )</t>
+          <t>W S2G VENT ( KI8401 )</t>
         </is>
       </c>
       <c r="F380" s="9" t="n">
-        <v>994</v>
+        <v>1200</v>
       </c>
       <c r="G380" s="6" t="n"/>
       <c r="H380" s="6" t="n"/>
@@ -7032,11 +7028,11 @@
       <c r="A381" s="7" t="n"/>
       <c r="B381" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3026 )</t>
+          <t>W S2G VENT ( KI8402 )</t>
         </is>
       </c>
       <c r="F381" s="9" t="n">
-        <v>432</v>
+        <v>2584</v>
       </c>
       <c r="G381" s="6" t="n"/>
       <c r="H381" s="6" t="n"/>
@@ -7049,11 +7045,11 @@
       <c r="A382" s="7" t="n"/>
       <c r="B382" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3027 )</t>
+          <t>ADIPOWER 26 ( KJ3010 )</t>
         </is>
       </c>
       <c r="F382" s="9" t="n">
-        <v>432</v>
+        <v>1205</v>
       </c>
       <c r="G382" s="6" t="n"/>
       <c r="H382" s="6" t="n"/>
@@ -7066,11 +7062,11 @@
       <c r="A383" s="7" t="n"/>
       <c r="B383" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( KK3033 )</t>
+          <t>S2G 26 TEX ( KK0666 )</t>
         </is>
       </c>
       <c r="F383" s="9" t="n">
-        <v>384</v>
+        <v>127</v>
       </c>
       <c r="G383" s="6" t="n"/>
       <c r="H383" s="6" t="n"/>
@@ -7083,11 +7079,11 @@
       <c r="A384" s="7" t="n"/>
       <c r="B384" s="8" t="inlineStr">
         <is>
-          <t>HANDBALL SPEZIAL ( LA3255 )</t>
+          <t>ADIPOWER 26 ( KK2836 )</t>
         </is>
       </c>
       <c r="F384" s="9" t="n">
-        <v>1100</v>
+        <v>275</v>
       </c>
       <c r="G384" s="6" t="n"/>
       <c r="H384" s="6" t="n"/>
@@ -7096,28 +7092,32 @@
       <c r="K384" s="6" t="n"/>
       <c r="L384" s="6" t="n"/>
     </row>
-    <row r="385">
-      <c r="A385" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 11 （加11部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="386" ht="18" customHeight="1">
-      <c r="A386" s="5" t="inlineStr">
-        <is>
-          <t>11A1</t>
-        </is>
-      </c>
-      <c r="B386" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F386" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="385" ht="15" customHeight="1">
+      <c r="A385" s="7" t="n"/>
+      <c r="B385" s="8" t="inlineStr">
+        <is>
+          <t>ADIPOWER 26 SL ( KK2838 )</t>
+        </is>
+      </c>
+      <c r="F385" s="9" t="n">
+        <v>379</v>
+      </c>
+      <c r="G385" s="6" t="n"/>
+      <c r="H385" s="6" t="n"/>
+      <c r="I385" s="6" t="n"/>
+      <c r="J385" s="6" t="n"/>
+      <c r="K385" s="6" t="n"/>
+      <c r="L385" s="6" t="n"/>
+    </row>
+    <row r="386" ht="15" customHeight="1">
+      <c r="A386" s="7" t="n"/>
+      <c r="B386" s="8" t="inlineStr">
+        <is>
+          <t>ADIPOWER 26 SL BOA ( KK2839 )</t>
+        </is>
+      </c>
+      <c r="F386" s="9" t="n">
+        <v>483</v>
       </c>
       <c r="G386" s="6" t="n"/>
       <c r="H386" s="6" t="n"/>
@@ -7130,11 +7130,11 @@
       <c r="A387" s="7" t="n"/>
       <c r="B387" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( HP7087 )</t>
+          <t>W ADIPOWER 26 SL BOA ( KK2843 )</t>
         </is>
       </c>
       <c r="F387" s="9" t="n">
-        <v>888</v>
+        <v>346</v>
       </c>
       <c r="G387" s="6" t="n"/>
       <c r="H387" s="6" t="n"/>
@@ -7147,11 +7147,11 @@
       <c r="A388" s="7" t="n"/>
       <c r="B388" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 TEX ( HP7088 )</t>
+          <t>W S2G 26 TEX ( KK2862 )</t>
         </is>
       </c>
       <c r="F388" s="9" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="G388" s="6" t="n"/>
       <c r="H388" s="6" t="n"/>
@@ -7164,11 +7164,11 @@
       <c r="A389" s="7" t="n"/>
       <c r="B389" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( HQ5054 )</t>
+          <t>S2G 26 TEX ( KK2872 )</t>
         </is>
       </c>
       <c r="F389" s="9" t="n">
-        <v>1178</v>
+        <v>249</v>
       </c>
       <c r="G389" s="6" t="n"/>
       <c r="H389" s="6" t="n"/>
@@ -7177,15 +7177,21 @@
       <c r="K389" s="6" t="n"/>
       <c r="L389" s="6" t="n"/>
     </row>
-    <row r="390" ht="15" customHeight="1">
-      <c r="A390" s="7" t="n"/>
-      <c r="B390" s="8" t="inlineStr">
-        <is>
-          <t>W ADIPOWER 26 SL BOA ( JP8385 )</t>
-        </is>
-      </c>
-      <c r="F390" s="9" t="n">
-        <v>349</v>
+    <row r="390" ht="18" customHeight="1">
+      <c r="A390" s="5" t="inlineStr">
+        <is>
+          <t>11A2</t>
+        </is>
+      </c>
+      <c r="B390" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F390" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G390" s="6" t="n"/>
       <c r="H390" s="6" t="n"/>
@@ -7198,11 +7204,11 @@
       <c r="A391" s="7" t="n"/>
       <c r="B391" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL ( JP8394 )</t>
+          <t>TOKYO W ( KK0036 )</t>
         </is>
       </c>
       <c r="F391" s="9" t="n">
-        <v>248</v>
+        <v>3490</v>
       </c>
       <c r="G391" s="6" t="n"/>
       <c r="H391" s="6" t="n"/>
@@ -7215,11 +7221,11 @@
       <c r="A392" s="7" t="n"/>
       <c r="B392" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL ( JP8395 )</t>
+          <t>TOKYO W ( KK0037 )</t>
         </is>
       </c>
       <c r="F392" s="9" t="n">
-        <v>79</v>
+        <v>1145</v>
       </c>
       <c r="G392" s="6" t="n"/>
       <c r="H392" s="6" t="n"/>
@@ -7232,11 +7238,11 @@
       <c r="A393" s="7" t="n"/>
       <c r="B393" s="8" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER ( JQ3560 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2523 )</t>
         </is>
       </c>
       <c r="F393" s="9" t="n">
-        <v>1203</v>
+        <v>310</v>
       </c>
       <c r="G393" s="6" t="n"/>
       <c r="H393" s="6" t="n"/>
@@ -7249,11 +7255,11 @@
       <c r="A394" s="7" t="n"/>
       <c r="B394" s="8" t="inlineStr">
         <is>
-          <t>W S2G 26 TEX ( JQ3563 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2524 )</t>
         </is>
       </c>
       <c r="F394" s="9" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G394" s="6" t="n"/>
       <c r="H394" s="6" t="n"/>
@@ -7266,11 +7272,11 @@
       <c r="A395" s="7" t="n"/>
       <c r="B395" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( JQ9311 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2572 )</t>
         </is>
       </c>
       <c r="F395" s="9" t="n">
-        <v>452</v>
+        <v>1597</v>
       </c>
       <c r="G395" s="6" t="n"/>
       <c r="H395" s="6" t="n"/>
@@ -7283,11 +7289,11 @@
       <c r="A396" s="7" t="n"/>
       <c r="B396" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 TEX ( JR1879 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2573 )</t>
         </is>
       </c>
       <c r="F396" s="9" t="n">
-        <v>189</v>
+        <v>1267</v>
       </c>
       <c r="G396" s="6" t="n"/>
       <c r="H396" s="6" t="n"/>
@@ -7300,11 +7306,11 @@
       <c r="A397" s="7" t="n"/>
       <c r="B397" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA ( JS4138 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2575 )</t>
         </is>
       </c>
       <c r="F397" s="9" t="n">
-        <v>377</v>
+        <v>3355</v>
       </c>
       <c r="G397" s="6" t="n"/>
       <c r="H397" s="6" t="n"/>
@@ -7317,11 +7323,11 @@
       <c r="A398" s="7" t="n"/>
       <c r="B398" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA ( JS4140 )</t>
+          <t>TAEKWONDO MEI ELITE W ( KK2576 )</t>
         </is>
       </c>
       <c r="F398" s="9" t="n">
-        <v>221</v>
+        <v>1632</v>
       </c>
       <c r="G398" s="6" t="n"/>
       <c r="H398" s="6" t="n"/>
@@ -7334,11 +7340,11 @@
       <c r="A399" s="7" t="n"/>
       <c r="B399" s="8" t="inlineStr">
         <is>
-          <t>S2G VENT ( KI1392 )</t>
+          <t>adidas TAEKWONDO W ( KK2705 )</t>
         </is>
       </c>
       <c r="F399" s="9" t="n">
-        <v>1107</v>
+        <v>2251</v>
       </c>
       <c r="G399" s="6" t="n"/>
       <c r="H399" s="6" t="n"/>
@@ -7347,15 +7353,21 @@
       <c r="K399" s="6" t="n"/>
       <c r="L399" s="6" t="n"/>
     </row>
-    <row r="400" ht="15" customHeight="1">
-      <c r="A400" s="7" t="n"/>
-      <c r="B400" s="8" t="inlineStr">
-        <is>
-          <t>S2G VENT ( KI8398 )</t>
-        </is>
-      </c>
-      <c r="F400" s="9" t="n">
-        <v>1203</v>
+    <row r="400" ht="18" customHeight="1">
+      <c r="A400" s="5" t="inlineStr">
+        <is>
+          <t>11B1</t>
+        </is>
+      </c>
+      <c r="B400" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F400" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G400" s="6" t="n"/>
       <c r="H400" s="6" t="n"/>
@@ -7368,11 +7380,11 @@
       <c r="A401" s="7" t="n"/>
       <c r="B401" s="8" t="inlineStr">
         <is>
-          <t>W S2G VENT ( KI8401 )</t>
+          <t>S2G 26 LEATHER ( HQ5054 )</t>
         </is>
       </c>
       <c r="F401" s="9" t="n">
-        <v>1200</v>
+        <v>2563</v>
       </c>
       <c r="G401" s="6" t="n"/>
       <c r="H401" s="6" t="n"/>
@@ -7385,11 +7397,11 @@
       <c r="A402" s="7" t="n"/>
       <c r="B402" s="8" t="inlineStr">
         <is>
-          <t>W S2G VENT ( KI8402 )</t>
+          <t>S2G 26 LEATHER ( JQ9311 )</t>
         </is>
       </c>
       <c r="F402" s="9" t="n">
-        <v>2584</v>
+        <v>1722</v>
       </c>
       <c r="G402" s="6" t="n"/>
       <c r="H402" s="6" t="n"/>
@@ -7402,11 +7414,11 @@
       <c r="A403" s="7" t="n"/>
       <c r="B403" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 ( KJ3010 )</t>
+          <t>TOKYO W ( KI3584 )</t>
         </is>
       </c>
       <c r="F403" s="9" t="n">
-        <v>1205</v>
+        <v>1274</v>
       </c>
       <c r="G403" s="6" t="n"/>
       <c r="H403" s="6" t="n"/>
@@ -7419,11 +7431,11 @@
       <c r="A404" s="7" t="n"/>
       <c r="B404" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 TEX ( KK0666 )</t>
+          <t>TOKYO W ( KJ7511 )</t>
         </is>
       </c>
       <c r="F404" s="9" t="n">
-        <v>127</v>
+        <v>1269</v>
       </c>
       <c r="G404" s="6" t="n"/>
       <c r="H404" s="6" t="n"/>
@@ -7436,11 +7448,11 @@
       <c r="A405" s="7" t="n"/>
       <c r="B405" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 ( KK2836 )</t>
+          <t>TOKYO W ( KJ7543 )</t>
         </is>
       </c>
       <c r="F405" s="9" t="n">
-        <v>275</v>
+        <v>563</v>
       </c>
       <c r="G405" s="6" t="n"/>
       <c r="H405" s="6" t="n"/>
@@ -7453,11 +7465,11 @@
       <c r="A406" s="7" t="n"/>
       <c r="B406" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL ( KK2838 )</t>
+          <t>TOKYO W ( KJ7551 )</t>
         </is>
       </c>
       <c r="F406" s="9" t="n">
-        <v>379</v>
+        <v>1008</v>
       </c>
       <c r="G406" s="6" t="n"/>
       <c r="H406" s="6" t="n"/>
@@ -7470,11 +7482,11 @@
       <c r="A407" s="7" t="n"/>
       <c r="B407" s="8" t="inlineStr">
         <is>
-          <t>ADIPOWER 26 SL BOA ( KK2839 )</t>
+          <t>TOKYO W ( KJ7552 )</t>
         </is>
       </c>
       <c r="F407" s="9" t="n">
-        <v>483</v>
+        <v>975</v>
       </c>
       <c r="G407" s="6" t="n"/>
       <c r="H407" s="6" t="n"/>
@@ -7487,11 +7499,11 @@
       <c r="A408" s="7" t="n"/>
       <c r="B408" s="8" t="inlineStr">
         <is>
-          <t>W ADIPOWER 26 SL BOA ( KK2843 )</t>
+          <t>TOKYO W ( KK0030 )</t>
         </is>
       </c>
       <c r="F408" s="9" t="n">
-        <v>346</v>
+        <v>493</v>
       </c>
       <c r="G408" s="6" t="n"/>
       <c r="H408" s="6" t="n"/>
@@ -7504,11 +7516,11 @@
       <c r="A409" s="7" t="n"/>
       <c r="B409" s="8" t="inlineStr">
         <is>
-          <t>W S2G 26 TEX ( KK2862 )</t>
+          <t>TOKYO W ( KK0031 )</t>
         </is>
       </c>
       <c r="F409" s="9" t="n">
-        <v>62</v>
+        <v>694</v>
       </c>
       <c r="G409" s="6" t="n"/>
       <c r="H409" s="6" t="n"/>
@@ -7521,11 +7533,11 @@
       <c r="A410" s="7" t="n"/>
       <c r="B410" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 TEX ( KK2872 )</t>
+          <t>TOKYO W ( KK0036 )</t>
         </is>
       </c>
       <c r="F410" s="9" t="n">
-        <v>249</v>
+        <v>472</v>
       </c>
       <c r="G410" s="6" t="n"/>
       <c r="H410" s="6" t="n"/>
@@ -7534,21 +7546,15 @@
       <c r="K410" s="6" t="n"/>
       <c r="L410" s="6" t="n"/>
     </row>
-    <row r="411" ht="18" customHeight="1">
-      <c r="A411" s="5" t="inlineStr">
-        <is>
-          <t>11A2</t>
-        </is>
-      </c>
-      <c r="B411" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F411" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="411" ht="15" customHeight="1">
+      <c r="A411" s="7" t="n"/>
+      <c r="B411" s="8" t="inlineStr">
+        <is>
+          <t>TOKYO W ( KK0037 )</t>
+        </is>
+      </c>
+      <c r="F411" s="9" t="n">
+        <v>2450</v>
       </c>
       <c r="G411" s="6" t="n"/>
       <c r="H411" s="6" t="n"/>
@@ -7561,11 +7567,11 @@
       <c r="A412" s="7" t="n"/>
       <c r="B412" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0036 )</t>
+          <t>W S2G 26 LEATHER ( KK2864 )</t>
         </is>
       </c>
       <c r="F412" s="9" t="n">
-        <v>3490</v>
+        <v>548</v>
       </c>
       <c r="G412" s="6" t="n"/>
       <c r="H412" s="6" t="n"/>
@@ -7578,11 +7584,11 @@
       <c r="A413" s="7" t="n"/>
       <c r="B413" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0037 )</t>
+          <t>W S2G 26 LEATHER ( KK2865 )</t>
         </is>
       </c>
       <c r="F413" s="9" t="n">
-        <v>1145</v>
+        <v>395</v>
       </c>
       <c r="G413" s="6" t="n"/>
       <c r="H413" s="6" t="n"/>
@@ -7595,11 +7601,11 @@
       <c r="A414" s="7" t="n"/>
       <c r="B414" s="8" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2523 )</t>
+          <t>S2G 26 LEATHER ( KK2871 )</t>
         </is>
       </c>
       <c r="F414" s="9" t="n">
-        <v>310</v>
+        <v>442</v>
       </c>
       <c r="G414" s="6" t="n"/>
       <c r="H414" s="6" t="n"/>
@@ -7612,11 +7618,11 @@
       <c r="A415" s="7" t="n"/>
       <c r="B415" s="8" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2524 )</t>
+          <t>TOKYO W ( LA3432 )</t>
         </is>
       </c>
       <c r="F415" s="9" t="n">
-        <v>100</v>
+        <v>664</v>
       </c>
       <c r="G415" s="6" t="n"/>
       <c r="H415" s="6" t="n"/>
@@ -7629,11 +7635,11 @@
       <c r="A416" s="7" t="n"/>
       <c r="B416" s="8" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2572 )</t>
+          <t>TOKYO W ( LA3433 )</t>
         </is>
       </c>
       <c r="F416" s="9" t="n">
-        <v>1597</v>
+        <v>5111</v>
       </c>
       <c r="G416" s="6" t="n"/>
       <c r="H416" s="6" t="n"/>
@@ -7642,15 +7648,21 @@
       <c r="K416" s="6" t="n"/>
       <c r="L416" s="6" t="n"/>
     </row>
-    <row r="417" ht="15" customHeight="1">
-      <c r="A417" s="7" t="n"/>
-      <c r="B417" s="8" t="inlineStr">
-        <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2573 )</t>
-        </is>
-      </c>
-      <c r="F417" s="9" t="n">
-        <v>1267</v>
+    <row r="417" ht="18" customHeight="1">
+      <c r="A417" s="5" t="inlineStr">
+        <is>
+          <t>11B2</t>
+        </is>
+      </c>
+      <c r="B417" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F417" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G417" s="6" t="n"/>
       <c r="H417" s="6" t="n"/>
@@ -7663,11 +7675,11 @@
       <c r="A418" s="7" t="n"/>
       <c r="B418" s="8" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2575 )</t>
+          <t>SAMBA J ( IF1944 )</t>
         </is>
       </c>
       <c r="F418" s="9" t="n">
-        <v>3355</v>
+        <v>3405</v>
       </c>
       <c r="G418" s="6" t="n"/>
       <c r="H418" s="6" t="n"/>
@@ -7680,11 +7692,11 @@
       <c r="A419" s="7" t="n"/>
       <c r="B419" s="8" t="inlineStr">
         <is>
-          <t>TAEKWONDO MEI ELITE W ( KK2576 )</t>
+          <t>SAMBA J ( IF1945 )</t>
         </is>
       </c>
       <c r="F419" s="9" t="n">
-        <v>1632</v>
+        <v>2673</v>
       </c>
       <c r="G419" s="6" t="n"/>
       <c r="H419" s="6" t="n"/>
@@ -7697,11 +7709,11 @@
       <c r="A420" s="7" t="n"/>
       <c r="B420" s="8" t="inlineStr">
         <is>
-          <t>adidas TAEKWONDO W ( KK2705 )</t>
+          <t>S2G 26 BOA ( JQ3463 )</t>
         </is>
       </c>
       <c r="F420" s="9" t="n">
-        <v>2251</v>
+        <v>3274</v>
       </c>
       <c r="G420" s="6" t="n"/>
       <c r="H420" s="6" t="n"/>
@@ -7710,21 +7722,15 @@
       <c r="K420" s="6" t="n"/>
       <c r="L420" s="6" t="n"/>
     </row>
-    <row r="421" ht="18" customHeight="1">
-      <c r="A421" s="5" t="inlineStr">
-        <is>
-          <t>11B1</t>
-        </is>
-      </c>
-      <c r="B421" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F421" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="421" ht="15" customHeight="1">
+      <c r="A421" s="7" t="n"/>
+      <c r="B421" s="8" t="inlineStr">
+        <is>
+          <t>W S2G 26 BOA ( KK2866 )</t>
+        </is>
+      </c>
+      <c r="F421" s="9" t="n">
+        <v>1084</v>
       </c>
       <c r="G421" s="6" t="n"/>
       <c r="H421" s="6" t="n"/>
@@ -7737,11 +7743,11 @@
       <c r="A422" s="7" t="n"/>
       <c r="B422" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( HQ5054 )</t>
+          <t>W S2G 26 BOA ( KK2867 )</t>
         </is>
       </c>
       <c r="F422" s="9" t="n">
-        <v>2563</v>
+        <v>62</v>
       </c>
       <c r="G422" s="6" t="n"/>
       <c r="H422" s="6" t="n"/>
@@ -7754,11 +7760,11 @@
       <c r="A423" s="7" t="n"/>
       <c r="B423" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( JQ9311 )</t>
+          <t>S2G 26 BOA ( KK2868 )</t>
         </is>
       </c>
       <c r="F423" s="9" t="n">
-        <v>1722</v>
+        <v>1989</v>
       </c>
       <c r="G423" s="6" t="n"/>
       <c r="H423" s="6" t="n"/>
@@ -7771,11 +7777,11 @@
       <c r="A424" s="7" t="n"/>
       <c r="B424" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KI3584 )</t>
+          <t>S2G 26 BOA ( KK2869 )</t>
         </is>
       </c>
       <c r="F424" s="9" t="n">
-        <v>1274</v>
+        <v>32</v>
       </c>
       <c r="G424" s="6" t="n"/>
       <c r="H424" s="6" t="n"/>
@@ -7788,11 +7794,11 @@
       <c r="A425" s="7" t="n"/>
       <c r="B425" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7511 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F425" s="9" t="n">
-        <v>1269</v>
+        <v>4929</v>
       </c>
       <c r="G425" s="6" t="n"/>
       <c r="H425" s="6" t="n"/>
@@ -7801,15 +7807,21 @@
       <c r="K425" s="6" t="n"/>
       <c r="L425" s="6" t="n"/>
     </row>
-    <row r="426" ht="15" customHeight="1">
-      <c r="A426" s="7" t="n"/>
-      <c r="B426" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( KJ7543 )</t>
-        </is>
-      </c>
-      <c r="F426" s="9" t="n">
-        <v>563</v>
+    <row r="426" ht="18" customHeight="1">
+      <c r="A426" s="5" t="inlineStr">
+        <is>
+          <t>11C</t>
+        </is>
+      </c>
+      <c r="B426" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F426" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G426" s="6" t="n"/>
       <c r="H426" s="6" t="n"/>
@@ -7822,11 +7834,11 @@
       <c r="A427" s="7" t="n"/>
       <c r="B427" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7551 )</t>
+          <t>TOKYO MJ W ( JR4790 )</t>
         </is>
       </c>
       <c r="F427" s="9" t="n">
-        <v>1008</v>
+        <v>4659</v>
       </c>
       <c r="G427" s="6" t="n"/>
       <c r="H427" s="6" t="n"/>
@@ -7839,11 +7851,11 @@
       <c r="A428" s="7" t="n"/>
       <c r="B428" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7552 )</t>
+          <t>ADISTAR XLG 2.0 J ( KZ6449 )</t>
         </is>
       </c>
       <c r="F428" s="9" t="n">
-        <v>975</v>
+        <v>1670</v>
       </c>
       <c r="G428" s="6" t="n"/>
       <c r="H428" s="6" t="n"/>
@@ -7856,11 +7868,11 @@
       <c r="A429" s="7" t="n"/>
       <c r="B429" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0030 )</t>
+          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
         </is>
       </c>
       <c r="F429" s="9" t="n">
-        <v>493</v>
+        <v>6999</v>
       </c>
       <c r="G429" s="6" t="n"/>
       <c r="H429" s="6" t="n"/>
@@ -7873,11 +7885,11 @@
       <c r="A430" s="7" t="n"/>
       <c r="B430" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0031 )</t>
+          <t>ADISTAR XLG 2.0 W ( KZ9163 )</t>
         </is>
       </c>
       <c r="F430" s="9" t="n">
-        <v>694</v>
+        <v>2034</v>
       </c>
       <c r="G430" s="6" t="n"/>
       <c r="H430" s="6" t="n"/>
@@ -7890,11 +7902,11 @@
       <c r="A431" s="7" t="n"/>
       <c r="B431" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KK0036 )</t>
+          <t>ADISTAR XLG 2.0 J ( LA1814 )</t>
         </is>
       </c>
       <c r="F431" s="9" t="n">
-        <v>472</v>
+        <v>4305</v>
       </c>
       <c r="G431" s="6" t="n"/>
       <c r="H431" s="6" t="n"/>
@@ -7903,32 +7915,28 @@
       <c r="K431" s="6" t="n"/>
       <c r="L431" s="6" t="n"/>
     </row>
-    <row r="432" ht="15" customHeight="1">
-      <c r="A432" s="7" t="n"/>
-      <c r="B432" s="8" t="inlineStr">
-        <is>
-          <t>TOKYO W ( KK0037 )</t>
-        </is>
-      </c>
-      <c r="F432" s="9" t="n">
-        <v>2450</v>
-      </c>
-      <c r="G432" s="6" t="n"/>
-      <c r="H432" s="6" t="n"/>
-      <c r="I432" s="6" t="n"/>
-      <c r="J432" s="6" t="n"/>
-      <c r="K432" s="6" t="n"/>
-      <c r="L432" s="6" t="n"/>
-    </row>
-    <row r="433" ht="15" customHeight="1">
-      <c r="A433" s="7" t="n"/>
-      <c r="B433" s="8" t="inlineStr">
-        <is>
-          <t>W S2G 26 LEATHER ( KK2864 )</t>
-        </is>
-      </c>
-      <c r="F433" s="9" t="n">
-        <v>548</v>
+    <row r="432">
+      <c r="A432" s="4" t="inlineStr">
+        <is>
+          <t>LEAN 12 （加12部）</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="18" customHeight="1">
+      <c r="A433" s="5" t="inlineStr">
+        <is>
+          <t>12A</t>
+        </is>
+      </c>
+      <c r="B433" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F433" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G433" s="6" t="n"/>
       <c r="H433" s="6" t="n"/>
@@ -7941,11 +7949,11 @@
       <c r="A434" s="7" t="n"/>
       <c r="B434" s="8" t="inlineStr">
         <is>
-          <t>W S2G 26 LEATHER ( KK2865 )</t>
+          <t>1609ER RS ( HQ5208 )</t>
         </is>
       </c>
       <c r="F434" s="9" t="n">
-        <v>395</v>
+        <v>3259</v>
       </c>
       <c r="G434" s="6" t="n"/>
       <c r="H434" s="6" t="n"/>
@@ -7958,11 +7966,11 @@
       <c r="A435" s="7" t="n"/>
       <c r="B435" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 LEATHER ( KK2871 )</t>
+          <t>TOKYO W ( JI0182 )</t>
         </is>
       </c>
       <c r="F435" s="9" t="n">
-        <v>442</v>
+        <v>310</v>
       </c>
       <c r="G435" s="6" t="n"/>
       <c r="H435" s="6" t="n"/>
@@ -7975,11 +7983,11 @@
       <c r="A436" s="7" t="n"/>
       <c r="B436" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( LA3432 )</t>
+          <t>1609ER RS ( KH9907 )</t>
         </is>
       </c>
       <c r="F436" s="9" t="n">
-        <v>664</v>
+        <v>3315</v>
       </c>
       <c r="G436" s="6" t="n"/>
       <c r="H436" s="6" t="n"/>
@@ -7992,11 +8000,11 @@
       <c r="A437" s="7" t="n"/>
       <c r="B437" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( LA3433 )</t>
+          <t>1609ER RS ( KH9908 )</t>
         </is>
       </c>
       <c r="F437" s="9" t="n">
-        <v>5111</v>
+        <v>800</v>
       </c>
       <c r="G437" s="6" t="n"/>
       <c r="H437" s="6" t="n"/>
@@ -8005,21 +8013,15 @@
       <c r="K437" s="6" t="n"/>
       <c r="L437" s="6" t="n"/>
     </row>
-    <row r="438" ht="18" customHeight="1">
-      <c r="A438" s="5" t="inlineStr">
-        <is>
-          <t>11B2</t>
-        </is>
-      </c>
-      <c r="B438" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F438" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
+    <row r="438" ht="15" customHeight="1">
+      <c r="A438" s="7" t="n"/>
+      <c r="B438" s="8" t="inlineStr">
+        <is>
+          <t>1609ER RS ( KH9909 )</t>
+        </is>
+      </c>
+      <c r="F438" s="9" t="n">
+        <v>215</v>
       </c>
       <c r="G438" s="6" t="n"/>
       <c r="H438" s="6" t="n"/>
@@ -8032,11 +8034,11 @@
       <c r="A439" s="7" t="n"/>
       <c r="B439" s="8" t="inlineStr">
         <is>
-          <t>SAMBA J ( IF1944 )</t>
+          <t>1609ER RS ( KI9853 )</t>
         </is>
       </c>
       <c r="F439" s="9" t="n">
-        <v>3405</v>
+        <v>371</v>
       </c>
       <c r="G439" s="6" t="n"/>
       <c r="H439" s="6" t="n"/>
@@ -8049,11 +8051,11 @@
       <c r="A440" s="7" t="n"/>
       <c r="B440" s="8" t="inlineStr">
         <is>
-          <t>SAMBA J ( IF1945 )</t>
+          <t>1609ER RS ( KI9855 )</t>
         </is>
       </c>
       <c r="F440" s="9" t="n">
-        <v>2673</v>
+        <v>886</v>
       </c>
       <c r="G440" s="6" t="n"/>
       <c r="H440" s="6" t="n"/>
@@ -8066,11 +8068,11 @@
       <c r="A441" s="7" t="n"/>
       <c r="B441" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 BOA ( JQ3463 )</t>
+          <t>1609ER RS ( KI9860 )</t>
         </is>
       </c>
       <c r="F441" s="9" t="n">
-        <v>3274</v>
+        <v>800</v>
       </c>
       <c r="G441" s="6" t="n"/>
       <c r="H441" s="6" t="n"/>
@@ -8083,11 +8085,11 @@
       <c r="A442" s="7" t="n"/>
       <c r="B442" s="8" t="inlineStr">
         <is>
-          <t>W S2G 26 BOA ( KK2866 )</t>
+          <t>TOKYO W ( KJ7510 )</t>
         </is>
       </c>
       <c r="F442" s="9" t="n">
-        <v>1084</v>
+        <v>6000</v>
       </c>
       <c r="G442" s="6" t="n"/>
       <c r="H442" s="6" t="n"/>
@@ -8096,15 +8098,21 @@
       <c r="K442" s="6" t="n"/>
       <c r="L442" s="6" t="n"/>
     </row>
-    <row r="443" ht="15" customHeight="1">
-      <c r="A443" s="7" t="n"/>
-      <c r="B443" s="8" t="inlineStr">
-        <is>
-          <t>W S2G 26 BOA ( KK2867 )</t>
-        </is>
-      </c>
-      <c r="F443" s="9" t="n">
-        <v>62</v>
+    <row r="443" ht="18" customHeight="1">
+      <c r="A443" s="5" t="inlineStr">
+        <is>
+          <t>12C</t>
+        </is>
+      </c>
+      <c r="B443" s="5" t="inlineStr">
+        <is>
+          <t>鞋型 + ART</t>
+        </is>
+      </c>
+      <c r="F443" s="5" t="inlineStr">
+        <is>
+          <t>訂單</t>
+        </is>
       </c>
       <c r="G443" s="6" t="n"/>
       <c r="H443" s="6" t="n"/>
@@ -8117,11 +8125,11 @@
       <c r="A444" s="7" t="n"/>
       <c r="B444" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 BOA ( KK2868 )</t>
+          <t>ADISTAR XLG 2.0 ( HQ7468 )</t>
         </is>
       </c>
       <c r="F444" s="9" t="n">
-        <v>1989</v>
+        <v>7697</v>
       </c>
       <c r="G444" s="6" t="n"/>
       <c r="H444" s="6" t="n"/>
@@ -8134,11 +8142,11 @@
       <c r="A445" s="7" t="n"/>
       <c r="B445" s="8" t="inlineStr">
         <is>
-          <t>S2G 26 BOA ( KK2869 )</t>
+          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
         </is>
       </c>
       <c r="F445" s="9" t="n">
-        <v>32</v>
+        <v>1467</v>
       </c>
       <c r="G445" s="6" t="n"/>
       <c r="H445" s="6" t="n"/>
@@ -8155,7 +8163,7 @@
         </is>
       </c>
       <c r="F446" s="9" t="n">
-        <v>4929</v>
+        <v>4359</v>
       </c>
       <c r="G446" s="6" t="n"/>
       <c r="H446" s="6" t="n"/>
@@ -8167,7 +8175,7 @@
     <row r="447" ht="18" customHeight="1">
       <c r="A447" s="5" t="inlineStr">
         <is>
-          <t>11C</t>
+          <t>12D</t>
         </is>
       </c>
       <c r="B447" s="5" t="inlineStr">
@@ -8191,11 +8199,11 @@
       <c r="A448" s="7" t="n"/>
       <c r="B448" s="8" t="inlineStr">
         <is>
-          <t>TOKYO MJ W ( JR4790 )</t>
+          <t>ADISTAR XLG 2.0 ( HQ7468 )</t>
         </is>
       </c>
       <c r="F448" s="9" t="n">
-        <v>4659</v>
+        <v>9667</v>
       </c>
       <c r="G448" s="6" t="n"/>
       <c r="H448" s="6" t="n"/>
@@ -8208,11 +8216,11 @@
       <c r="A449" s="7" t="n"/>
       <c r="B449" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KZ6449 )</t>
+          <t>ADISTAR XLG 2.0 J ( KZ6450 )</t>
         </is>
       </c>
       <c r="F449" s="9" t="n">
-        <v>4394</v>
+        <v>2586</v>
       </c>
       <c r="G449" s="6" t="n"/>
       <c r="H449" s="6" t="n"/>
@@ -8225,11 +8233,11 @@
       <c r="A450" s="7" t="n"/>
       <c r="B450" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
+          <t>ADISTAR XLG 2.0 W ( KZ9161 )</t>
         </is>
       </c>
       <c r="F450" s="9" t="n">
-        <v>6999</v>
+        <v>860</v>
       </c>
       <c r="G450" s="6" t="n"/>
       <c r="H450" s="6" t="n"/>
@@ -8246,7 +8254,7 @@
         </is>
       </c>
       <c r="F451" s="9" t="n">
-        <v>5267</v>
+        <v>1475</v>
       </c>
       <c r="G451" s="6" t="n"/>
       <c r="H451" s="6" t="n"/>
@@ -8259,11 +8267,11 @@
       <c r="A452" s="7" t="n"/>
       <c r="B452" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( LA1814 )</t>
+          <t>ADISTAR XLG 2.0 W ( KZ9344 )</t>
         </is>
       </c>
       <c r="F452" s="9" t="n">
-        <v>4305</v>
+        <v>5000</v>
       </c>
       <c r="G452" s="6" t="n"/>
       <c r="H452" s="6" t="n"/>
@@ -8272,1764 +8280,1230 @@
       <c r="K452" s="6" t="n"/>
       <c r="L452" s="6" t="n"/>
     </row>
-    <row r="453">
-      <c r="A453" s="4" t="inlineStr">
-        <is>
-          <t>LEAN 12 （加12部）</t>
-        </is>
-      </c>
-    </row>
-    <row r="454" ht="18" customHeight="1">
-      <c r="A454" s="5" t="inlineStr">
-        <is>
-          <t>12A</t>
-        </is>
-      </c>
-      <c r="B454" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F454" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
-      </c>
-      <c r="G454" s="6" t="n"/>
-      <c r="H454" s="6" t="n"/>
-      <c r="I454" s="6" t="n"/>
-      <c r="J454" s="6" t="n"/>
-      <c r="K454" s="6" t="n"/>
-      <c r="L454" s="6" t="n"/>
-    </row>
-    <row r="455" ht="15" customHeight="1">
-      <c r="A455" s="7" t="n"/>
-      <c r="B455" s="8" t="inlineStr">
-        <is>
-          <t>1609ER RS ( HQ5207 )</t>
-        </is>
-      </c>
-      <c r="F455" s="9" t="n">
-        <v>5921</v>
-      </c>
-      <c r="G455" s="6" t="n"/>
-      <c r="H455" s="6" t="n"/>
-      <c r="I455" s="6" t="n"/>
-      <c r="J455" s="6" t="n"/>
-      <c r="K455" s="6" t="n"/>
-      <c r="L455" s="6" t="n"/>
-    </row>
-    <row r="456" ht="15" customHeight="1">
+    <row r="454">
+      <c r="A454" s="10" t="inlineStr">
+        <is>
+          <t>OCS 固定單位（直接從廠務組織編制表讀入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" s="11" t="inlineStr">
+        <is>
+          <t>組底配套</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
       <c r="A456" s="7" t="n"/>
       <c r="B456" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( HQ5208 )</t>
-        </is>
-      </c>
-      <c r="F456" s="9" t="n">
-        <v>3259</v>
-      </c>
-      <c r="G456" s="6" t="n"/>
-      <c r="H456" s="6" t="n"/>
-      <c r="I456" s="6" t="n"/>
-      <c r="J456" s="6" t="n"/>
-      <c r="K456" s="6" t="n"/>
-      <c r="L456" s="6" t="n"/>
-    </row>
-    <row r="457" ht="15" customHeight="1">
+          <t>組底倉庫/ kho</t>
+        </is>
+      </c>
+      <c r="L456" s="9" t="n">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="457">
       <c r="A457" s="7" t="n"/>
       <c r="B457" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( HQ5209 )</t>
-        </is>
-      </c>
-      <c r="F457" s="9" t="n">
-        <v>4458</v>
-      </c>
-      <c r="G457" s="6" t="n"/>
-      <c r="H457" s="6" t="n"/>
-      <c r="I457" s="6" t="n"/>
-      <c r="J457" s="6" t="n"/>
-      <c r="K457" s="6" t="n"/>
-      <c r="L457" s="6" t="n"/>
-    </row>
-    <row r="458" ht="15" customHeight="1">
+          <t>整理組/Tổ chỉnh lý</t>
+        </is>
+      </c>
+      <c r="L457" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="458">
       <c r="A458" s="7" t="n"/>
       <c r="B458" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( JI0182 )</t>
-        </is>
-      </c>
-      <c r="F458" s="9" t="n">
-        <v>310</v>
-      </c>
-      <c r="G458" s="6" t="n"/>
-      <c r="H458" s="6" t="n"/>
-      <c r="I458" s="6" t="n"/>
-      <c r="J458" s="6" t="n"/>
-      <c r="K458" s="6" t="n"/>
-      <c r="L458" s="6" t="n"/>
-    </row>
-    <row r="459" ht="15" customHeight="1">
+          <t>外包組/Tổ GCN</t>
+        </is>
+      </c>
+      <c r="L458" s="9" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="459">
       <c r="A459" s="7" t="n"/>
       <c r="B459" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KH9907 )</t>
-        </is>
-      </c>
-      <c r="F459" s="9" t="n">
-        <v>5180</v>
-      </c>
-      <c r="G459" s="6" t="n"/>
-      <c r="H459" s="6" t="n"/>
-      <c r="I459" s="6" t="n"/>
-      <c r="J459" s="6" t="n"/>
-      <c r="K459" s="6" t="n"/>
-      <c r="L459" s="6" t="n"/>
-    </row>
-    <row r="460" ht="15" customHeight="1">
+          <t>打粗組/Tổ mài thô</t>
+        </is>
+      </c>
+      <c r="L459" s="9" t="n">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="460">
       <c r="A460" s="7" t="n"/>
       <c r="B460" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KH9908 )</t>
-        </is>
-      </c>
-      <c r="F460" s="9" t="n">
-        <v>1108</v>
-      </c>
-      <c r="G460" s="6" t="n"/>
-      <c r="H460" s="6" t="n"/>
-      <c r="I460" s="6" t="n"/>
-      <c r="J460" s="6" t="n"/>
-      <c r="K460" s="6" t="n"/>
-      <c r="L460" s="6" t="n"/>
-    </row>
-    <row r="461" ht="15" customHeight="1">
+          <t>UV/水洗組/Tổ rửa nước</t>
+        </is>
+      </c>
+      <c r="L460" s="9" t="n"/>
+    </row>
+    <row r="461">
       <c r="A461" s="7" t="n"/>
       <c r="B461" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KH9909 )</t>
-        </is>
-      </c>
-      <c r="F461" s="9" t="n">
-        <v>215</v>
-      </c>
-      <c r="G461" s="6" t="n"/>
-      <c r="H461" s="6" t="n"/>
-      <c r="I461" s="6" t="n"/>
-      <c r="J461" s="6" t="n"/>
-      <c r="K461" s="6" t="n"/>
-      <c r="L461" s="6" t="n"/>
-    </row>
-    <row r="462" ht="15" customHeight="1">
-      <c r="A462" s="7" t="n"/>
-      <c r="B462" s="8" t="inlineStr">
-        <is>
-          <t>1609ER RS ( KI9853 )</t>
-        </is>
-      </c>
-      <c r="F462" s="9" t="n">
-        <v>371</v>
-      </c>
-      <c r="G462" s="6" t="n"/>
-      <c r="H462" s="6" t="n"/>
-      <c r="I462" s="6" t="n"/>
-      <c r="J462" s="6" t="n"/>
-      <c r="K462" s="6" t="n"/>
-      <c r="L462" s="6" t="n"/>
-    </row>
-    <row r="463" ht="15" customHeight="1">
-      <c r="A463" s="7" t="n"/>
-      <c r="B463" s="8" t="inlineStr">
-        <is>
-          <t>1609ER RS ( KI9855 )</t>
-        </is>
-      </c>
-      <c r="F463" s="9" t="n">
-        <v>886</v>
-      </c>
-      <c r="G463" s="6" t="n"/>
-      <c r="H463" s="6" t="n"/>
-      <c r="I463" s="6" t="n"/>
-      <c r="J463" s="6" t="n"/>
-      <c r="K463" s="6" t="n"/>
-      <c r="L463" s="6" t="n"/>
-    </row>
-    <row r="464" ht="15" customHeight="1">
+          <t>Tổ phối liệu PXD/大底课配套组</t>
+        </is>
+      </c>
+      <c r="L461" s="9" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" s="11" t="inlineStr">
+        <is>
+          <t>自動化</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
       <c r="A464" s="7" t="n"/>
       <c r="B464" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KI9857 )</t>
-        </is>
-      </c>
-      <c r="F464" s="9" t="n">
-        <v>790</v>
-      </c>
-      <c r="G464" s="6" t="n"/>
-      <c r="H464" s="6" t="n"/>
-      <c r="I464" s="6" t="n"/>
-      <c r="J464" s="6" t="n"/>
-      <c r="K464" s="6" t="n"/>
-      <c r="L464" s="6" t="n"/>
-    </row>
-    <row r="465" ht="15" customHeight="1">
+          <t>同材共裁 1,2組</t>
+        </is>
+      </c>
+      <c r="L464" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="465">
       <c r="A465" s="7" t="n"/>
       <c r="B465" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KI9860 )</t>
-        </is>
-      </c>
-      <c r="F465" s="9" t="n">
-        <v>800</v>
-      </c>
-      <c r="G465" s="6" t="n"/>
-      <c r="H465" s="6" t="n"/>
-      <c r="I465" s="6" t="n"/>
-      <c r="J465" s="6" t="n"/>
-      <c r="K465" s="6" t="n"/>
-      <c r="L465" s="6" t="n"/>
-    </row>
-    <row r="466" ht="15" customHeight="1">
+          <t>自動裁斷1,2組</t>
+        </is>
+      </c>
+      <c r="L465" s="9" t="n">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="466">
       <c r="A466" s="7" t="n"/>
       <c r="B466" s="8" t="inlineStr">
         <is>
-          <t>1609ER RS ( KI9861 )</t>
-        </is>
-      </c>
-      <c r="F466" s="9" t="n">
-        <v>345</v>
-      </c>
-      <c r="G466" s="6" t="n"/>
-      <c r="H466" s="6" t="n"/>
-      <c r="I466" s="6" t="n"/>
-      <c r="J466" s="6" t="n"/>
-      <c r="K466" s="6" t="n"/>
-      <c r="L466" s="6" t="n"/>
-    </row>
-    <row r="467" ht="15" customHeight="1">
+          <t>鞋墊手工組</t>
+        </is>
+      </c>
+      <c r="L466" s="9" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="467">
       <c r="A467" s="7" t="n"/>
       <c r="B467" s="8" t="inlineStr">
         <is>
-          <t>TOKYO W ( KJ7510 )</t>
-        </is>
-      </c>
-      <c r="F467" s="9" t="n">
-        <v>6000</v>
-      </c>
-      <c r="G467" s="6" t="n"/>
-      <c r="H467" s="6" t="n"/>
-      <c r="I467" s="6" t="n"/>
-      <c r="J467" s="6" t="n"/>
-      <c r="K467" s="6" t="n"/>
-      <c r="L467" s="6" t="n"/>
-    </row>
-    <row r="468" ht="18" customHeight="1">
-      <c r="A468" s="5" t="inlineStr">
-        <is>
-          <t>12C</t>
-        </is>
-      </c>
-      <c r="B468" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F468" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
-      </c>
-      <c r="G468" s="6" t="n"/>
-      <c r="H468" s="6" t="n"/>
-      <c r="I468" s="6" t="n"/>
-      <c r="J468" s="6" t="n"/>
-      <c r="K468" s="6" t="n"/>
-      <c r="L468" s="6" t="n"/>
-    </row>
-    <row r="469" ht="15" customHeight="1">
-      <c r="A469" s="7" t="n"/>
-      <c r="B469" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 ( HQ7468 )</t>
-        </is>
-      </c>
-      <c r="F469" s="9" t="n">
-        <v>8981</v>
-      </c>
-      <c r="G469" s="6" t="n"/>
-      <c r="H469" s="6" t="n"/>
-      <c r="I469" s="6" t="n"/>
-      <c r="J469" s="6" t="n"/>
-      <c r="K469" s="6" t="n"/>
-      <c r="L469" s="6" t="n"/>
-    </row>
-    <row r="470" ht="15" customHeight="1">
-      <c r="A470" s="7" t="n"/>
-      <c r="B470" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7893 )</t>
-        </is>
-      </c>
-      <c r="F470" s="9" t="n">
-        <v>851</v>
-      </c>
-      <c r="G470" s="6" t="n"/>
-      <c r="H470" s="6" t="n"/>
-      <c r="I470" s="6" t="n"/>
-      <c r="J470" s="6" t="n"/>
-      <c r="K470" s="6" t="n"/>
-      <c r="L470" s="6" t="n"/>
-    </row>
-    <row r="471" ht="15" customHeight="1">
+          <t>自動化保全技術組/Bảo trì TĐH</t>
+        </is>
+      </c>
+      <c r="L467" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" s="7" t="n"/>
+      <c r="B468" s="8" t="inlineStr">
+        <is>
+          <t>自動化倉庫 Kho TĐH</t>
+        </is>
+      </c>
+      <c r="L468" s="9" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" s="11" t="inlineStr">
+        <is>
+          <t>電腦針車</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
       <c r="A471" s="7" t="n"/>
       <c r="B471" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KJ7895 )</t>
-        </is>
-      </c>
-      <c r="F471" s="9" t="n">
-        <v>4231</v>
-      </c>
-      <c r="G471" s="6" t="n"/>
-      <c r="H471" s="6" t="n"/>
-      <c r="I471" s="6" t="n"/>
-      <c r="J471" s="6" t="n"/>
-      <c r="K471" s="6" t="n"/>
-      <c r="L471" s="6" t="n"/>
-    </row>
-    <row r="472" ht="15" customHeight="1">
+          <t>折邊/TGB</t>
+        </is>
+      </c>
+      <c r="L471" s="9" t="n">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="472">
       <c r="A472" s="7" t="n"/>
       <c r="B472" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KZ6449 )</t>
-        </is>
-      </c>
-      <c r="F472" s="9" t="n">
-        <v>12202</v>
-      </c>
-      <c r="G472" s="6" t="n"/>
-      <c r="H472" s="6" t="n"/>
-      <c r="I472" s="6" t="n"/>
-      <c r="J472" s="6" t="n"/>
-      <c r="K472" s="6" t="n"/>
-      <c r="L472" s="6" t="n"/>
-    </row>
-    <row r="473" ht="15" customHeight="1">
+          <t>電腦針車/ MVT</t>
+        </is>
+      </c>
+      <c r="L472" s="9" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="473">
       <c r="A473" s="7" t="n"/>
       <c r="B473" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 ( KZ9155 )</t>
-        </is>
-      </c>
-      <c r="F473" s="9" t="n">
-        <v>5880</v>
-      </c>
-      <c r="G473" s="6" t="n"/>
-      <c r="H473" s="6" t="n"/>
-      <c r="I473" s="6" t="n"/>
-      <c r="J473" s="6" t="n"/>
-      <c r="K473" s="6" t="n"/>
-      <c r="L473" s="6" t="n"/>
-    </row>
-    <row r="474" ht="15" customHeight="1">
+          <t>電腦針車倉庫/ Kho MVT</t>
+        </is>
+      </c>
+      <c r="L473" s="9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="474">
       <c r="A474" s="7" t="n"/>
       <c r="B474" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( LA1814 )</t>
-        </is>
-      </c>
-      <c r="F474" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G474" s="6" t="n"/>
-      <c r="H474" s="6" t="n"/>
-      <c r="I474" s="6" t="n"/>
-      <c r="J474" s="6" t="n"/>
-      <c r="K474" s="6" t="n"/>
-      <c r="L474" s="6" t="n"/>
-    </row>
-    <row r="475" ht="18" customHeight="1">
-      <c r="A475" s="5" t="inlineStr">
-        <is>
-          <t>12D</t>
-        </is>
-      </c>
-      <c r="B475" s="5" t="inlineStr">
-        <is>
-          <t>鞋型 + ART</t>
-        </is>
-      </c>
-      <c r="F475" s="5" t="inlineStr">
-        <is>
-          <t>訂單</t>
-        </is>
-      </c>
-      <c r="G475" s="6" t="n"/>
-      <c r="H475" s="6" t="n"/>
-      <c r="I475" s="6" t="n"/>
-      <c r="J475" s="6" t="n"/>
-      <c r="K475" s="6" t="n"/>
-      <c r="L475" s="6" t="n"/>
-    </row>
-    <row r="476" ht="15" customHeight="1">
-      <c r="A476" s="7" t="n"/>
-      <c r="B476" s="8" t="inlineStr">
-        <is>
-          <t>ADISTAR XLG 2.0 ( HQ7468 )</t>
-        </is>
-      </c>
-      <c r="F476" s="9" t="n">
-        <v>14417</v>
-      </c>
-      <c r="G476" s="6" t="n"/>
-      <c r="H476" s="6" t="n"/>
-      <c r="I476" s="6" t="n"/>
-      <c r="J476" s="6" t="n"/>
-      <c r="K476" s="6" t="n"/>
-      <c r="L476" s="6" t="n"/>
-    </row>
-    <row r="477" ht="15" customHeight="1">
+          <t>電腦針車保全技術組/ Bảo trì MVT</t>
+        </is>
+      </c>
+      <c r="L474" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" s="11" t="inlineStr">
+        <is>
+          <t>印刷</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
       <c r="A477" s="7" t="n"/>
       <c r="B477" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KJ7893 )</t>
-        </is>
-      </c>
-      <c r="F477" s="9" t="n">
-        <v>3696</v>
-      </c>
-      <c r="G477" s="6" t="n"/>
-      <c r="H477" s="6" t="n"/>
-      <c r="I477" s="6" t="n"/>
-      <c r="J477" s="6" t="n"/>
-      <c r="K477" s="6" t="n"/>
-      <c r="L477" s="6" t="n"/>
-    </row>
-    <row r="478" ht="15" customHeight="1">
+          <t>高周波/ In cao tần</t>
+        </is>
+      </c>
+      <c r="L477" s="9" t="n">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="478">
       <c r="A478" s="7" t="n"/>
       <c r="B478" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( KZ6450 )</t>
-        </is>
-      </c>
-      <c r="F478" s="9" t="n">
-        <v>2586</v>
-      </c>
-      <c r="G478" s="6" t="n"/>
-      <c r="H478" s="6" t="n"/>
-      <c r="I478" s="6" t="n"/>
-      <c r="J478" s="6" t="n"/>
-      <c r="K478" s="6" t="n"/>
-      <c r="L478" s="6" t="n"/>
-    </row>
-    <row r="479" ht="15" customHeight="1">
+          <t>印刷組/ In Dầu</t>
+        </is>
+      </c>
+      <c r="L478" s="9" t="n">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="479">
       <c r="A479" s="7" t="n"/>
       <c r="B479" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KZ9161 )</t>
-        </is>
-      </c>
-      <c r="F479" s="9" t="n">
-        <v>1435</v>
-      </c>
-      <c r="G479" s="6" t="n"/>
-      <c r="H479" s="6" t="n"/>
-      <c r="I479" s="6" t="n"/>
-      <c r="J479" s="6" t="n"/>
-      <c r="K479" s="6" t="n"/>
-      <c r="L479" s="6" t="n"/>
-    </row>
-    <row r="480" ht="15" customHeight="1">
+          <t>配套組/ Tổ phối đôi</t>
+        </is>
+      </c>
+      <c r="L479" s="9" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="480">
       <c r="A480" s="7" t="n"/>
       <c r="B480" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KZ9162 )</t>
-        </is>
-      </c>
-      <c r="F480" s="9" t="n">
-        <v>4799</v>
-      </c>
-      <c r="G480" s="6" t="n"/>
-      <c r="H480" s="6" t="n"/>
-      <c r="I480" s="6" t="n"/>
-      <c r="J480" s="6" t="n"/>
-      <c r="K480" s="6" t="n"/>
-      <c r="L480" s="6" t="n"/>
-    </row>
-    <row r="481" ht="15" customHeight="1">
+          <t>網板組/ Khuôn In lụa</t>
+        </is>
+      </c>
+      <c r="L480" s="9" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="481">
       <c r="A481" s="7" t="n"/>
       <c r="B481" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KZ9163 )</t>
-        </is>
-      </c>
-      <c r="F481" s="9" t="n">
-        <v>2334</v>
-      </c>
-      <c r="G481" s="6" t="n"/>
-      <c r="H481" s="6" t="n"/>
-      <c r="I481" s="6" t="n"/>
-      <c r="J481" s="6" t="n"/>
-      <c r="K481" s="6" t="n"/>
-      <c r="L481" s="6" t="n"/>
-    </row>
-    <row r="482" ht="15" customHeight="1">
+          <t>印刷房/ Phòng In dầu</t>
+        </is>
+      </c>
+      <c r="L481" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="482">
       <c r="A482" s="7" t="n"/>
       <c r="B482" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 W ( KZ9344 )</t>
-        </is>
-      </c>
-      <c r="F482" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G482" s="6" t="n"/>
-      <c r="H482" s="6" t="n"/>
-      <c r="I482" s="6" t="n"/>
-      <c r="J482" s="6" t="n"/>
-      <c r="K482" s="6" t="n"/>
-      <c r="L482" s="6" t="n"/>
-    </row>
-    <row r="483" ht="15" customHeight="1">
+          <t>印刷開發/ Khai phát ISD</t>
+        </is>
+      </c>
+      <c r="L482" s="9" t="n">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="483">
       <c r="A483" s="7" t="n"/>
       <c r="B483" s="8" t="inlineStr">
         <is>
-          <t>ADISTAR XLG 2.0 J ( LA1814 )</t>
-        </is>
-      </c>
-      <c r="F483" s="9" t="n">
-        <v>5000</v>
-      </c>
-      <c r="G483" s="6" t="n"/>
-      <c r="H483" s="6" t="n"/>
-      <c r="I483" s="6" t="n"/>
-      <c r="J483" s="6" t="n"/>
-      <c r="K483" s="6" t="n"/>
-      <c r="L483" s="6" t="n"/>
+          <t>加工組/ Gia công ngoài</t>
+        </is>
+      </c>
+      <c r="L483" s="9" t="n">
+        <v>15</v>
+      </c>
     </row>
     <row r="485">
-      <c r="A485" s="10" t="inlineStr">
-        <is>
-          <t>OCS 固定單位（直接從廠務組織編制表讀入）</t>
+      <c r="A485" s="11" t="inlineStr">
+        <is>
+          <t>設備工程</t>
         </is>
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="11" t="inlineStr">
-        <is>
-          <t>組底配套</t>
-        </is>
+      <c r="A486" s="7" t="n"/>
+      <c r="B486" s="8" t="inlineStr">
+        <is>
+          <t>保全/ Bảo trì</t>
+        </is>
+      </c>
+      <c r="L486" s="9" t="n">
+        <v>56</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" s="7" t="n"/>
       <c r="B487" s="8" t="inlineStr">
         <is>
-          <t>組底倉庫/ kho</t>
+          <t>西工/bảo trì RB</t>
         </is>
       </c>
       <c r="L487" s="9" t="n">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" s="7" t="n"/>
-      <c r="B488" s="8" t="inlineStr">
-        <is>
-          <t>整理組/Tổ chỉnh lý</t>
-        </is>
-      </c>
-      <c r="L488" s="9" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="7" t="n"/>
-      <c r="B489" s="8" t="inlineStr">
-        <is>
-          <t>外包組/Tổ GCN</t>
-        </is>
-      </c>
-      <c r="L489" s="9" t="n">
+      <c r="A489" s="10" t="inlineStr">
+        <is>
+          <t>RB / QC（直接從廠務組織編制表讀入）</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" s="11" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="18" customHeight="1">
+      <c r="A491" s="3" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="K491" s="3" t="inlineStr">
+        <is>
+          <t>上月人數</t>
+        </is>
+      </c>
+      <c r="L491" s="3" t="inlineStr">
+        <is>
+          <t>本月人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" s="8" t="inlineStr">
+        <is>
+          <t>預備組RB/tổ dự bị</t>
+        </is>
+      </c>
+      <c r="K492" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="L492" s="9" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" s="8" t="inlineStr">
+        <is>
+          <t>RB生管/ QLSX</t>
+        </is>
+      </c>
+      <c r="K493" s="9" t="n">
         <v>4</v>
       </c>
-    </row>
-    <row r="490">
-      <c r="A490" s="7" t="n"/>
-      <c r="B490" s="8" t="inlineStr">
-        <is>
-          <t>打粗組/Tổ mài thô</t>
-        </is>
-      </c>
-      <c r="L490" s="9" t="n">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" s="7" t="n"/>
-      <c r="B491" s="8" t="inlineStr">
-        <is>
-          <t>UV/水洗組/Tổ rửa nước</t>
-        </is>
-      </c>
-      <c r="L491" s="9" t="n"/>
-    </row>
-    <row r="492">
-      <c r="A492" s="7" t="n"/>
-      <c r="B492" s="8" t="inlineStr">
-        <is>
-          <t>Tổ phối liệu PXD/大底课配套组</t>
-        </is>
-      </c>
-      <c r="L492" s="9" t="n">
-        <v>7</v>
+      <c r="L493" s="9" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="11" t="inlineStr">
-        <is>
-          <t>自動化</t>
-        </is>
+      <c r="A494" s="8" t="inlineStr">
+        <is>
+          <t>RB倉庫生管</t>
+        </is>
+      </c>
+      <c r="K494" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="L494" s="9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="495">
-      <c r="A495" s="7" t="n"/>
-      <c r="B495" s="8" t="inlineStr">
-        <is>
-          <t>同材共裁 1,2組</t>
-        </is>
+      <c r="A495" s="8" t="inlineStr">
+        <is>
+          <t>出半成品</t>
+        </is>
+      </c>
+      <c r="K495" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="L495" s="9" t="n">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
-      <c r="A496" s="7" t="n"/>
-      <c r="B496" s="8" t="inlineStr">
-        <is>
-          <t>自動裁斷1,2組</t>
-        </is>
+      <c r="A496" s="8" t="inlineStr">
+        <is>
+          <t>模具/ khuôn RB</t>
+        </is>
+      </c>
+      <c r="K496" s="9" t="n">
+        <v>6</v>
       </c>
       <c r="L496" s="9" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
     </row>
     <row r="497">
-      <c r="A497" s="7" t="n"/>
-      <c r="B497" s="8" t="inlineStr">
-        <is>
-          <t>鞋墊手工組</t>
-        </is>
+      <c r="A497" s="8" t="inlineStr">
+        <is>
+          <t>密練組A</t>
+        </is>
+      </c>
+      <c r="K497" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="L497" s="9" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
     </row>
     <row r="498">
-      <c r="A498" s="7" t="n"/>
-      <c r="B498" s="8" t="inlineStr">
-        <is>
-          <t>自動化保全技術組/Bảo trì TĐH</t>
-        </is>
+      <c r="A498" s="8" t="inlineStr">
+        <is>
+          <t>密練組B</t>
+        </is>
+      </c>
+      <c r="K498" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="L498" s="9" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="499">
-      <c r="A499" s="7" t="n"/>
-      <c r="B499" s="8" t="inlineStr">
-        <is>
-          <t>自動化倉庫 Kho TĐH</t>
-        </is>
+      <c r="A499" s="8" t="inlineStr">
+        <is>
+          <t>混A組/ Tổ trộn A</t>
+        </is>
+      </c>
+      <c r="K499" s="9" t="n">
+        <v>15</v>
       </c>
       <c r="L499" s="9" t="n">
-        <v>12</v>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" s="8" t="inlineStr">
+        <is>
+          <t>混B組/ Tổ trộn B</t>
+        </is>
+      </c>
+      <c r="K500" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L500" s="9" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="501">
-      <c r="A501" s="11" t="inlineStr">
-        <is>
-          <t>電腦針車</t>
-        </is>
+      <c r="A501" s="8" t="inlineStr">
+        <is>
+          <t>混C組/ Tổ trộn C</t>
+        </is>
+      </c>
+      <c r="K501" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="L501" s="9" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="502">
-      <c r="A502" s="7" t="n"/>
-      <c r="B502" s="8" t="inlineStr">
-        <is>
-          <t>折邊/TGB</t>
-        </is>
+      <c r="A502" s="8" t="inlineStr">
+        <is>
+          <t>熱A組/ Ép nhiệt A</t>
+        </is>
+      </c>
+      <c r="K502" s="9" t="n">
+        <v>60</v>
       </c>
       <c r="L502" s="9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" s="8" t="inlineStr">
+        <is>
+          <t>熱B組/ Ép nhiệt B</t>
+        </is>
+      </c>
+      <c r="K503" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L503" s="9" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" s="8" t="inlineStr">
+        <is>
+          <t>熱C組/ Ép nhiệt C</t>
+        </is>
+      </c>
+      <c r="K504" s="9" t="n">
+        <v>60</v>
+      </c>
+      <c r="L504" s="9" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" s="8" t="inlineStr">
+        <is>
+          <t>整理A組/ Chỉnh lý A</t>
+        </is>
+      </c>
+      <c r="K505" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L505" s="9" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" s="8" t="inlineStr">
+        <is>
+          <t>整理B組/ Chỉnh lý B</t>
+        </is>
+      </c>
+      <c r="K506" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L506" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" s="8" t="inlineStr">
+        <is>
+          <t>整理C組/ Chỉnh lý C</t>
+        </is>
+      </c>
+      <c r="K507" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="L507" s="9" t="n">
         <v>23</v>
       </c>
     </row>
-    <row r="503">
-      <c r="A503" s="7" t="n"/>
-      <c r="B503" s="8" t="inlineStr">
-        <is>
-          <t>電腦針車/ MVT</t>
-        </is>
-      </c>
-      <c r="L503" s="9" t="n">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="504">
-      <c r="A504" s="7" t="n"/>
-      <c r="B504" s="8" t="inlineStr">
-        <is>
-          <t>電腦針車倉庫/ Kho MVT</t>
-        </is>
-      </c>
-      <c r="L504" s="9" t="n">
+    <row r="508">
+      <c r="A508" s="8" t="inlineStr">
+        <is>
+          <t>技術組 kỹ thuật RB</t>
+        </is>
+      </c>
+      <c r="K508" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="L508" s="9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="8" t="inlineStr">
+        <is>
+          <t>硫化組/Tổ lưu biến</t>
+        </is>
+      </c>
+      <c r="K509" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="L509" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="11" t="inlineStr">
+        <is>
+          <t>QC</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="18" customHeight="1">
+      <c r="A512" s="3" t="inlineStr">
+        <is>
+          <t>單位</t>
+        </is>
+      </c>
+      <c r="K512" s="3" t="inlineStr">
+        <is>
+          <t>上月人數</t>
+        </is>
+      </c>
+      <c r="L512" s="3" t="inlineStr">
+        <is>
+          <t>本月人數</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="8" t="inlineStr">
+        <is>
+          <t>OCPT</t>
+        </is>
+      </c>
+      <c r="K513" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L513" s="9" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="8" t="inlineStr">
+        <is>
+          <t>實驗室</t>
+        </is>
+      </c>
+      <c r="K514" s="9" t="n">
         <v>18</v>
       </c>
-    </row>
-    <row r="505">
-      <c r="A505" s="7" t="n"/>
-      <c r="B505" s="8" t="inlineStr">
-        <is>
-          <t>電腦針車保全技術組/ Bảo trì MVT</t>
-        </is>
-      </c>
-      <c r="L505" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="507">
-      <c r="A507" s="11" t="inlineStr">
-        <is>
-          <t>印刷</t>
-        </is>
-      </c>
-    </row>
-    <row r="508">
-      <c r="A508" s="7" t="n"/>
-      <c r="B508" s="8" t="inlineStr">
-        <is>
-          <t>高周波/ In cao tần</t>
-        </is>
-      </c>
-      <c r="L508" s="9" t="n">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="509">
-      <c r="A509" s="7" t="n"/>
-      <c r="B509" s="8" t="inlineStr">
-        <is>
-          <t>印刷組/ In Dầu</t>
-        </is>
-      </c>
-      <c r="L509" s="9" t="n">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="510">
-      <c r="A510" s="7" t="n"/>
-      <c r="B510" s="8" t="inlineStr">
-        <is>
-          <t>配套組/ Tổ phối đôi</t>
-        </is>
-      </c>
-      <c r="L510" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="511">
-      <c r="A511" s="7" t="n"/>
-      <c r="B511" s="8" t="inlineStr">
-        <is>
-          <t>網板組/ Khuôn In lụa</t>
-        </is>
-      </c>
-      <c r="L511" s="9" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="512">
-      <c r="A512" s="7" t="n"/>
-      <c r="B512" s="8" t="inlineStr">
-        <is>
-          <t>印刷房/ Phòng In dầu</t>
-        </is>
-      </c>
-      <c r="L512" s="9" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="513">
-      <c r="A513" s="7" t="n"/>
-      <c r="B513" s="8" t="inlineStr">
-        <is>
-          <t>印刷開發/ Khai phát ISD</t>
-        </is>
-      </c>
-      <c r="L513" s="9" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="514">
-      <c r="A514" s="7" t="n"/>
-      <c r="B514" s="8" t="inlineStr">
-        <is>
-          <t>加工組/ Gia công ngoài</t>
-        </is>
-      </c>
       <c r="L514" s="9" t="n">
-        <v>15</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="8" t="inlineStr">
+        <is>
+          <t>课部助理</t>
+        </is>
+      </c>
+      <c r="K515" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L515" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="516">
-      <c r="A516" s="11" t="inlineStr">
-        <is>
-          <t>設備工程</t>
-        </is>
+      <c r="A516" s="8" t="inlineStr">
+        <is>
+          <t>藺榮華的翻译/协理的助理</t>
+        </is>
+      </c>
+      <c r="K516" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L516" s="9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="517">
-      <c r="A517" s="7" t="n"/>
-      <c r="B517" s="8" t="inlineStr">
-        <is>
-          <t>保全/ Bảo trì</t>
-        </is>
+      <c r="A517" s="8" t="inlineStr">
+        <is>
+          <t>QA</t>
+        </is>
+      </c>
+      <c r="K517" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="L517" s="9" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="518">
-      <c r="A518" s="7" t="n"/>
-      <c r="B518" s="8" t="inlineStr">
-        <is>
-          <t>西工/bảo trì RB</t>
-        </is>
+      <c r="A518" s="8" t="inlineStr">
+        <is>
+          <t>樣品室 QC</t>
+        </is>
+      </c>
+      <c r="K518" s="9" t="n">
+        <v>4</v>
       </c>
       <c r="L518" s="9" t="n">
-        <v>6</v>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="8" t="inlineStr">
+        <is>
+          <t>开发 QA</t>
+        </is>
+      </c>
+      <c r="K519" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="L519" s="9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="520">
-      <c r="A520" s="10" t="inlineStr">
-        <is>
-          <t>RB / QC（直接從廠務組織編制表讀入）</t>
-        </is>
+      <c r="A520" s="8" t="inlineStr">
+        <is>
+          <t>檢驗真皮組</t>
+        </is>
+      </c>
+      <c r="K520" s="9" t="n">
+        <v>48</v>
+      </c>
+      <c r="L520" s="9" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="521">
-      <c r="A521" s="11" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-    </row>
-    <row r="522" ht="18" customHeight="1">
-      <c r="A522" s="3" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
-      </c>
-      <c r="K522" s="3" t="inlineStr">
-        <is>
-          <t>上月人數</t>
-        </is>
-      </c>
-      <c r="L522" s="3" t="inlineStr">
-        <is>
-          <t>本月人數</t>
-        </is>
+      <c r="A521" s="8" t="inlineStr">
+        <is>
+          <t>檢驗副料組</t>
+        </is>
+      </c>
+      <c r="K521" s="9" t="n">
+        <v>29</v>
+      </c>
+      <c r="L521" s="9" t="n">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="8" t="inlineStr">
+        <is>
+          <t>收料組</t>
+        </is>
+      </c>
+      <c r="K522" s="9" t="n">
+        <v>18</v>
+      </c>
+      <c r="L522" s="9" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="8" t="inlineStr">
         <is>
-          <t>預備組RB/tổ dự bị</t>
+          <t>底料檢驗組</t>
         </is>
       </c>
       <c r="K523" s="9" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L523" s="9" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="8" t="inlineStr">
         <is>
-          <t>RB生管/ QLSX</t>
+          <t>EVC 檢驗</t>
         </is>
       </c>
       <c r="K524" s="9" t="n">
         <v>4</v>
       </c>
       <c r="L524" s="9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="8" t="inlineStr">
         <is>
-          <t>RB倉庫生管</t>
+          <t>T2 中底廠商</t>
         </is>
       </c>
       <c r="K525" s="9" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L525" s="9" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="8" t="inlineStr">
         <is>
-          <t>出半成品</t>
+          <t>T3 外包底料</t>
         </is>
       </c>
       <c r="K526" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L526" s="9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="8" t="inlineStr">
         <is>
-          <t>模具/ khuôn RB</t>
+          <t>印刷高周波QC</t>
         </is>
       </c>
       <c r="K527" s="9" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L527" s="9" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="8" t="inlineStr">
         <is>
-          <t>密練組A</t>
+          <t>外包QC部件</t>
         </is>
       </c>
       <c r="K528" s="9" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="L528" s="9" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="8" t="inlineStr">
         <is>
-          <t>密練組B</t>
+          <t>QCRB</t>
         </is>
       </c>
       <c r="K529" s="9" t="n">
-        <v>8</v>
+        <v>49</v>
       </c>
       <c r="L529" s="9" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="8" t="inlineStr">
         <is>
-          <t>混A組/ Tổ trộn A</t>
+          <t>外包 RB QC</t>
         </is>
       </c>
       <c r="K530" s="9" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L530" s="9" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="8" t="inlineStr">
         <is>
-          <t>混B組/ Tổ trộn B</t>
+          <t>自動化中心/同材共裁</t>
         </is>
       </c>
       <c r="K531" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L531" s="9" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" s="8" t="inlineStr">
         <is>
-          <t>混C組/ Tổ trộn C</t>
+          <t>電腦針車 QC</t>
         </is>
       </c>
       <c r="K532" s="9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L532" s="9" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" s="8" t="inlineStr">
         <is>
-          <t>熱A組/ Ép nhiệt A</t>
+          <t>QC 貼底課</t>
         </is>
       </c>
       <c r="K533" s="9" t="n">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="L533" s="9" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" s="8" t="inlineStr">
         <is>
-          <t>熱B組/ Ép nhiệt B</t>
+          <t>外包QC貼底</t>
         </is>
       </c>
       <c r="K534" s="9" t="n">
-        <v>60</v>
+        <v>9</v>
       </c>
       <c r="L534" s="9" t="n">
-        <v>42</v>
+        <v>4</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" s="8" t="inlineStr">
         <is>
-          <t>熱C組/ Ép nhiệt C</t>
+          <t>QC 1</t>
         </is>
       </c>
       <c r="K535" s="9" t="n">
-        <v>60</v>
+        <v>13</v>
       </c>
       <c r="L535" s="9" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" s="8" t="inlineStr">
         <is>
-          <t>整理A組/ Chỉnh lý A</t>
+          <t>QC 2</t>
         </is>
       </c>
       <c r="K536" s="9" t="n">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="L536" s="9" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" s="8" t="inlineStr">
         <is>
-          <t>整理B組/ Chỉnh lý B</t>
+          <t>QC 3</t>
         </is>
       </c>
       <c r="K537" s="9" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L537" s="9" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" s="8" t="inlineStr">
         <is>
-          <t>整理C組/ Chỉnh lý C</t>
+          <t>QC 5</t>
         </is>
       </c>
       <c r="K538" s="9" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="L538" s="9" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" s="8" t="inlineStr">
         <is>
-          <t>技術組 kỹ thuật RB</t>
+          <t>QC 6</t>
         </is>
       </c>
       <c r="K539" s="9" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L539" s="9" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" s="8" t="inlineStr">
         <is>
-          <t>硫化組/Tổ lưu biến</t>
+          <t>QC 7</t>
         </is>
       </c>
       <c r="K540" s="9" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L540" s="9" t="n">
-        <v>3</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="8" t="inlineStr">
+        <is>
+          <t>QC 8</t>
+        </is>
+      </c>
+      <c r="K541" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L541" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="542">
-      <c r="A542" s="11" t="inlineStr">
-        <is>
-          <t>QC</t>
-        </is>
-      </c>
-    </row>
-    <row r="543" ht="18" customHeight="1">
-      <c r="A543" s="3" t="inlineStr">
-        <is>
-          <t>單位</t>
-        </is>
-      </c>
-      <c r="K543" s="3" t="inlineStr">
-        <is>
-          <t>上月人數</t>
-        </is>
-      </c>
-      <c r="L543" s="3" t="inlineStr">
-        <is>
-          <t>本月人數</t>
-        </is>
+      <c r="A542" s="8" t="inlineStr">
+        <is>
+          <t>QC 9</t>
+        </is>
+      </c>
+      <c r="K542" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L542" s="9" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="8" t="inlineStr">
+        <is>
+          <t>QC 10</t>
+        </is>
+      </c>
+      <c r="K543" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="L543" s="9" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" s="8" t="inlineStr">
         <is>
-          <t>OCPT</t>
+          <t>QC 11</t>
         </is>
       </c>
       <c r="K544" s="9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L544" s="9" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" s="8" t="inlineStr">
         <is>
-          <t>實驗室</t>
+          <t>QC 12</t>
         </is>
       </c>
       <c r="K545" s="9" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="L545" s="9" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" s="8" t="inlineStr">
         <is>
-          <t>课部助理</t>
+          <t>QC YH</t>
         </is>
       </c>
       <c r="K546" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L546" s="9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" s="8" t="inlineStr">
         <is>
-          <t>藺榮華的翻译/协理的助理</t>
+          <t>QC YH（针车鞋面）</t>
         </is>
       </c>
       <c r="K547" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L547" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" s="8" t="inlineStr">
         <is>
-          <t>QA</t>
+          <t>美城QC (成型）</t>
         </is>
       </c>
       <c r="K548" s="9" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L548" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" s="8" t="inlineStr">
         <is>
-          <t>樣品室 QC</t>
+          <t>验货员</t>
         </is>
       </c>
       <c r="K549" s="9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L549" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="550">
       <c r="A550" s="8" t="inlineStr">
         <is>
-          <t>开发 QA</t>
+          <t>包裝員</t>
         </is>
       </c>
       <c r="K550" s="9" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="L550" s="9" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" s="8" t="inlineStr">
         <is>
-          <t>檢驗真皮組</t>
+          <t>验货员（专员）</t>
         </is>
       </c>
       <c r="K551" s="9" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L551" s="9" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
     </row>
     <row r="552">
       <c r="A552" s="8" t="inlineStr">
         <is>
-          <t>檢驗副料組</t>
+          <t>美兴QC（鞋面）</t>
         </is>
       </c>
       <c r="K552" s="9" t="n">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="L552" s="9" t="n">
-        <v>28</v>
+        <v>10</v>
       </c>
     </row>
     <row r="553">
       <c r="A553" s="8" t="inlineStr">
         <is>
-          <t>收料組</t>
+          <t>JIATAI（鞋面）</t>
         </is>
       </c>
       <c r="K553" s="9" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="L553" s="9" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
       <c r="A554" s="8" t="inlineStr">
         <is>
-          <t>底料檢驗組</t>
+          <t>美君（鞋面）</t>
         </is>
       </c>
       <c r="K554" s="9" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L554" s="9" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555">
       <c r="A555" s="8" t="inlineStr">
         <is>
-          <t>EVC 檢驗</t>
+          <t>品包1組 1,2,3,5)</t>
         </is>
       </c>
       <c r="K555" s="9" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
       <c r="L555" s="9" t="n">
-        <v>4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" s="8" t="inlineStr">
         <is>
-          <t>T2 中底廠商</t>
+          <t>品包2組 (6,7,8,9)</t>
         </is>
       </c>
       <c r="K556" s="9" t="n">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="L556" s="9" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
     </row>
     <row r="557">
       <c r="A557" s="8" t="inlineStr">
         <is>
-          <t>T3 外包底料</t>
+          <t>品包3組 (10,11,12,YH)</t>
         </is>
       </c>
       <c r="K557" s="9" t="n">
-        <v>4</v>
+        <v>46</v>
       </c>
       <c r="L557" s="9" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
     </row>
     <row r="558">
       <c r="A558" s="8" t="inlineStr">
         <is>
-          <t>印刷高周波QC</t>
+          <t>掃描組</t>
         </is>
       </c>
       <c r="K558" s="9" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L558" s="9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" s="8" t="inlineStr">
         <is>
-          <t>外包QC部件</t>
+          <t>貼外箱標組</t>
         </is>
       </c>
       <c r="K559" s="9" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="L559" s="9" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="560">
       <c r="A560" s="8" t="inlineStr">
         <is>
-          <t>QCRB</t>
+          <t>QC 入庫和領料、樣品室</t>
         </is>
       </c>
       <c r="K560" s="9" t="n">
-        <v>49</v>
+        <v>16</v>
       </c>
       <c r="L560" s="9" t="n">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="561">
-      <c r="A561" s="8" t="inlineStr">
-        <is>
-          <t>外包 RB QC</t>
-        </is>
-      </c>
-      <c r="K561" s="9" t="n">
-        <v>8</v>
-      </c>
-      <c r="L561" s="9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="562">
-      <c r="A562" s="8" t="inlineStr">
-        <is>
-          <t>自動化中心/同材共裁</t>
-        </is>
-      </c>
-      <c r="K562" s="9" t="n">
-        <v>4</v>
-      </c>
-      <c r="L562" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" s="8" t="inlineStr">
-        <is>
-          <t>電腦針車 QC</t>
-        </is>
-      </c>
-      <c r="K563" s="9" t="n">
-        <v>14</v>
-      </c>
-      <c r="L563" s="9" t="n">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="564">
-      <c r="A564" s="8" t="inlineStr">
-        <is>
-          <t>QC 貼底課</t>
-        </is>
-      </c>
-      <c r="K564" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="L564" s="9" t="n">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="565">
-      <c r="A565" s="8" t="inlineStr">
-        <is>
-          <t>外包QC貼底</t>
-        </is>
-      </c>
-      <c r="K565" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L565" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="566">
-      <c r="A566" s="8" t="inlineStr">
-        <is>
-          <t>QC 1</t>
-        </is>
-      </c>
-      <c r="K566" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L566" s="9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="567">
-      <c r="A567" s="8" t="inlineStr">
-        <is>
-          <t>QC 2</t>
-        </is>
-      </c>
-      <c r="K567" s="9" t="n">
-        <v>12</v>
-      </c>
-      <c r="L567" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="568">
-      <c r="A568" s="8" t="inlineStr">
-        <is>
-          <t>QC 3</t>
-        </is>
-      </c>
-      <c r="K568" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L568" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="569">
-      <c r="A569" s="8" t="inlineStr">
-        <is>
-          <t>QC 5</t>
-        </is>
-      </c>
-      <c r="K569" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L569" s="9" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="570">
-      <c r="A570" s="8" t="inlineStr">
-        <is>
-          <t>QC 6</t>
-        </is>
-      </c>
-      <c r="K570" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L570" s="9" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="571">
-      <c r="A571" s="8" t="inlineStr">
-        <is>
-          <t>QC 7</t>
-        </is>
-      </c>
-      <c r="K571" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L571" s="9" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="572">
-      <c r="A572" s="8" t="inlineStr">
-        <is>
-          <t>QC 8</t>
-        </is>
-      </c>
-      <c r="K572" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L572" s="9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="573">
-      <c r="A573" s="8" t="inlineStr">
-        <is>
-          <t>QC 9</t>
-        </is>
-      </c>
-      <c r="K573" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L573" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="574">
-      <c r="A574" s="8" t="inlineStr">
-        <is>
-          <t>QC 10</t>
-        </is>
-      </c>
-      <c r="K574" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L574" s="9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="575">
-      <c r="A575" s="8" t="inlineStr">
-        <is>
-          <t>QC 11</t>
-        </is>
-      </c>
-      <c r="K575" s="9" t="n">
-        <v>11</v>
-      </c>
-      <c r="L575" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="576">
-      <c r="A576" s="8" t="inlineStr">
-        <is>
-          <t>QC 12</t>
-        </is>
-      </c>
-      <c r="K576" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="L576" s="9" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="577">
-      <c r="A577" s="8" t="inlineStr">
-        <is>
-          <t>QC YH</t>
-        </is>
-      </c>
-      <c r="K577" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="L577" s="9" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="578">
-      <c r="A578" s="8" t="inlineStr">
-        <is>
-          <t>QC YH（针车鞋面）</t>
-        </is>
-      </c>
-      <c r="K578" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L578" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="579">
-      <c r="A579" s="8" t="inlineStr">
-        <is>
-          <t>美城QC (成型）</t>
-        </is>
-      </c>
-      <c r="K579" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="L579" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="580">
-      <c r="A580" s="8" t="inlineStr">
-        <is>
-          <t>验货员</t>
-        </is>
-      </c>
-      <c r="K580" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L580" s="9" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="581">
-      <c r="A581" s="8" t="inlineStr">
-        <is>
-          <t>包裝員</t>
-        </is>
-      </c>
-      <c r="K581" s="9" t="n">
-        <v>22</v>
-      </c>
-      <c r="L581" s="9" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="582">
-      <c r="A582" s="8" t="inlineStr">
-        <is>
-          <t>验货员（专员）</t>
-        </is>
-      </c>
-      <c r="K582" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="L582" s="9" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="583">
-      <c r="A583" s="8" t="inlineStr">
-        <is>
-          <t>美兴QC（鞋面）</t>
-        </is>
-      </c>
-      <c r="K583" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="L583" s="9" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="584">
-      <c r="A584" s="8" t="inlineStr">
-        <is>
-          <t>JIATAI（鞋面）</t>
-        </is>
-      </c>
-      <c r="K584" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="L584" s="9" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="585">
-      <c r="A585" s="8" t="inlineStr">
-        <is>
-          <t>美君（鞋面）</t>
-        </is>
-      </c>
-      <c r="K585" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L585" s="9" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="586">
-      <c r="A586" s="8" t="inlineStr">
-        <is>
-          <t>品包1組 1,2,3,5)</t>
-        </is>
-      </c>
-      <c r="K586" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="L586" s="9" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="587">
-      <c r="A587" s="8" t="inlineStr">
-        <is>
-          <t>品包2組 (6,7,8,9)</t>
-        </is>
-      </c>
-      <c r="K587" s="9" t="n">
-        <v>39</v>
-      </c>
-      <c r="L587" s="9" t="n">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="588">
-      <c r="A588" s="8" t="inlineStr">
-        <is>
-          <t>品包3組 (10,11,12,YH)</t>
-        </is>
-      </c>
-      <c r="K588" s="9" t="n">
-        <v>46</v>
-      </c>
-      <c r="L588" s="9" t="n">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="589">
-      <c r="A589" s="8" t="inlineStr">
-        <is>
-          <t>掃描組</t>
-        </is>
-      </c>
-      <c r="K589" s="9" t="n">
-        <v>19</v>
-      </c>
-      <c r="L589" s="9" t="n">
         <v>16</v>
       </c>
     </row>
-    <row r="590">
-      <c r="A590" s="8" t="inlineStr">
-        <is>
-          <t>貼外箱標組</t>
-        </is>
-      </c>
-      <c r="K590" s="9" t="n">
-        <v>9</v>
-      </c>
-      <c r="L590" s="9" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="591">
-      <c r="A591" s="8" t="inlineStr">
-        <is>
-          <t>QC 入庫和領料、樣品室</t>
-        </is>
-      </c>
-      <c r="K591" s="9" t="n">
-        <v>16</v>
-      </c>
-      <c r="L591" s="9" t="n">
-        <v>16</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="582">
+  <mergeCells count="551">
     <mergeCell ref="B300:E300"/>
     <mergeCell ref="B422:E422"/>
     <mergeCell ref="B360:E360"/>
     <mergeCell ref="B74:E74"/>
+    <mergeCell ref="A364:L364"/>
     <mergeCell ref="B68:E68"/>
     <mergeCell ref="B201:E201"/>
     <mergeCell ref="B139:E139"/>
@@ -10040,19 +9514,18 @@
     <mergeCell ref="B399:E399"/>
     <mergeCell ref="B203:E203"/>
     <mergeCell ref="B374:E374"/>
-    <mergeCell ref="B489:K489"/>
     <mergeCell ref="B361:E361"/>
     <mergeCell ref="A559:J559"/>
     <mergeCell ref="B232:E232"/>
     <mergeCell ref="A546:J546"/>
     <mergeCell ref="B326:E326"/>
     <mergeCell ref="B215:E215"/>
-    <mergeCell ref="A494:L494"/>
-    <mergeCell ref="A561:J561"/>
+    <mergeCell ref="A496:J496"/>
     <mergeCell ref="B21:E21"/>
     <mergeCell ref="A548:J548"/>
     <mergeCell ref="B263:E263"/>
     <mergeCell ref="A560:J560"/>
+    <mergeCell ref="A498:J498"/>
     <mergeCell ref="B244:E244"/>
     <mergeCell ref="B425:E425"/>
     <mergeCell ref="B229:E229"/>
@@ -10068,12 +9541,13 @@
     <mergeCell ref="B348:E348"/>
     <mergeCell ref="B298:E298"/>
     <mergeCell ref="B285:E285"/>
-    <mergeCell ref="B456:E456"/>
+    <mergeCell ref="A514:J514"/>
     <mergeCell ref="B64:E64"/>
     <mergeCell ref="B51:E51"/>
     <mergeCell ref="B443:E443"/>
     <mergeCell ref="B237:E237"/>
     <mergeCell ref="A534:J534"/>
+    <mergeCell ref="A509:J509"/>
     <mergeCell ref="B16:E16"/>
     <mergeCell ref="B138:E138"/>
     <mergeCell ref="B209:E209"/>
@@ -10083,7 +9557,6 @@
     <mergeCell ref="A555:J555"/>
     <mergeCell ref="B301:E301"/>
     <mergeCell ref="A549:J549"/>
-    <mergeCell ref="B432:E432"/>
     <mergeCell ref="A536:J536"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B140:E140"/>
@@ -10094,27 +9567,24 @@
     <mergeCell ref="B77:E77"/>
     <mergeCell ref="B11:E11"/>
     <mergeCell ref="B253:E253"/>
-    <mergeCell ref="A567:J567"/>
     <mergeCell ref="B440:E440"/>
     <mergeCell ref="B240:E240"/>
-    <mergeCell ref="B505:K505"/>
-    <mergeCell ref="B499:K499"/>
     <mergeCell ref="B377:E377"/>
     <mergeCell ref="B29:E29"/>
-    <mergeCell ref="A562:J562"/>
     <mergeCell ref="B158:E158"/>
     <mergeCell ref="B329:E329"/>
     <mergeCell ref="B6:E6"/>
     <mergeCell ref="B316:E316"/>
-    <mergeCell ref="A591:J591"/>
+    <mergeCell ref="A504:J504"/>
+    <mergeCell ref="A491:J491"/>
     <mergeCell ref="B24:E24"/>
     <mergeCell ref="B95:E95"/>
-    <mergeCell ref="A385:L385"/>
     <mergeCell ref="B89:E89"/>
     <mergeCell ref="B393:E393"/>
     <mergeCell ref="B160:E160"/>
     <mergeCell ref="B331:E331"/>
     <mergeCell ref="B368:E368"/>
+    <mergeCell ref="A506:J506"/>
     <mergeCell ref="B306:E306"/>
     <mergeCell ref="B97:E97"/>
     <mergeCell ref="B153:E153"/>
@@ -10122,71 +9592,66 @@
     <mergeCell ref="B395:E395"/>
     <mergeCell ref="B72:E72"/>
     <mergeCell ref="B370:E370"/>
-    <mergeCell ref="A580:J580"/>
     <mergeCell ref="B184:E184"/>
     <mergeCell ref="B228:E228"/>
-    <mergeCell ref="B518:K518"/>
-    <mergeCell ref="A582:J582"/>
+    <mergeCell ref="A517:J517"/>
     <mergeCell ref="B42:E42"/>
     <mergeCell ref="B17:E17"/>
-    <mergeCell ref="A581:J581"/>
-    <mergeCell ref="A575:J575"/>
+    <mergeCell ref="A519:J519"/>
     <mergeCell ref="B148:E148"/>
     <mergeCell ref="B446:E446"/>
     <mergeCell ref="B250:E250"/>
     <mergeCell ref="B44:E44"/>
-    <mergeCell ref="A586:J586"/>
     <mergeCell ref="B19:E19"/>
-    <mergeCell ref="A583:J583"/>
     <mergeCell ref="B317:E317"/>
-    <mergeCell ref="A577:J577"/>
     <mergeCell ref="B448:E448"/>
+    <mergeCell ref="B467:K467"/>
     <mergeCell ref="B304:E304"/>
     <mergeCell ref="B108:E108"/>
     <mergeCell ref="B375:E375"/>
-    <mergeCell ref="A501:L501"/>
     <mergeCell ref="B83:E83"/>
     <mergeCell ref="B254:E254"/>
     <mergeCell ref="B319:E319"/>
-    <mergeCell ref="B477:E477"/>
     <mergeCell ref="B20:E20"/>
     <mergeCell ref="B85:E85"/>
+    <mergeCell ref="B256:E256"/>
     <mergeCell ref="B383:E383"/>
     <mergeCell ref="A530:J530"/>
     <mergeCell ref="B159:E159"/>
     <mergeCell ref="B401:E401"/>
-    <mergeCell ref="A576:J576"/>
+    <mergeCell ref="A505:J505"/>
     <mergeCell ref="B96:E96"/>
+    <mergeCell ref="B460:K460"/>
     <mergeCell ref="B167:E167"/>
     <mergeCell ref="B272:E272"/>
     <mergeCell ref="A532:J532"/>
     <mergeCell ref="B161:E161"/>
     <mergeCell ref="B332:E332"/>
-    <mergeCell ref="B459:E459"/>
     <mergeCell ref="B259:E259"/>
+    <mergeCell ref="A507:J507"/>
     <mergeCell ref="B111:E111"/>
     <mergeCell ref="B98:E98"/>
-    <mergeCell ref="A521:L521"/>
     <mergeCell ref="B225:E225"/>
     <mergeCell ref="B274:E274"/>
     <mergeCell ref="B396:E396"/>
-    <mergeCell ref="B461:E461"/>
-    <mergeCell ref="A571:J571"/>
+    <mergeCell ref="B480:K480"/>
     <mergeCell ref="B175:E175"/>
     <mergeCell ref="B162:E162"/>
     <mergeCell ref="B267:E267"/>
-    <mergeCell ref="B491:K491"/>
     <mergeCell ref="B398:E398"/>
     <mergeCell ref="B373:E373"/>
-    <mergeCell ref="A516:L516"/>
+    <mergeCell ref="A218:L218"/>
+    <mergeCell ref="B457:K457"/>
     <mergeCell ref="B269:E269"/>
-    <mergeCell ref="A453:L453"/>
+    <mergeCell ref="B486:K486"/>
     <mergeCell ref="A525:J525"/>
     <mergeCell ref="B325:E325"/>
     <mergeCell ref="A533:J533"/>
     <mergeCell ref="B45:E45"/>
+    <mergeCell ref="B458:K458"/>
     <mergeCell ref="B343:E343"/>
     <mergeCell ref="B414:E414"/>
+    <mergeCell ref="A518:J518"/>
     <mergeCell ref="B91:E91"/>
     <mergeCell ref="B389:E389"/>
     <mergeCell ref="B327:E327"/>
@@ -10202,30 +9667,31 @@
     <mergeCell ref="B264:E264"/>
     <mergeCell ref="B320:E320"/>
     <mergeCell ref="B391:E391"/>
+    <mergeCell ref="B385:E385"/>
+    <mergeCell ref="B483:K483"/>
+    <mergeCell ref="A520:J520"/>
     <mergeCell ref="B409:E409"/>
     <mergeCell ref="B86:E86"/>
     <mergeCell ref="B151:E151"/>
     <mergeCell ref="A551:J551"/>
+    <mergeCell ref="B468:K468"/>
     <mergeCell ref="B101:E101"/>
     <mergeCell ref="B182:E182"/>
     <mergeCell ref="A531:J531"/>
     <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B467:E467"/>
-    <mergeCell ref="B246:E246"/>
+    <mergeCell ref="A515:J515"/>
     <mergeCell ref="B40:E40"/>
     <mergeCell ref="B211:E211"/>
     <mergeCell ref="B338:E338"/>
-    <mergeCell ref="B469:E469"/>
-    <mergeCell ref="A579:J579"/>
+    <mergeCell ref="A508:J508"/>
     <mergeCell ref="B183:E183"/>
-    <mergeCell ref="A573:J573"/>
     <mergeCell ref="B177:E177"/>
     <mergeCell ref="B33:E33"/>
     <mergeCell ref="B104:E104"/>
     <mergeCell ref="B275:E275"/>
     <mergeCell ref="B164:E164"/>
     <mergeCell ref="B406:E406"/>
-    <mergeCell ref="B462:E462"/>
+    <mergeCell ref="B340:E340"/>
     <mergeCell ref="B114:E114"/>
     <mergeCell ref="B41:E41"/>
     <mergeCell ref="B212:E212"/>
@@ -10236,13 +9702,11 @@
     <mergeCell ref="B404:E404"/>
     <mergeCell ref="A5:L5"/>
     <mergeCell ref="B66:E66"/>
-    <mergeCell ref="B180:E180"/>
+    <mergeCell ref="B473:K473"/>
     <mergeCell ref="A526:J526"/>
     <mergeCell ref="B130:E130"/>
     <mergeCell ref="B117:E117"/>
-    <mergeCell ref="B508:K508"/>
     <mergeCell ref="B353:E353"/>
-    <mergeCell ref="B480:E480"/>
     <mergeCell ref="B67:E67"/>
     <mergeCell ref="A528:J528"/>
     <mergeCell ref="B61:E61"/>
@@ -10259,11 +9723,14 @@
     <mergeCell ref="A485:L485"/>
     <mergeCell ref="B127:E127"/>
     <mergeCell ref="B394:E394"/>
+    <mergeCell ref="B478:K478"/>
     <mergeCell ref="B265:E265"/>
-    <mergeCell ref="B458:E458"/>
     <mergeCell ref="A554:J554"/>
+    <mergeCell ref="A541:J541"/>
+    <mergeCell ref="B482:K482"/>
     <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B483:E483"/>
+    <mergeCell ref="B479:K479"/>
+    <mergeCell ref="B185:E185"/>
     <mergeCell ref="A539:J539"/>
     <mergeCell ref="B122:E122"/>
     <mergeCell ref="B56:E56"/>
@@ -10275,7 +9742,6 @@
     <mergeCell ref="B341:E341"/>
     <mergeCell ref="B347:E347"/>
     <mergeCell ref="B412:E412"/>
-    <mergeCell ref="B504:K504"/>
     <mergeCell ref="B120:E120"/>
     <mergeCell ref="B278:E278"/>
     <mergeCell ref="B405:E405"/>
@@ -10285,10 +9751,10 @@
     <mergeCell ref="B407:E407"/>
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B438:E438"/>
+    <mergeCell ref="A542:J542"/>
     <mergeCell ref="B359:E359"/>
     <mergeCell ref="A529:J529"/>
     <mergeCell ref="B133:E133"/>
-    <mergeCell ref="B497:K497"/>
     <mergeCell ref="B204:E204"/>
     <mergeCell ref="B198:E198"/>
     <mergeCell ref="B369:E369"/>
@@ -10304,21 +9770,24 @@
     <mergeCell ref="B227:E227"/>
     <mergeCell ref="B420:E420"/>
     <mergeCell ref="B202:E202"/>
-    <mergeCell ref="B492:K492"/>
+    <mergeCell ref="A324:L324"/>
     <mergeCell ref="B199:E199"/>
+    <mergeCell ref="A180:L180"/>
     <mergeCell ref="B435:E435"/>
     <mergeCell ref="B291:E291"/>
     <mergeCell ref="B70:E70"/>
+    <mergeCell ref="B465:K465"/>
     <mergeCell ref="B293:E293"/>
     <mergeCell ref="A547:J547"/>
     <mergeCell ref="B322:E322"/>
+    <mergeCell ref="A490:L490"/>
+    <mergeCell ref="A497:J497"/>
     <mergeCell ref="A557:J557"/>
     <mergeCell ref="B88:E88"/>
     <mergeCell ref="B82:E82"/>
     <mergeCell ref="B349:E349"/>
-    <mergeCell ref="B495:K495"/>
+    <mergeCell ref="A499:J499"/>
     <mergeCell ref="B128:E128"/>
-    <mergeCell ref="B364:E364"/>
     <mergeCell ref="B146:E146"/>
     <mergeCell ref="B413:E413"/>
     <mergeCell ref="B217:E217"/>
@@ -10328,27 +9797,24 @@
     <mergeCell ref="B428:E428"/>
     <mergeCell ref="B344:E344"/>
     <mergeCell ref="B415:E415"/>
+    <mergeCell ref="A494:J494"/>
     <mergeCell ref="B123:E123"/>
     <mergeCell ref="B221:E221"/>
     <mergeCell ref="B110:E110"/>
-    <mergeCell ref="B479:E479"/>
-    <mergeCell ref="A185:L185"/>
-    <mergeCell ref="A568:J568"/>
+    <mergeCell ref="A470:L470"/>
     <mergeCell ref="B141:E141"/>
     <mergeCell ref="B439:E439"/>
     <mergeCell ref="A552:J552"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="A570:J570"/>
     <mergeCell ref="B248:E248"/>
     <mergeCell ref="B441:E441"/>
-    <mergeCell ref="B517:K517"/>
+    <mergeCell ref="B297:E297"/>
     <mergeCell ref="B235:E235"/>
     <mergeCell ref="B362:E362"/>
     <mergeCell ref="B14:E14"/>
     <mergeCell ref="B136:E136"/>
     <mergeCell ref="B312:E312"/>
     <mergeCell ref="B299:E299"/>
-    <mergeCell ref="B470:E470"/>
     <mergeCell ref="B13:E13"/>
     <mergeCell ref="B78:E78"/>
     <mergeCell ref="B249:E249"/>
@@ -10358,39 +9824,36 @@
     <mergeCell ref="B376:E376"/>
     <mergeCell ref="B436:E436"/>
     <mergeCell ref="B363:E363"/>
-    <mergeCell ref="A256:L256"/>
-    <mergeCell ref="A563:J563"/>
     <mergeCell ref="A550:J550"/>
     <mergeCell ref="B154:E154"/>
     <mergeCell ref="B390:E390"/>
+    <mergeCell ref="A500:J500"/>
     <mergeCell ref="B129:E129"/>
-    <mergeCell ref="A565:J565"/>
     <mergeCell ref="B365:E365"/>
     <mergeCell ref="B25:E25"/>
     <mergeCell ref="B156:E156"/>
-    <mergeCell ref="B454:E454"/>
-    <mergeCell ref="A564:J564"/>
+    <mergeCell ref="A502:J502"/>
     <mergeCell ref="B131:E131"/>
     <mergeCell ref="B429:E429"/>
-    <mergeCell ref="B513:K513"/>
-    <mergeCell ref="B465:E465"/>
+    <mergeCell ref="B223:E223"/>
     <mergeCell ref="B220:E220"/>
     <mergeCell ref="B247:E247"/>
+    <mergeCell ref="A432:L432"/>
     <mergeCell ref="B195:E195"/>
     <mergeCell ref="B431:E431"/>
     <mergeCell ref="B231:E231"/>
     <mergeCell ref="B287:E287"/>
     <mergeCell ref="B262:E262"/>
     <mergeCell ref="B53:E53"/>
-    <mergeCell ref="B514:K514"/>
     <mergeCell ref="B289:E289"/>
-    <mergeCell ref="A340:L340"/>
-    <mergeCell ref="A578:J578"/>
-    <mergeCell ref="A486:L486"/>
+    <mergeCell ref="A511:L511"/>
     <mergeCell ref="A553:J553"/>
     <mergeCell ref="B84:E84"/>
+    <mergeCell ref="B481:K481"/>
+    <mergeCell ref="B456:K456"/>
     <mergeCell ref="B434:E434"/>
     <mergeCell ref="B15:E15"/>
+    <mergeCell ref="A513:J513"/>
     <mergeCell ref="B142:E142"/>
     <mergeCell ref="B313:E313"/>
     <mergeCell ref="B80:E80"/>
@@ -10403,24 +9866,22 @@
     <mergeCell ref="B386:E386"/>
     <mergeCell ref="B442:E442"/>
     <mergeCell ref="B242:E242"/>
+    <mergeCell ref="A489:L489"/>
     <mergeCell ref="B302:E302"/>
     <mergeCell ref="B81:E81"/>
     <mergeCell ref="B252:E252"/>
     <mergeCell ref="B208:E208"/>
     <mergeCell ref="B366:E366"/>
-    <mergeCell ref="A589:J589"/>
-    <mergeCell ref="B460:E460"/>
     <mergeCell ref="B210:E210"/>
     <mergeCell ref="B381:E381"/>
+    <mergeCell ref="A501:J501"/>
     <mergeCell ref="A59:L59"/>
     <mergeCell ref="B318:E318"/>
-    <mergeCell ref="A572:J572"/>
-    <mergeCell ref="A566:J566"/>
     <mergeCell ref="B170:E170"/>
     <mergeCell ref="B437:E437"/>
     <mergeCell ref="B157:E157"/>
     <mergeCell ref="B333:E333"/>
-    <mergeCell ref="B455:E455"/>
+    <mergeCell ref="A503:J503"/>
     <mergeCell ref="B234:E234"/>
     <mergeCell ref="B34:E34"/>
     <mergeCell ref="B172:E172"/>
@@ -10428,46 +9889,40 @@
     <mergeCell ref="B99:E99"/>
     <mergeCell ref="B270:E270"/>
     <mergeCell ref="B397:E397"/>
-    <mergeCell ref="B457:E457"/>
     <mergeCell ref="B257:E257"/>
     <mergeCell ref="B239:E239"/>
     <mergeCell ref="B92:E92"/>
     <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B502:K502"/>
     <mergeCell ref="B94:E94"/>
-    <mergeCell ref="A584:J584"/>
+    <mergeCell ref="A521:J521"/>
     <mergeCell ref="B150:E150"/>
     <mergeCell ref="B125:E125"/>
     <mergeCell ref="B321:E321"/>
-    <mergeCell ref="B475:E475"/>
-    <mergeCell ref="A585:J585"/>
     <mergeCell ref="A523:J523"/>
     <mergeCell ref="B152:E152"/>
     <mergeCell ref="B323:E323"/>
     <mergeCell ref="B450:E450"/>
-    <mergeCell ref="B468:E468"/>
     <mergeCell ref="A143:L143"/>
+    <mergeCell ref="A516:J516"/>
     <mergeCell ref="B145:E145"/>
     <mergeCell ref="B387:E387"/>
     <mergeCell ref="B181:E181"/>
     <mergeCell ref="B452:E452"/>
+    <mergeCell ref="B471:K471"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="B258:E258"/>
     <mergeCell ref="B147:E147"/>
     <mergeCell ref="B451:E451"/>
+    <mergeCell ref="B464:K464"/>
     <mergeCell ref="B245:E245"/>
-    <mergeCell ref="B481:E481"/>
-    <mergeCell ref="B510:K510"/>
-    <mergeCell ref="A507:L507"/>
     <mergeCell ref="B260:E260"/>
-    <mergeCell ref="A574:J574"/>
-    <mergeCell ref="B490:K490"/>
-    <mergeCell ref="B463:E463"/>
+    <mergeCell ref="B472:K472"/>
+    <mergeCell ref="B466:K466"/>
+    <mergeCell ref="B477:K477"/>
     <mergeCell ref="B36:E36"/>
     <mergeCell ref="B207:E207"/>
     <mergeCell ref="B163:E163"/>
     <mergeCell ref="B334:E334"/>
-    <mergeCell ref="A569:J569"/>
     <mergeCell ref="B113:E113"/>
     <mergeCell ref="B173:E173"/>
     <mergeCell ref="B137:E137"/>
@@ -10477,26 +9932,24 @@
     <mergeCell ref="B336:E336"/>
     <mergeCell ref="B115:E115"/>
     <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B473:E473"/>
     <mergeCell ref="B102:E102"/>
     <mergeCell ref="B273:E273"/>
+    <mergeCell ref="A454:L454"/>
     <mergeCell ref="B400:E400"/>
-    <mergeCell ref="B503:K503"/>
     <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B459:K459"/>
     <mergeCell ref="B402:E402"/>
+    <mergeCell ref="A455:L455"/>
+    <mergeCell ref="B461:K461"/>
     <mergeCell ref="A522:J522"/>
-    <mergeCell ref="A520:L520"/>
-    <mergeCell ref="A587:J587"/>
     <mergeCell ref="B191:E191"/>
     <mergeCell ref="B178:E178"/>
-    <mergeCell ref="B476:E476"/>
     <mergeCell ref="A524:J524"/>
     <mergeCell ref="B255:E255"/>
     <mergeCell ref="B226:E226"/>
     <mergeCell ref="B426:E426"/>
     <mergeCell ref="B49:E49"/>
-    <mergeCell ref="B478:E478"/>
-    <mergeCell ref="A588:J588"/>
+    <mergeCell ref="A246:L246"/>
     <mergeCell ref="B266:E266"/>
     <mergeCell ref="B284:E284"/>
     <mergeCell ref="B222:E222"/>
@@ -10505,25 +9958,21 @@
     <mergeCell ref="B26:E26"/>
     <mergeCell ref="B197:E197"/>
     <mergeCell ref="B268:E268"/>
-    <mergeCell ref="B324:E324"/>
-    <mergeCell ref="A297:L297"/>
-    <mergeCell ref="B50:E50"/>
     <mergeCell ref="B330:E330"/>
     <mergeCell ref="B487:K487"/>
-    <mergeCell ref="B482:E482"/>
-    <mergeCell ref="B286:E286"/>
+    <mergeCell ref="B50:E50"/>
+    <mergeCell ref="B474:K474"/>
     <mergeCell ref="B90:E90"/>
     <mergeCell ref="B261:E261"/>
     <mergeCell ref="B27:E27"/>
-    <mergeCell ref="B488:K488"/>
+    <mergeCell ref="A492:J492"/>
     <mergeCell ref="A535:J535"/>
-    <mergeCell ref="B471:E471"/>
     <mergeCell ref="B179:E179"/>
     <mergeCell ref="A537:J537"/>
     <mergeCell ref="B166:E166"/>
     <mergeCell ref="B337:E337"/>
     <mergeCell ref="B408:E408"/>
-    <mergeCell ref="B464:E464"/>
+    <mergeCell ref="A512:J512"/>
     <mergeCell ref="B116:E116"/>
     <mergeCell ref="B352:E352"/>
     <mergeCell ref="B103:E103"/>
@@ -10535,23 +9984,18 @@
     <mergeCell ref="B339:E339"/>
     <mergeCell ref="B410:E410"/>
     <mergeCell ref="B423:E423"/>
-    <mergeCell ref="B466:E466"/>
-    <mergeCell ref="B472:E472"/>
     <mergeCell ref="B118:E118"/>
-    <mergeCell ref="B496:K496"/>
+    <mergeCell ref="A463:L463"/>
+    <mergeCell ref="A286:L286"/>
     <mergeCell ref="B281:E281"/>
     <mergeCell ref="B403:E403"/>
     <mergeCell ref="B55:E55"/>
-    <mergeCell ref="A223:L223"/>
-    <mergeCell ref="B511:K511"/>
     <mergeCell ref="B169:E169"/>
-    <mergeCell ref="B498:K498"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B355:E355"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B200:E200"/>
     <mergeCell ref="B134:E134"/>
-    <mergeCell ref="A590:J590"/>
     <mergeCell ref="B194:E194"/>
     <mergeCell ref="B121:E121"/>
     <mergeCell ref="B292:E292"/>
@@ -10570,11 +10014,13 @@
     <mergeCell ref="B358:E358"/>
     <mergeCell ref="A107:L107"/>
     <mergeCell ref="A556:J556"/>
+    <mergeCell ref="A476:L476"/>
     <mergeCell ref="A543:J543"/>
     <mergeCell ref="A558:J558"/>
     <mergeCell ref="B187:E187"/>
     <mergeCell ref="A545:J545"/>
     <mergeCell ref="B447:E447"/>
+    <mergeCell ref="A495:J495"/>
     <mergeCell ref="B241:E241"/>
     <mergeCell ref="B124:E124"/>
     <mergeCell ref="B251:E251"/>
@@ -10582,28 +10028,24 @@
     <mergeCell ref="A538:J538"/>
     <mergeCell ref="B216:E216"/>
     <mergeCell ref="B213:E213"/>
-    <mergeCell ref="B474:E474"/>
     <mergeCell ref="B449:E449"/>
     <mergeCell ref="B305:E305"/>
     <mergeCell ref="B188:E188"/>
     <mergeCell ref="B126:E126"/>
     <mergeCell ref="B424:E424"/>
     <mergeCell ref="B280:E280"/>
-    <mergeCell ref="B218:E218"/>
     <mergeCell ref="B351:E351"/>
     <mergeCell ref="B411:E411"/>
     <mergeCell ref="B190:E190"/>
     <mergeCell ref="B295:E295"/>
     <mergeCell ref="B46:E46"/>
-    <mergeCell ref="A542:L542"/>
     <mergeCell ref="B282:E282"/>
-    <mergeCell ref="B512:K512"/>
     <mergeCell ref="B48:E48"/>
     <mergeCell ref="B219:E219"/>
-    <mergeCell ref="B509:K509"/>
     <mergeCell ref="B346:E346"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B73:E73"/>
+    <mergeCell ref="A493:J493"/>
     <mergeCell ref="B371:E371"/>
     <mergeCell ref="B10:E10"/>
     <mergeCell ref="B308:E308"/>
